--- a/outputs/weekly_unit_change_database.xlsx
+++ b/outputs/weekly_unit_change_database.xlsx
@@ -8,15 +8,23 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="房源变化" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前房源数据库" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="价单导入情况" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="降价房源" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增房源" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="售出房源" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="其他变化" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前房源数据库" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="价单导入情况" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'房源变化'!$A$1:$N$110</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'当前房源数据库'!$A$1:$J$698</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'价单导入情况'!$A$1:$I$77</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'版本记录'!$A$1:$F$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'降价房源'!$A$1:$N$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'新增房源'!$A$1:$N$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'售出房源'!$A$1:$N$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'其他变化'!$A$1:$N$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'当前房源数据库'!$A$1:$J$698</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'价单导入情况'!$A$1:$I$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'版本记录'!$A$1:$F$153</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -6491,6 +6499,6366 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:N18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>楼盘名</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>房号</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>居室</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>朝向</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>原售价</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>原售价生效日期</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>现售价</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>现售价生效日期</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>变化类型</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>原状态</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>现状态</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>价格变化</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>入库时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>City Reach</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Third</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>North/East</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>496000</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>22.05.2026</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>479950</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>01.07.2026</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>PRICE_DROP</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="n">
+        <v>-16050</v>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:04:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>City Reach</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Ground</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>North/East</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>357500</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>22.05.2026</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>349950</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>01.07.2026</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>PRICE_DROP</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="n">
+        <v>-7550</v>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:04:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>City Reach</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>First</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>North/West</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>485500</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>22.05.2026</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>469950</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>01.07.2026</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>PRICE_DROP</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="n">
+        <v>-15550</v>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:04:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>RM9 - Eastbrook Village</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="3" t="n">
+        <v>454000</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>24.06.2026</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>450000</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>03.07.2026</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>PRICE_DROP</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="n">
+        <v>-4000</v>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:57:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>RM9 - Eastbrook Village</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="3" t="n">
+        <v>464000</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>24.06.2026</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>457000</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>03.07.2026</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>PRICE_DROP</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="n">
+        <v>-7000</v>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:57:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>RM9 - Eastbrook Village</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="3" t="n">
+        <v>457000</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>24.06.2026</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>452000</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>03.07.2026</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>PRICE_DROP</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:57:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>RM9 - Eastbrook Village</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="3" t="n">
+        <v>457000</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>24.06.2026</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>452000</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>03.07.2026</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>PRICE_DROP</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:57:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>RM9 - Eastbrook Village</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="3" t="n">
+        <v>465000</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>24.06.2026</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>457000</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>03.07.2026</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>PRICE_DROP</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="n">
+        <v>-8000</v>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:57:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>RM9 - Eastbrook Village</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="3" t="n">
+        <v>568000</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>24.06.2026</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>555000</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>03.07.2026</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>PRICE_DROP</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="n">
+        <v>-13000</v>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:57:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>RM9 - Eastbrook Village</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="3" t="n">
+        <v>568000</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>24.06.2026</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>555000</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>03.07.2026</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>PRICE_DROP</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="n">
+        <v>-13000</v>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:57:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>RM9 - Eastbrook Village</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="3" t="n">
+        <v>568000</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>24.06.2026</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>555000</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>03.07.2026</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>PRICE_DROP</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="n">
+        <v>-13000</v>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:57:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>RM9 - Eastbrook Village</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="3" t="n">
+        <v>568000</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>24.06.2026</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>555000</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>03.07.2026</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>PRICE_DROP</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="n">
+        <v>-13000</v>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:57:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>RM9 - Eastbrook Village</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="3" t="n">
+        <v>461000</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>24.06.2026</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>460000</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>03.07.2026</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>PRICE_DROP</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:57:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>SE1 - Bermondsey Place</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>B2.7.04</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>North-East Dual Aspect</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>747500</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>25.06.2026</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>737500</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>04.07.2026</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>PRICE_DROP</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:52:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>SW6 - King's Road Park</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>H1-19-06</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3 Bedroom</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>South / West</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>2975500</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>28.06.2026</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>2975000</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>05.07.2026</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>PRICE_DROP</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="n">
+        <v>-500</v>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:53:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>W12 - White City Living</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>W.30.01</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>30/31</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Penthouse</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>South/West/North</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>27.06.26</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>3990000</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>02.07.26</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>PRICE_DROP</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:01:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>W12 - White City Living</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>W.30.02</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>30/31</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Penthouse</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>South/East/North</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>27.06.26</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>3990000</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>02.07.26</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>PRICE_DROP</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:01:26</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N18"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>楼盘名</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>房号</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>居室</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>朝向</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>原售价</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>原售价生效日期</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>现售价</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>现售价生效日期</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>变化类型</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>原状态</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>现状态</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>价格变化</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>入库时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>B4 - Glasswater Locks</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2 Bed</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>13.06.26</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>300000</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:58:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>B4 - Glasswater Locks</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2 Bed</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>10.06.26</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>435000</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:58:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>B4 - Glasswater Locks</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1 bed</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>10.06.26</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>275000</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:58:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>E1 - London Dock</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>1236</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>1335000</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="n"/>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:59:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>E1 - London Dock</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>1268</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>797000</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:59:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>E1 - London Dock</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>827 - SA</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>708000</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>BACK_ON_MARKET</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>RESERVED</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>AVAILABLE</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:00:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>E2 - Regent's View</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>D.06.09</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>29.06.2026</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>579000</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>06.07.2026</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:00:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>E2 - Regent's View</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>D.07.08</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>North/East</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>29.06.2026</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>900000</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>06.07.2026</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="n"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:00:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>E2 - Regent's View</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>D.08.05</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>29.06.2026</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>910000</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>06.07.2026</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:00:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>E2 - Regent's View</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>D.08.06</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>North/East</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>29.06.2026</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>915000</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>06.07.2026</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="n"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:00:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>E3 - Bow Green</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>B6.06 Reserved</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Bow Green - ready to move in Core B Pricelist</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>610000</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Bow Green Ready to Move In_Core B Pricelist</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="n"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>E3 - Bow Green</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>B7.03 Reserved</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>North East</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Bow Green - ready to move in Core B Pricelist</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>620000</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Bow Green Ready to Move In_Core B Pricelist</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="n"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Marleigh Park</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>D11</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>South/East</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>22.05.2026</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>399950</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>01.07.2026</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:04:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>SE1 - Bermondsey (London Square)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>16.06.26</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>29.06.26</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="n"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>SE1 - Bermondsey (London Square)</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2 Bed 2 Bath</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>16.06.26</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>855000</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>29.06.26</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>SE1 - Bermondsey (London Square)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>16.06.26</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>29.06.26</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>SE1 - Bermondsey (London Square)</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>16.06.26</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>650000</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>29.06.26</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>SE17 - The Wilderly</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>11B.A.06.01</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>West &amp; North East</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>743000</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>July 2026</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SE17 - The Wilderly</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>11B.A.06.02</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>North East</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>1040000</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>July 2026</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>SE17 - The Wilderly</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>11B.A.06.03</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>North East</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>1035000</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>July 2026</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="n"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SE17 - The Wilderly</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>11B.A.06.04</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>1036000</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>July 2026</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SE17 - The Wilderly</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>11B.A.06.05</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>South East</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>774000</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>July 2026</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="n"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>SE17 - The Wilderly</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>11B.A.06.06</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>July 2026</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>SE17 - The Wilderly</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>11B.A.06.07</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>South West</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>1045000</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>July 2026</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="n"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>SE17 - The Wilderly</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>11B.A.06.08</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>1040000</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>July 2026</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="n"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>SE17 - The Wilderly</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>11B.A.17.01</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>West &amp; North East</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>850000</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>July 2026</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="n"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>SE17 - The Wilderly</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>11B.A.17.02</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>North East</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>July 2026</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="n"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>SE17 - The Wilderly</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>11B.A.17.03</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>North East</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>1195000</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>July 2026</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="n"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>SE17 - The Wilderly</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>11B.A.17.04</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>1153000</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>July 2026</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>SE17 - The Wilderly</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>11B.A.17.05</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>South East</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>857000</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>July 2026</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="n"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>SE17 - The Wilderly</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>11B.A.17.06</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>837000</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>July 2026</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="n"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>SE17 - The Wilderly</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>11B.A.17.07</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>South West</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>1170000</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>July 2026</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="n"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>SE3 - Kidbrooke Village</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>2-3-4</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>29.06.26</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>06.07.26</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Show Apartment</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:53:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>SW19 - Wimbledon Bridge House (London Square)</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>1 Bed</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>15.06.26</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>29.06.26</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="n"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>SW19 - Wimbledon Bridge House (London Square)</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>2 Bed</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>15.06.26</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>1185000</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>29.06.26</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="n"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>SW19 - Wimbledon Bridge House (London Square)</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>1 Bed</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>15.06.26</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>710000</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>29.06.26</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="n"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>SW19 - Wimbledon Bridge House (London Square)</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Suite</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>15.06.26</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>512500</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>29.06.26</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="n"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>SW19 - Wimbledon Bridge House (London Square)</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Suite</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="n"/>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>15.06.26</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>507500</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>29.06.26</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="n"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>SW19 - Wimbledon Bridge House (London Square)</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Suite</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="n"/>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>15.06.26</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>517500</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>29.06.26</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="n"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>SW19 - Wimbledon Bridge House (London Square)</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>1 Bed</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>15.06.26</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>720000</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>29.06.26</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="n"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>SW6 - Chelsea Waterfront Tower East</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>30.2</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="n"/>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>8th June 2026</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>5842000</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>29th June 2026</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="n"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>SW6 - King's Road Park</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>G1.3-01-04</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>2 Bedroom</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>S/W - Park Views</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="n"/>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>28.06.2026</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>1370000</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>05.07.2026</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="n"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:53:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>SW6 - King's Road Park</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>G1.4-00-06</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>2 Bedroom</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>S – Park Views</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>28.06.2026</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="n"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>05.07.2026</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="n"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:53:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>UB1 - The Green Quarter</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>2 Bed 2.5 Bath</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>N &amp; W</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>2350</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="n"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:00:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>W12 - White City Living</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>W.14.03</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>North/East</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n"/>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>27.06.26</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>775000</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>02.07.26</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="n"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:01:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>W2 - Trillium</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>I.01.07</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>North/West</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="n"/>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="n"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>W2 - Trillium</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>I.08.05</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>South/West</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="n"/>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="n"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="n"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>W2 - Trillium</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>I.10.07</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>North/West</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="n"/>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="n"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>W2 - Trillium</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>I.14.01</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>North/East</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>1598500</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="n"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>W2 - Trillium</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>I.14.06</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="n"/>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="n"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="n"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>W2 - Trillium</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>I.17.03</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="n"/>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="n"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="n"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>W2 - Trillium</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>I.20.06</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>North/West</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="n"/>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>2505000</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="n"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:04</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N53"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>楼盘名</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>房号</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>居室</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>朝向</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>原售价</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>原售价生效日期</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>现售价</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>现售价生效日期</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>变化类型</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>原状态</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>现状态</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>价格变化</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>入库时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>B4 - Glasswater Locks</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>002 (Show Home)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2 Bed</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="3" t="n">
+        <v>435000</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>10.06.26</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:58:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>E1 - London Dock</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="3" t="n">
+        <v>806000</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:59:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>E2 - Regent's View</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>D.08.08</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>North/East</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>915000</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>29.06.2026</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>06.07.2026</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:00:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>E2 - Regent's View</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>D.10.05</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>935000</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>29.06.2026</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>06.07.2026</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n"/>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:00:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>E3 - Bow Green</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>B5.02 Reserved</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>South West</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>610000</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Bow Green - ready to move in Core B Pricelist</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Bow Green Ready to Move In_Core B Pricelist</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>E3 - Bow Green</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>B6.06</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>610000</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Bow Green - ready to move in Core B Pricelist</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Bow Green Ready to Move In_Core B Pricelist</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>E3 - Bow Green</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>B7.03</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>North East</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>620000</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Bow Green - ready to move in Core B Pricelist</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Bow Green Ready to Move In_Core B Pricelist</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Marleigh Park</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>GF</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>South/East</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>399950</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>22.05.2026</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>01.07.2026</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:04:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Marleigh Park</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>D25</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>South/East</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>399950</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>22.05.2026</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>01.07.2026</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:04:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>SE1 - Bermondsey (London Square)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>645000</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>16.06.26</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>29.06.26</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SE1 - Bermondsey (London Square)</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>16.06.26</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>29.06.26</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>SE11 - Oval Village</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>B1.17.1</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>YY</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Triple</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>28.06.2026</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>05.07.2026</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>RESERVED</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:55:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>SE11 - Oval Village</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>B1.17.2</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>28.06.2026</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>05.07.2026</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:55:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>SE11 - Oval Village</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>B2.1.6</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1B, 1B</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>28.06.2026</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>05.07.2026</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:55:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>SW19 - Wimbledon Bridge House (London Square)</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2 Bed</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1225000</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>15.06.26</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>29.06.26</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>SW19 - Wimbledon Bridge House (London Square)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Suite</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>502500</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>15.06.26</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>29.06.26</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>SW19 - Wimbledon Bridge House (London Square)</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Suite</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>512500</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>15.06.26</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>29.06.26</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>SW19 - Wimbledon Bridge House (London Square)</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1 Bed</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>15.06.26</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>29.06.26</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SW19 - Wimbledon Bridge House (London Square)</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1 Bed</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>597500</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>15.06.26</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>29.06.26</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>SW19 - Wimbledon Bridge House (London Square)</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Suite</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>517500</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>15.06.26</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>29.06.26</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SW19 - Wimbledon Bridge House (London Square)</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1 Bed</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>South East</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>740000</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>15.06.26</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>29.06.26</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SW6 - Chelsea Waterfront Tower East</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>14.2</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>8th June 2026</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>29th June 2026</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:02:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>W12 - White City Living</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>W.08.01</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>North/West</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>775000</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>27.06.26</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>02.07.26</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:01:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>W12 - White City Living</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>W.14.01</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>North/West</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>27.06.26</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>02.07.26</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:01:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>W2 - Trillium</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>I.02.05</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>South/ West</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>W2 - Trillium</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>I.02.07</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>North/West</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>W2 - Trillium</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>I.07.07</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>North/West</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>2005000</v>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>W2 - Trillium</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>I.13.01</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>North/East</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>W2 - Trillium</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>I.13.07</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>North/West</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>2181500</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>W2 - Trillium</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>I.15.03</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>1199000</v>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>W2 - Trillium</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>I.15.05</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>South/West</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>W2 - Trillium</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>I.17.04</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>1115000</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>W2 - Trillium</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>I.20.01</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>North/East</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>1845000</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>W2 - Trillium</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>I.22.01</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>North/East</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>1897000</v>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>W2 - Trillium</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>I.22.04*</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>1205000</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:04</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N36"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>楼盘名</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>房号</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>居室</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>朝向</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>原售价</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>原售价生效日期</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>现售价</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>现售价生效日期</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>变化类型</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>原状态</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>现状态</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>价格变化</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>入库时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>RM9 - Eastbrook Village</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="3" t="n">
+        <v>460000</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>24.06.2026</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>462000</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>03.07.2026</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>PRICE_INCREASE</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:57:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>RM9 - Eastbrook Village</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="3" t="n">
+        <v>460000</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>24.06.2026</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>465000</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>03.07.2026</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>PRICE_INCREASE</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:57:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SE11 - Oval Village</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>B1.18.2</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1450000</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>28.06.2026</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>1475000</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>05.07.2026</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>PRICE_INCREASE</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>25000</v>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:55:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>UB1 - The Green Quarter</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2 Bed 2.5 Bath</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>N &amp; W</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>1850</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>2375</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>PRICE_INCREASE</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="n">
+        <v>525</v>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:00:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>UB1 - The Green Quarter</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2 Bed 2.5 Bath</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>N &amp; W</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>1875</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>2400</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>PRICE_INCREASE</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="n">
+        <v>525</v>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:00:58</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -36624,7 +42992,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -39349,7 +45717,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/outputs/weekly_unit_change_database.xlsx
+++ b/outputs/weekly_unit_change_database.xlsx
@@ -17,14 +17,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'房源变化'!$A$1:$N$110</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'降价房源'!$A$1:$N$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'房源变化'!$A$1:$N$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'降价房源'!$A$1:$N$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'新增房源'!$A$1:$N$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'售出房源'!$A$1:$N$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'其他变化'!$A$1:$N$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'当前房源数据库'!$A$1:$J$698</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'当前房源数据库'!$A$1:$J$712</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'价单导入情况'!$A$1:$I$77</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'版本记录'!$A$1:$F$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'版本记录'!$A$1:$F$155</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N110"/>
+  <dimension ref="A1:N111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -5211,32 +5211,34 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>W.14.03</t>
+          <t>V18.02</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3+Study</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>North/East</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="n"/>
+          <t>South/West/North</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>2850000</v>
+      </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
           <t>27.06.26</t>
         </is>
       </c>
       <c r="H88" s="3" t="n">
-        <v>775000</v>
+        <v>2815000</v>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
@@ -5245,15 +5247,17 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>NEW_RELEASE</t>
+          <t>PRICE_DROP</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr"/>
-      <c r="M88" s="2" t="n"/>
+      <c r="M88" s="2" t="n">
+        <v>-35000</v>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-09T09:53:11</t>
         </is>
       </c>
     </row>
@@ -5265,34 +5269,32 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>W.30.01</t>
+          <t>W.14.03</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>30/31</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Penthouse</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>South/West/North</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="n">
-        <v>4000000</v>
-      </c>
+          <t>North/East</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="n"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
           <t>27.06.26</t>
         </is>
       </c>
       <c r="H89" s="3" t="n">
-        <v>3990000</v>
+        <v>775000</v>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
@@ -5301,14 +5303,12 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>PRICE_DROP</t>
+          <t>NEW_RELEASE</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr"/>
-      <c r="M89" s="2" t="n">
-        <v>-10000</v>
-      </c>
+      <c r="M89" s="2" t="n"/>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>2026-07-08T17:01:26</t>
@@ -5323,7 +5323,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>W.30.02</t>
+          <t>W.30.01</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>South/East/North</t>
+          <t>South/West/North</t>
         </is>
       </c>
       <c r="F90" s="3" t="n">
@@ -5381,33 +5381,35 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>W.08.01</t>
+          <t>W.30.02</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>30/31</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Penthouse</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
+          <t>South/East/North</t>
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>775000</v>
+        <v>4000000</v>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
           <t>27.06.26</t>
         </is>
       </c>
-      <c r="H91" s="2" t="n"/>
+      <c r="H91" s="3" t="n">
+        <v>3990000</v>
+      </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
           <t>02.07.26</t>
@@ -5415,16 +5417,14 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>SOLD</t>
+          <t>PRICE_DROP</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>缺失</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="n"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="n">
+        <v>-10000</v>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>2026-07-08T17:01:26</t>
@@ -5439,12 +5439,12 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>W.14.01</t>
+          <t>W.08.01</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -5457,7 +5457,9 @@
           <t>North/West</t>
         </is>
       </c>
-      <c r="F92" s="2" t="n"/>
+      <c r="F92" s="3" t="n">
+        <v>775000</v>
+      </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
           <t>27.06.26</t>
@@ -5490,22 +5492,22 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>I.01.07</t>
+          <t>W.14.01</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -5516,26 +5518,30 @@
       <c r="F93" s="2" t="n"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>28.06.26</t>
+          <t>27.06.26</t>
         </is>
       </c>
       <c r="H93" s="2" t="n"/>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>05.07.26</t>
+          <t>02.07.26</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>NEW_RELEASE</t>
+          <t>SOLD</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
-      <c r="L93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
       <c r="M93" s="2" t="n"/>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:04</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
     </row>
@@ -5547,22 +5553,22 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>I.08.05</t>
+          <t>I.01.07</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>South/West</t>
+          <t>North/West</t>
         </is>
       </c>
       <c r="F94" s="2" t="n"/>
@@ -5599,22 +5605,22 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>I.10.07</t>
+          <t>I.08.05</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
+          <t>South/West</t>
         </is>
       </c>
       <c r="F95" s="2" t="n"/>
@@ -5651,22 +5657,22 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>I.14.01</t>
+          <t>I.10.07</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>North/East</t>
+          <t>North/West</t>
         </is>
       </c>
       <c r="F96" s="2" t="n"/>
@@ -5675,9 +5681,7 @@
           <t>28.06.26</t>
         </is>
       </c>
-      <c r="H96" s="3" t="n">
-        <v>1598500</v>
-      </c>
+      <c r="H96" s="2" t="n"/>
       <c r="I96" s="2" t="inlineStr">
         <is>
           <t>05.07.26</t>
@@ -5705,7 +5709,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>I.14.06</t>
+          <t>I.14.01</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -5715,12 +5719,12 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>North/East</t>
         </is>
       </c>
       <c r="F97" s="2" t="n"/>
@@ -5729,7 +5733,9 @@
           <t>28.06.26</t>
         </is>
       </c>
-      <c r="H97" s="2" t="n"/>
+      <c r="H97" s="3" t="n">
+        <v>1598500</v>
+      </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
           <t>05.07.26</t>
@@ -5757,22 +5763,22 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>I.17.03</t>
+          <t>I.14.06</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>West</t>
         </is>
       </c>
       <c r="F98" s="2" t="n"/>
@@ -5809,22 +5815,22 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>I.20.06</t>
+          <t>I.17.03</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
+          <t>South</t>
         </is>
       </c>
       <c r="F99" s="2" t="n"/>
@@ -5833,9 +5839,7 @@
           <t>28.06.26</t>
         </is>
       </c>
-      <c r="H99" s="3" t="n">
-        <v>2505000</v>
-      </c>
+      <c r="H99" s="2" t="n"/>
       <c r="I99" s="2" t="inlineStr">
         <is>
           <t>05.07.26</t>
@@ -5863,33 +5867,33 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>I.02.05</t>
+          <t>I.20.06</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>South/ West</t>
-        </is>
-      </c>
-      <c r="F100" s="3" t="n">
-        <v>1350000</v>
-      </c>
+          <t>North/West</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="n"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
           <t>28.06.26</t>
         </is>
       </c>
-      <c r="H100" s="2" t="n"/>
+      <c r="H100" s="3" t="n">
+        <v>2505000</v>
+      </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
           <t>05.07.26</t>
@@ -5897,15 +5901,11 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>SOLD</t>
+          <t>NEW_RELEASE</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr"/>
-      <c r="L100" s="2" t="inlineStr">
-        <is>
-          <t>缺失</t>
-        </is>
-      </c>
+      <c r="L100" s="2" t="inlineStr"/>
       <c r="M100" s="2" t="n"/>
       <c r="N100" s="2" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>I.02.07</t>
+          <t>I.02.05</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -5931,15 +5931,17 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="n"/>
+          <t>South/ West</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>1350000</v>
+      </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
           <t>28.06.26</t>
@@ -5977,12 +5979,12 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>I.07.07</t>
+          <t>I.02.07</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -5995,9 +5997,7 @@
           <t>North/West</t>
         </is>
       </c>
-      <c r="F102" s="3" t="n">
-        <v>2005000</v>
-      </c>
+      <c r="F102" s="2" t="n"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
           <t>28.06.26</t>
@@ -6035,25 +6035,27 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>I.13.01</t>
+          <t>I.07.07</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>North/East</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="n"/>
+          <t>North/West</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>2005000</v>
+      </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
           <t>28.06.26</t>
@@ -6091,7 +6093,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>I.13.07</t>
+          <t>I.13.01</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -6101,17 +6103,15 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
-        </is>
-      </c>
-      <c r="F104" s="3" t="n">
-        <v>2181500</v>
-      </c>
+          <t>North/East</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="n"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
           <t>28.06.26</t>
@@ -6149,26 +6149,26 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>I.15.03</t>
+          <t>I.13.07</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North/West</t>
         </is>
       </c>
       <c r="F105" s="3" t="n">
-        <v>1199000</v>
+        <v>2181500</v>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>I.15.05</t>
+          <t>I.15.03</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -6217,15 +6217,17 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>South/West</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="n"/>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>1199000</v>
+      </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
           <t>28.06.26</t>
@@ -6263,27 +6265,25 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>I.17.04</t>
+          <t>I.15.05</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>K</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="F107" s="3" t="n">
-        <v>1115000</v>
-      </c>
+          <t>South/West</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="n"/>
       <c r="G107" s="2" t="inlineStr">
         <is>
           <t>28.06.26</t>
@@ -6321,26 +6321,26 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>I.20.01</t>
+          <t>I.17.04</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>J</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>North/East</t>
+          <t>South</t>
         </is>
       </c>
       <c r="F108" s="3" t="n">
-        <v>1845000</v>
+        <v>1115000</v>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
@@ -6379,12 +6379,12 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>I.22.01</t>
+          <t>I.20.01</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -6398,7 +6398,7 @@
         </is>
       </c>
       <c r="F109" s="3" t="n">
-        <v>1897000</v>
+        <v>1845000</v>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>I.22.04*</t>
+          <t>I.22.01</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -6447,16 +6447,16 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North/East</t>
         </is>
       </c>
       <c r="F110" s="3" t="n">
-        <v>1205000</v>
+        <v>1897000</v>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
@@ -6487,8 +6487,66 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>W2 - Trillium</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>I.22.04*</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>1205000</v>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="n"/>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="n"/>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N110"/>
+  <autoFilter ref="A1:N111"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6499,7 +6557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -7388,17 +7446,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>W.30.01</t>
+          <t>V18.02</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>30/31</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Penthouse</t>
+          <t>3+Study</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -7407,7 +7465,7 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>4000000</v>
+        <v>2850000</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
@@ -7415,7 +7473,7 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>3990000</v>
+        <v>2815000</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
@@ -7430,11 +7488,11 @@
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="n">
-        <v>-10000</v>
+        <v>-35000</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-09T09:53:11</t>
         </is>
       </c>
     </row>
@@ -7446,7 +7504,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>W.30.02</t>
+          <t>W.30.01</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -7461,7 +7519,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>South/East/North</t>
+          <t>South/West/North</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
@@ -7496,8 +7554,66 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>W12 - White City Living</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>W.30.02</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>30/31</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Penthouse</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>South/East/North</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>27.06.26</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>3990000</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>02.07.26</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>PRICE_DROP</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:01:26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N18"/>
+  <autoFilter ref="A1:N19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12859,7 +12975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J698"/>
+  <dimension ref="A1:J712"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -40308,12 +40424,12 @@
       </c>
       <c r="B640" s="2" t="inlineStr">
         <is>
-          <t>W.09.01</t>
+          <t>V10.02</t>
         </is>
       </c>
       <c r="C640" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D640" s="2" t="inlineStr">
@@ -40323,10 +40439,12 @@
       </c>
       <c r="E640" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
-        </is>
-      </c>
-      <c r="F640" s="2" t="n"/>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="F640" s="3" t="n">
+        <v>762500</v>
+      </c>
       <c r="G640" s="2" t="inlineStr"/>
       <c r="H640" s="2" t="inlineStr">
         <is>
@@ -40335,12 +40453,12 @@
       </c>
       <c r="I640" s="2" t="inlineStr">
         <is>
-          <t>WCL - Solaris Two 02.07.26.pdf</t>
+          <t>WCL-Ready to Move In- Solaris One 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J640" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-09T09:53:11</t>
         </is>
       </c>
     </row>
@@ -40352,26 +40470,26 @@
       </c>
       <c r="B641" s="2" t="inlineStr">
         <is>
-          <t>W.09.04</t>
+          <t>V11.01</t>
         </is>
       </c>
       <c r="C641" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D641" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E641" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
+          <t>South/East/North</t>
         </is>
       </c>
       <c r="F641" s="3" t="n">
-        <v>762500</v>
+        <v>1800000</v>
       </c>
       <c r="G641" s="2" t="inlineStr"/>
       <c r="H641" s="2" t="inlineStr">
@@ -40381,12 +40499,12 @@
       </c>
       <c r="I641" s="2" t="inlineStr">
         <is>
-          <t>WCL - Solaris Two 02.07.26.pdf</t>
+          <t>WCL-Ready to Move In- Solaris One 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J641" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-09T09:53:11</t>
         </is>
       </c>
     </row>
@@ -40398,26 +40516,26 @@
       </c>
       <c r="B642" s="2" t="inlineStr">
         <is>
-          <t>W.10.02</t>
+          <t>V12.01</t>
         </is>
       </c>
       <c r="C642" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D642" s="2" t="inlineStr">
         <is>
-          <t>3+Study</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E642" s="2" t="inlineStr">
         <is>
-          <t>North/East</t>
+          <t>Sout/East/North</t>
         </is>
       </c>
       <c r="F642" s="3" t="n">
-        <v>2000000</v>
+        <v>2080000</v>
       </c>
       <c r="G642" s="2" t="inlineStr"/>
       <c r="H642" s="2" t="inlineStr">
@@ -40427,12 +40545,12 @@
       </c>
       <c r="I642" s="2" t="inlineStr">
         <is>
-          <t>WCL - Solaris Two 02.07.26.pdf</t>
+          <t>WCL-Ready to Move In- Solaris One 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J642" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-09T09:53:11</t>
         </is>
       </c>
     </row>
@@ -40444,25 +40562,27 @@
       </c>
       <c r="B643" s="2" t="inlineStr">
         <is>
-          <t>W.13.04</t>
+          <t>V15.02</t>
         </is>
       </c>
       <c r="C643" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D643" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E643" s="2" t="inlineStr">
         <is>
-          <t>South/East</t>
-        </is>
-      </c>
-      <c r="F643" s="2" t="n"/>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="F643" s="3" t="n">
+        <v>785000</v>
+      </c>
       <c r="G643" s="2" t="inlineStr"/>
       <c r="H643" s="2" t="inlineStr">
         <is>
@@ -40471,12 +40591,12 @@
       </c>
       <c r="I643" s="2" t="inlineStr">
         <is>
-          <t>WCL - Solaris Two 02.07.26.pdf</t>
+          <t>WCL-Ready to Move In- Solaris One 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J643" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-09T09:53:11</t>
         </is>
       </c>
     </row>
@@ -40488,12 +40608,12 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>W.14.03</t>
+          <t>V16.02</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D644" s="2" t="inlineStr">
@@ -40503,11 +40623,11 @@
       </c>
       <c r="E644" s="2" t="inlineStr">
         <is>
-          <t>North/East</t>
+          <t>East</t>
         </is>
       </c>
       <c r="F644" s="3" t="n">
-        <v>775000</v>
+        <v>787500</v>
       </c>
       <c r="G644" s="2" t="inlineStr"/>
       <c r="H644" s="2" t="inlineStr">
@@ -40517,12 +40637,12 @@
       </c>
       <c r="I644" s="2" t="inlineStr">
         <is>
-          <t>WCL - Solaris Two 02.07.26.pdf</t>
+          <t>WCL-Ready to Move In- Solaris One 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J644" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-09T09:53:11</t>
         </is>
       </c>
     </row>
@@ -40534,26 +40654,26 @@
       </c>
       <c r="B645" s="2" t="inlineStr">
         <is>
-          <t>W.14.04</t>
+          <t>V18.02</t>
         </is>
       </c>
       <c r="C645" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D645" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3+Study</t>
         </is>
       </c>
       <c r="E645" s="2" t="inlineStr">
         <is>
-          <t>South/East</t>
+          <t>South/West/North</t>
         </is>
       </c>
       <c r="F645" s="3" t="n">
-        <v>1005000</v>
+        <v>2815000</v>
       </c>
       <c r="G645" s="2" t="inlineStr"/>
       <c r="H645" s="2" t="inlineStr">
@@ -40563,12 +40683,12 @@
       </c>
       <c r="I645" s="2" t="inlineStr">
         <is>
-          <t>WCL - Solaris Two 02.07.26.pdf</t>
+          <t>WCL-Ready to Move In- Solaris One 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J645" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-09T09:53:11</t>
         </is>
       </c>
     </row>
@@ -40580,25 +40700,27 @@
       </c>
       <c r="B646" s="2" t="inlineStr">
         <is>
-          <t>W.17.02</t>
+          <t>V19.01</t>
         </is>
       </c>
       <c r="C646" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D646" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3+Study</t>
         </is>
       </c>
       <c r="E646" s="2" t="inlineStr">
         <is>
-          <t>North/East</t>
-        </is>
-      </c>
-      <c r="F646" s="2" t="n"/>
+          <t>South/East/North</t>
+        </is>
+      </c>
+      <c r="F646" s="3" t="n">
+        <v>2945000</v>
+      </c>
       <c r="G646" s="2" t="inlineStr"/>
       <c r="H646" s="2" t="inlineStr">
         <is>
@@ -40607,12 +40729,12 @@
       </c>
       <c r="I646" s="2" t="inlineStr">
         <is>
-          <t>WCL - Solaris Two 02.07.26.pdf</t>
+          <t>WCL-Ready to Move In- Solaris One 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J646" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-09T09:53:11</t>
         </is>
       </c>
     </row>
@@ -40624,12 +40746,12 @@
       </c>
       <c r="B647" s="2" t="inlineStr">
         <is>
-          <t>W.17.03</t>
+          <t>V4.06</t>
         </is>
       </c>
       <c r="C647" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D647" s="2" t="inlineStr">
@@ -40639,11 +40761,11 @@
       </c>
       <c r="E647" s="2" t="inlineStr">
         <is>
-          <t>South/East</t>
+          <t>South/West</t>
         </is>
       </c>
       <c r="F647" s="3" t="n">
-        <v>1020000</v>
+        <v>1065000</v>
       </c>
       <c r="G647" s="2" t="inlineStr"/>
       <c r="H647" s="2" t="inlineStr">
@@ -40653,12 +40775,12 @@
       </c>
       <c r="I647" s="2" t="inlineStr">
         <is>
-          <t>WCL - Solaris Two 02.07.26.pdf</t>
+          <t>WCL-Ready to Move In- Solaris One 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J647" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-09T09:53:11</t>
         </is>
       </c>
     </row>
@@ -40670,27 +40792,25 @@
       </c>
       <c r="B648" s="2" t="inlineStr">
         <is>
-          <t>W.18.03</t>
+          <t>V5.02</t>
         </is>
       </c>
       <c r="C648" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D648" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E648" s="2" t="inlineStr">
         <is>
-          <t>South/East</t>
-        </is>
-      </c>
-      <c r="F648" s="3" t="n">
-        <v>1025000</v>
-      </c>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="F648" s="2" t="n"/>
       <c r="G648" s="2" t="inlineStr"/>
       <c r="H648" s="2" t="inlineStr">
         <is>
@@ -40699,12 +40819,12 @@
       </c>
       <c r="I648" s="2" t="inlineStr">
         <is>
-          <t>WCL - Solaris Two 02.07.26.pdf</t>
+          <t>WCL-Ready to Move In- Solaris One 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J648" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-09T09:53:11</t>
         </is>
       </c>
     </row>
@@ -40716,22 +40836,22 @@
       </c>
       <c r="B649" s="2" t="inlineStr">
         <is>
-          <t>W.20.04</t>
+          <t>V6.01</t>
         </is>
       </c>
       <c r="C649" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D649" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E649" s="2" t="inlineStr">
         <is>
-          <t>South/East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="F649" s="2" t="n"/>
@@ -40743,12 +40863,12 @@
       </c>
       <c r="I649" s="2" t="inlineStr">
         <is>
-          <t>WCL - Solaris Two 02.07.26.pdf</t>
+          <t>WCL-Ready to Move In- Solaris One 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J649" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-09T09:53:11</t>
         </is>
       </c>
     </row>
@@ -40760,26 +40880,26 @@
       </c>
       <c r="B650" s="2" t="inlineStr">
         <is>
-          <t>W.21.03</t>
+          <t>V6.02</t>
         </is>
       </c>
       <c r="C650" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D650" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E650" s="2" t="inlineStr">
         <is>
-          <t>South/East</t>
+          <t>East</t>
         </is>
       </c>
       <c r="F650" s="3" t="n">
-        <v>1040000</v>
+        <v>752500</v>
       </c>
       <c r="G650" s="2" t="inlineStr"/>
       <c r="H650" s="2" t="inlineStr">
@@ -40789,12 +40909,12 @@
       </c>
       <c r="I650" s="2" t="inlineStr">
         <is>
-          <t>WCL - Solaris Two 02.07.26.pdf</t>
+          <t>WCL-Ready to Move In- Solaris One 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J650" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-09T09:53:11</t>
         </is>
       </c>
     </row>
@@ -40806,27 +40926,25 @@
       </c>
       <c r="B651" s="2" t="inlineStr">
         <is>
-          <t>W.27.01</t>
+          <t>V7.01</t>
         </is>
       </c>
       <c r="C651" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D651" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E651" s="2" t="inlineStr">
         <is>
-          <t>South/East/North</t>
-        </is>
-      </c>
-      <c r="F651" s="3" t="n">
-        <v>2550000</v>
-      </c>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="F651" s="2" t="n"/>
       <c r="G651" s="2" t="inlineStr"/>
       <c r="H651" s="2" t="inlineStr">
         <is>
@@ -40835,12 +40953,12 @@
       </c>
       <c r="I651" s="2" t="inlineStr">
         <is>
-          <t>WCL - Solaris Two 02.07.26.pdf</t>
+          <t>WCL-Ready to Move In- Solaris One 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J651" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-09T09:53:11</t>
         </is>
       </c>
     </row>
@@ -40852,26 +40970,26 @@
       </c>
       <c r="B652" s="2" t="inlineStr">
         <is>
-          <t>W.27.02</t>
+          <t>V7.02</t>
         </is>
       </c>
       <c r="C652" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D652" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E652" s="2" t="inlineStr">
         <is>
-          <t>South/West/North</t>
+          <t>East</t>
         </is>
       </c>
       <c r="F652" s="3" t="n">
-        <v>2550000</v>
+        <v>755000</v>
       </c>
       <c r="G652" s="2" t="inlineStr"/>
       <c r="H652" s="2" t="inlineStr">
@@ -40881,12 +40999,12 @@
       </c>
       <c r="I652" s="2" t="inlineStr">
         <is>
-          <t>WCL - Solaris Two 02.07.26.pdf</t>
+          <t>WCL-Ready to Move In- Solaris One 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J652" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-09T09:53:11</t>
         </is>
       </c>
     </row>
@@ -40898,26 +41016,26 @@
       </c>
       <c r="B653" s="2" t="inlineStr">
         <is>
-          <t>W.30.01</t>
+          <t>V9.02</t>
         </is>
       </c>
       <c r="C653" s="2" t="inlineStr">
         <is>
-          <t>30/31</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D653" s="2" t="inlineStr">
         <is>
-          <t>Penthouse</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E653" s="2" t="inlineStr">
         <is>
-          <t>South/West/North</t>
+          <t>East</t>
         </is>
       </c>
       <c r="F653" s="3" t="n">
-        <v>3990000</v>
+        <v>760000</v>
       </c>
       <c r="G653" s="2" t="inlineStr"/>
       <c r="H653" s="2" t="inlineStr">
@@ -40927,12 +41045,12 @@
       </c>
       <c r="I653" s="2" t="inlineStr">
         <is>
-          <t>WCL - Solaris Two 02.07.26.pdf</t>
+          <t>WCL-Ready to Move In- Solaris One 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J653" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-09T09:53:11</t>
         </is>
       </c>
     </row>
@@ -40944,27 +41062,25 @@
       </c>
       <c r="B654" s="2" t="inlineStr">
         <is>
-          <t>W.30.02</t>
+          <t>W.09.01</t>
         </is>
       </c>
       <c r="C654" s="2" t="inlineStr">
         <is>
-          <t>30/31</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D654" s="2" t="inlineStr">
         <is>
-          <t>Penthouse</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E654" s="2" t="inlineStr">
         <is>
-          <t>South/East/North</t>
-        </is>
-      </c>
-      <c r="F654" s="3" t="n">
-        <v>3990000</v>
-      </c>
+          <t>North/West</t>
+        </is>
+      </c>
+      <c r="F654" s="2" t="n"/>
       <c r="G654" s="2" t="inlineStr"/>
       <c r="H654" s="2" t="inlineStr">
         <is>
@@ -40985,190 +41101,194 @@
     <row r="655">
       <c r="A655" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B655" s="2" t="inlineStr">
         <is>
-          <t>I.01.07</t>
+          <t>W.09.04</t>
         </is>
       </c>
       <c r="C655" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D655" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D655" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
       <c r="E655" s="2" t="inlineStr">
         <is>
           <t>North/West</t>
         </is>
       </c>
-      <c r="F655" s="2" t="n"/>
+      <c r="F655" s="3" t="n">
+        <v>762500</v>
+      </c>
       <c r="G655" s="2" t="inlineStr"/>
       <c r="H655" s="2" t="inlineStr">
         <is>
-          <t>01.07.26</t>
+          <t>02.07.26</t>
         </is>
       </c>
       <c r="I655" s="2" t="inlineStr">
         <is>
-          <t>Trillium Price List 01.07.26.pdf</t>
+          <t>WCL - Solaris Two 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J655" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:32</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
     </row>
     <row r="656">
       <c r="A656" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B656" s="2" t="inlineStr">
         <is>
-          <t>I.08.05</t>
+          <t>W.10.02</t>
         </is>
       </c>
       <c r="C656" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D656" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>3+Study</t>
         </is>
       </c>
       <c r="E656" s="2" t="inlineStr">
         <is>
-          <t>South/West</t>
-        </is>
-      </c>
-      <c r="F656" s="2" t="n"/>
+          <t>North/East</t>
+        </is>
+      </c>
+      <c r="F656" s="3" t="n">
+        <v>2000000</v>
+      </c>
       <c r="G656" s="2" t="inlineStr"/>
       <c r="H656" s="2" t="inlineStr">
         <is>
-          <t>01.07.26</t>
+          <t>02.07.26</t>
         </is>
       </c>
       <c r="I656" s="2" t="inlineStr">
         <is>
-          <t>Trillium Price List 01.07.26.pdf</t>
+          <t>WCL - Solaris Two 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J656" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:32</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
     </row>
     <row r="657">
       <c r="A657" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B657" s="2" t="inlineStr">
         <is>
-          <t>I.10.06</t>
+          <t>W.13.04</t>
         </is>
       </c>
       <c r="C657" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D657" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E657" s="2" t="inlineStr">
         <is>
-          <t>West</t>
-        </is>
-      </c>
-      <c r="F657" s="3" t="n">
-        <v>1016000</v>
-      </c>
+          <t>South/East</t>
+        </is>
+      </c>
+      <c r="F657" s="2" t="n"/>
       <c r="G657" s="2" t="inlineStr"/>
       <c r="H657" s="2" t="inlineStr">
         <is>
-          <t>01.07.26</t>
+          <t>02.07.26</t>
         </is>
       </c>
       <c r="I657" s="2" t="inlineStr">
         <is>
-          <t>Trillium Price List 01.07.26.pdf</t>
+          <t>WCL - Solaris Two 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J657" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:32</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
     </row>
     <row r="658">
       <c r="A658" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B658" s="2" t="inlineStr">
         <is>
-          <t>I.10.07</t>
+          <t>W.14.03</t>
         </is>
       </c>
       <c r="C658" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D658" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E658" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
-        </is>
-      </c>
-      <c r="F658" s="2" t="n"/>
+          <t>North/East</t>
+        </is>
+      </c>
+      <c r="F658" s="3" t="n">
+        <v>775000</v>
+      </c>
       <c r="G658" s="2" t="inlineStr"/>
       <c r="H658" s="2" t="inlineStr">
         <is>
-          <t>01.07.26</t>
+          <t>02.07.26</t>
         </is>
       </c>
       <c r="I658" s="2" t="inlineStr">
         <is>
-          <t>Trillium Price List 01.07.26.pdf</t>
+          <t>WCL - Solaris Two 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J658" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:32</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
     </row>
     <row r="659">
       <c r="A659" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B659" s="2" t="inlineStr">
         <is>
-          <t>I.14.01</t>
+          <t>W.14.04</t>
         </is>
       </c>
       <c r="C659" s="2" t="inlineStr">
@@ -41178,435 +41298,441 @@
       </c>
       <c r="D659" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E659" s="2" t="inlineStr">
         <is>
-          <t>North/East</t>
+          <t>South/East</t>
         </is>
       </c>
       <c r="F659" s="3" t="n">
-        <v>1598500</v>
+        <v>1005000</v>
       </c>
       <c r="G659" s="2" t="inlineStr"/>
       <c r="H659" s="2" t="inlineStr">
         <is>
-          <t>01.07.26</t>
+          <t>02.07.26</t>
         </is>
       </c>
       <c r="I659" s="2" t="inlineStr">
         <is>
-          <t>Trillium Price List 01.07.26.pdf</t>
+          <t>WCL - Solaris Two 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J659" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:32</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
     </row>
     <row r="660">
       <c r="A660" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B660" s="2" t="inlineStr">
         <is>
-          <t>I.14.06</t>
+          <t>W.17.02</t>
         </is>
       </c>
       <c r="C660" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D660" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E660" s="2" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>North/East</t>
         </is>
       </c>
       <c r="F660" s="2" t="n"/>
       <c r="G660" s="2" t="inlineStr"/>
       <c r="H660" s="2" t="inlineStr">
         <is>
-          <t>01.07.26</t>
+          <t>02.07.26</t>
         </is>
       </c>
       <c r="I660" s="2" t="inlineStr">
         <is>
-          <t>Trillium Price List 01.07.26.pdf</t>
+          <t>WCL - Solaris Two 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J660" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:32</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
     </row>
     <row r="661">
       <c r="A661" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B661" s="2" t="inlineStr">
         <is>
-          <t>I.15.01</t>
+          <t>W.17.03</t>
         </is>
       </c>
       <c r="C661" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D661" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E661" s="2" t="inlineStr">
         <is>
-          <t>North/East</t>
+          <t>South/East</t>
         </is>
       </c>
       <c r="F661" s="3" t="n">
-        <v>1613500</v>
+        <v>1020000</v>
       </c>
       <c r="G661" s="2" t="inlineStr"/>
       <c r="H661" s="2" t="inlineStr">
         <is>
-          <t>01.07.26</t>
+          <t>02.07.26</t>
         </is>
       </c>
       <c r="I661" s="2" t="inlineStr">
         <is>
-          <t>Trillium Price List 01.07.26.pdf</t>
+          <t>WCL - Solaris Two 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J661" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:32</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
     </row>
     <row r="662">
       <c r="A662" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B662" s="2" t="inlineStr">
         <is>
-          <t>I.16.05</t>
+          <t>W.18.03</t>
         </is>
       </c>
       <c r="C662" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D662" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E662" s="2" t="inlineStr">
         <is>
-          <t>South/West</t>
-        </is>
-      </c>
-      <c r="F662" s="2" t="n"/>
+          <t>South/East</t>
+        </is>
+      </c>
+      <c r="F662" s="3" t="n">
+        <v>1025000</v>
+      </c>
       <c r="G662" s="2" t="inlineStr"/>
       <c r="H662" s="2" t="inlineStr">
         <is>
-          <t>01.07.26</t>
+          <t>02.07.26</t>
         </is>
       </c>
       <c r="I662" s="2" t="inlineStr">
         <is>
-          <t>Trillium Price List 01.07.26.pdf</t>
+          <t>WCL - Solaris Two 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J662" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:32</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
     </row>
     <row r="663">
       <c r="A663" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B663" s="2" t="inlineStr">
         <is>
-          <t>I.17.01</t>
+          <t>W.20.04</t>
         </is>
       </c>
       <c r="C663" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D663" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E663" s="2" t="inlineStr">
         <is>
-          <t>North /East</t>
-        </is>
-      </c>
-      <c r="F663" s="3" t="n">
-        <v>1680500</v>
-      </c>
+          <t>South/East</t>
+        </is>
+      </c>
+      <c r="F663" s="2" t="n"/>
       <c r="G663" s="2" t="inlineStr"/>
       <c r="H663" s="2" t="inlineStr">
         <is>
-          <t>01.07.26</t>
+          <t>02.07.26</t>
         </is>
       </c>
       <c r="I663" s="2" t="inlineStr">
         <is>
-          <t>Trillium Price List 01.07.26.pdf</t>
+          <t>WCL - Solaris Two 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J663" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:32</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
     </row>
     <row r="664">
       <c r="A664" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B664" s="2" t="inlineStr">
         <is>
-          <t>I.17.03</t>
+          <t>W.21.03</t>
         </is>
       </c>
       <c r="C664" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D664" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E664" s="2" t="inlineStr">
         <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="F664" s="2" t="n"/>
+          <t>South/East</t>
+        </is>
+      </c>
+      <c r="F664" s="3" t="n">
+        <v>1040000</v>
+      </c>
       <c r="G664" s="2" t="inlineStr"/>
       <c r="H664" s="2" t="inlineStr">
         <is>
-          <t>01.07.26</t>
+          <t>02.07.26</t>
         </is>
       </c>
       <c r="I664" s="2" t="inlineStr">
         <is>
-          <t>Trillium Price List 01.07.26.pdf</t>
+          <t>WCL - Solaris Two 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J664" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:32</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
     </row>
     <row r="665">
       <c r="A665" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B665" s="2" t="inlineStr">
         <is>
-          <t>I.17.05</t>
+          <t>W.27.01</t>
         </is>
       </c>
       <c r="C665" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D665" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E665" s="2" t="inlineStr">
         <is>
-          <t>South/West</t>
+          <t>South/East/North</t>
         </is>
       </c>
       <c r="F665" s="3" t="n">
-        <v>2474500</v>
+        <v>2550000</v>
       </c>
       <c r="G665" s="2" t="inlineStr"/>
       <c r="H665" s="2" t="inlineStr">
         <is>
-          <t>01.07.26</t>
+          <t>02.07.26</t>
         </is>
       </c>
       <c r="I665" s="2" t="inlineStr">
         <is>
-          <t>Trillium Price List 01.07.26.pdf</t>
+          <t>WCL - Solaris Two 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J665" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:32</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
     </row>
     <row r="666">
       <c r="A666" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B666" s="2" t="inlineStr">
         <is>
-          <t>I.18.02</t>
+          <t>W.27.02</t>
         </is>
       </c>
       <c r="C666" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D666" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E666" s="2" t="inlineStr">
         <is>
-          <t>South/East</t>
-        </is>
-      </c>
-      <c r="F666" s="2" t="n"/>
+          <t>South/West/North</t>
+        </is>
+      </c>
+      <c r="F666" s="3" t="n">
+        <v>2550000</v>
+      </c>
       <c r="G666" s="2" t="inlineStr"/>
       <c r="H666" s="2" t="inlineStr">
         <is>
-          <t>01.07.26</t>
+          <t>02.07.26</t>
         </is>
       </c>
       <c r="I666" s="2" t="inlineStr">
         <is>
-          <t>Trillium Price List 01.07.26.pdf</t>
+          <t>WCL - Solaris Two 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J666" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:32</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
     </row>
     <row r="667">
       <c r="A667" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B667" s="2" t="inlineStr">
         <is>
-          <t>I.18.05</t>
+          <t>W.30.01</t>
         </is>
       </c>
       <c r="C667" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>30/31</t>
         </is>
       </c>
       <c r="D667" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>Penthouse</t>
         </is>
       </c>
       <c r="E667" s="2" t="inlineStr">
         <is>
-          <t>South/West</t>
-        </is>
-      </c>
-      <c r="F667" s="2" t="n"/>
+          <t>South/West/North</t>
+        </is>
+      </c>
+      <c r="F667" s="3" t="n">
+        <v>3990000</v>
+      </c>
       <c r="G667" s="2" t="inlineStr"/>
       <c r="H667" s="2" t="inlineStr">
         <is>
-          <t>01.07.26</t>
+          <t>02.07.26</t>
         </is>
       </c>
       <c r="I667" s="2" t="inlineStr">
         <is>
-          <t>Trillium Price List 01.07.26.pdf</t>
+          <t>WCL - Solaris Two 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J667" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:32</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
     </row>
     <row r="668">
       <c r="A668" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B668" s="2" t="inlineStr">
         <is>
-          <t>I.19.03</t>
+          <t>W.30.02</t>
         </is>
       </c>
       <c r="C668" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>30/31</t>
         </is>
       </c>
       <c r="D668" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>Penthouse</t>
         </is>
       </c>
       <c r="E668" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>South/East/North</t>
         </is>
       </c>
       <c r="F668" s="3" t="n">
-        <v>1238000</v>
+        <v>3990000</v>
       </c>
       <c r="G668" s="2" t="inlineStr"/>
       <c r="H668" s="2" t="inlineStr">
         <is>
-          <t>01.07.26</t>
+          <t>02.07.26</t>
         </is>
       </c>
       <c r="I668" s="2" t="inlineStr">
         <is>
-          <t>Trillium Price List 01.07.26.pdf</t>
+          <t>WCL - Solaris Two 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J668" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:32</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
     </row>
@@ -41618,12 +41744,12 @@
       </c>
       <c r="B669" s="2" t="inlineStr">
         <is>
-          <t>I.20.06</t>
+          <t>I.01.07</t>
         </is>
       </c>
       <c r="C669" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D669" s="2" t="inlineStr">
@@ -41636,9 +41762,7 @@
           <t>North/West</t>
         </is>
       </c>
-      <c r="F669" s="3" t="n">
-        <v>2505000</v>
-      </c>
+      <c r="F669" s="2" t="n"/>
       <c r="G669" s="2" t="inlineStr"/>
       <c r="H669" s="2" t="inlineStr">
         <is>
@@ -41664,27 +41788,25 @@
       </c>
       <c r="B670" s="2" t="inlineStr">
         <is>
-          <t>I.21.03</t>
+          <t>I.08.05</t>
         </is>
       </c>
       <c r="C670" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D670" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E670" s="2" t="inlineStr">
         <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="F670" s="3" t="n">
-        <v>1288500</v>
-      </c>
+          <t>South/West</t>
+        </is>
+      </c>
+      <c r="F670" s="2" t="n"/>
       <c r="G670" s="2" t="inlineStr"/>
       <c r="H670" s="2" t="inlineStr">
         <is>
@@ -41705,644 +41827,632 @@
     <row r="671">
       <c r="A671" s="2" t="inlineStr">
         <is>
-          <t>W6 - Fulham Reach</t>
+          <t>W2 - Trillium</t>
         </is>
       </c>
       <c r="B671" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>I.10.06</t>
         </is>
       </c>
       <c r="C671" s="2" t="inlineStr">
         <is>
-          <t>GF</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D671" s="2" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E671" s="2" t="inlineStr">
         <is>
-          <t>N,W</t>
+          <t>West</t>
         </is>
       </c>
       <c r="F671" s="3" t="n">
-        <v>597000</v>
+        <v>1016000</v>
       </c>
       <c r="G671" s="2" t="inlineStr"/>
       <c r="H671" s="2" t="inlineStr">
         <is>
-          <t>05.07.26</t>
+          <t>01.07.26</t>
         </is>
       </c>
       <c r="I671" s="2" t="inlineStr">
         <is>
-          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
+          <t>Trillium Price List 01.07.26.pdf</t>
         </is>
       </c>
       <c r="J671" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:57:26</t>
+          <t>2026-07-08T16:56:32</t>
         </is>
       </c>
     </row>
     <row r="672">
       <c r="A672" s="2" t="inlineStr">
         <is>
-          <t>W6 - Fulham Reach</t>
+          <t>W2 - Trillium</t>
         </is>
       </c>
       <c r="B672" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>I.10.07</t>
         </is>
       </c>
       <c r="C672" s="2" t="inlineStr">
         <is>
-          <t>GF</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D672" s="2" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E672" s="2" t="inlineStr">
         <is>
-          <t>N,W</t>
-        </is>
-      </c>
-      <c r="F672" s="3" t="n">
-        <v>598000</v>
-      </c>
+          <t>North/West</t>
+        </is>
+      </c>
+      <c r="F672" s="2" t="n"/>
       <c r="G672" s="2" t="inlineStr"/>
       <c r="H672" s="2" t="inlineStr">
         <is>
-          <t>05.07.26</t>
+          <t>01.07.26</t>
         </is>
       </c>
       <c r="I672" s="2" t="inlineStr">
         <is>
-          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
+          <t>Trillium Price List 01.07.26.pdf</t>
         </is>
       </c>
       <c r="J672" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:57:26</t>
+          <t>2026-07-08T16:56:32</t>
         </is>
       </c>
     </row>
     <row r="673">
       <c r="A673" s="2" t="inlineStr">
         <is>
-          <t>W6 - Fulham Reach</t>
+          <t>W2 - Trillium</t>
         </is>
       </c>
       <c r="B673" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>I.14.01</t>
         </is>
       </c>
       <c r="C673" s="2" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D673" s="2" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E673" s="2" t="inlineStr">
         <is>
-          <t>N,W</t>
+          <t>North/East</t>
         </is>
       </c>
       <c r="F673" s="3" t="n">
-        <v>584000</v>
+        <v>1598500</v>
       </c>
       <c r="G673" s="2" t="inlineStr"/>
       <c r="H673" s="2" t="inlineStr">
         <is>
-          <t>05.07.26</t>
+          <t>01.07.26</t>
         </is>
       </c>
       <c r="I673" s="2" t="inlineStr">
         <is>
-          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
+          <t>Trillium Price List 01.07.26.pdf</t>
         </is>
       </c>
       <c r="J673" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:57:26</t>
+          <t>2026-07-08T16:56:32</t>
         </is>
       </c>
     </row>
     <row r="674">
       <c r="A674" s="2" t="inlineStr">
         <is>
-          <t>W6 - Fulham Reach</t>
+          <t>W2 - Trillium</t>
         </is>
       </c>
       <c r="B674" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>I.14.06</t>
         </is>
       </c>
       <c r="C674" s="2" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D674" s="2" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E674" s="2" t="inlineStr">
         <is>
-          <t>N,W</t>
-        </is>
-      </c>
-      <c r="F674" s="3" t="n">
-        <v>604500</v>
-      </c>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="F674" s="2" t="n"/>
       <c r="G674" s="2" t="inlineStr"/>
       <c r="H674" s="2" t="inlineStr">
         <is>
-          <t>05.07.26</t>
+          <t>01.07.26</t>
         </is>
       </c>
       <c r="I674" s="2" t="inlineStr">
         <is>
-          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
+          <t>Trillium Price List 01.07.26.pdf</t>
         </is>
       </c>
       <c r="J674" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:57:26</t>
+          <t>2026-07-08T16:56:32</t>
         </is>
       </c>
     </row>
     <row r="675">
       <c r="A675" s="2" t="inlineStr">
         <is>
-          <t>W6 - Fulham Reach</t>
+          <t>W2 - Trillium</t>
         </is>
       </c>
       <c r="B675" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>I.15.01</t>
         </is>
       </c>
       <c r="C675" s="2" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D675" s="2" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E675" s="2" t="inlineStr">
         <is>
-          <t>N,W</t>
+          <t>North/East</t>
         </is>
       </c>
       <c r="F675" s="3" t="n">
-        <v>604500</v>
+        <v>1613500</v>
       </c>
       <c r="G675" s="2" t="inlineStr"/>
       <c r="H675" s="2" t="inlineStr">
         <is>
-          <t>05.07.26</t>
+          <t>01.07.26</t>
         </is>
       </c>
       <c r="I675" s="2" t="inlineStr">
         <is>
-          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
+          <t>Trillium Price List 01.07.26.pdf</t>
         </is>
       </c>
       <c r="J675" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:57:26</t>
+          <t>2026-07-08T16:56:32</t>
         </is>
       </c>
     </row>
     <row r="676">
       <c r="A676" s="2" t="inlineStr">
         <is>
-          <t>W6 - Fulham Reach</t>
+          <t>W2 - Trillium</t>
         </is>
       </c>
       <c r="B676" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>I.16.05</t>
         </is>
       </c>
       <c r="C676" s="2" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D676" s="2" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>K</t>
         </is>
       </c>
       <c r="E676" s="2" t="inlineStr">
         <is>
-          <t>N,W</t>
-        </is>
-      </c>
-      <c r="F676" s="3" t="n">
-        <v>584000</v>
-      </c>
+          <t>South/West</t>
+        </is>
+      </c>
+      <c r="F676" s="2" t="n"/>
       <c r="G676" s="2" t="inlineStr"/>
       <c r="H676" s="2" t="inlineStr">
         <is>
-          <t>05.07.26</t>
+          <t>01.07.26</t>
         </is>
       </c>
       <c r="I676" s="2" t="inlineStr">
         <is>
-          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
+          <t>Trillium Price List 01.07.26.pdf</t>
         </is>
       </c>
       <c r="J676" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:57:26</t>
+          <t>2026-07-08T16:56:32</t>
         </is>
       </c>
     </row>
     <row r="677">
       <c r="A677" s="2" t="inlineStr">
         <is>
-          <t>W6 - Fulham Reach</t>
+          <t>W2 - Trillium</t>
         </is>
       </c>
       <c r="B677" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>I.17.01</t>
         </is>
       </c>
       <c r="C677" s="2" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D677" s="2" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E677" s="2" t="inlineStr">
         <is>
-          <t>N,W</t>
+          <t>North /East</t>
         </is>
       </c>
       <c r="F677" s="3" t="n">
-        <v>610000</v>
+        <v>1680500</v>
       </c>
       <c r="G677" s="2" t="inlineStr"/>
       <c r="H677" s="2" t="inlineStr">
         <is>
-          <t>05.07.26</t>
+          <t>01.07.26</t>
         </is>
       </c>
       <c r="I677" s="2" t="inlineStr">
         <is>
-          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
+          <t>Trillium Price List 01.07.26.pdf</t>
         </is>
       </c>
       <c r="J677" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:57:26</t>
+          <t>2026-07-08T16:56:32</t>
         </is>
       </c>
     </row>
     <row r="678">
       <c r="A678" s="2" t="inlineStr">
         <is>
-          <t>W6 - Fulham Reach</t>
+          <t>W2 - Trillium</t>
         </is>
       </c>
       <c r="B678" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>I.17.03</t>
         </is>
       </c>
       <c r="C678" s="2" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D678" s="2" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E678" s="2" t="inlineStr">
         <is>
-          <t>N,W</t>
-        </is>
-      </c>
-      <c r="F678" s="3" t="n">
-        <v>610000</v>
-      </c>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F678" s="2" t="n"/>
       <c r="G678" s="2" t="inlineStr"/>
       <c r="H678" s="2" t="inlineStr">
         <is>
-          <t>05.07.26</t>
+          <t>01.07.26</t>
         </is>
       </c>
       <c r="I678" s="2" t="inlineStr">
         <is>
-          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
+          <t>Trillium Price List 01.07.26.pdf</t>
         </is>
       </c>
       <c r="J678" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:57:26</t>
+          <t>2026-07-08T16:56:32</t>
         </is>
       </c>
     </row>
     <row r="679">
       <c r="A679" s="2" t="inlineStr">
         <is>
-          <t>W6 - Fulham Reach</t>
+          <t>W2 - Trillium</t>
         </is>
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>I.17.05</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D679" s="2" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>K</t>
         </is>
       </c>
       <c r="E679" s="2" t="inlineStr">
         <is>
-          <t>N,W</t>
+          <t>South/West</t>
         </is>
       </c>
       <c r="F679" s="3" t="n">
-        <v>617500</v>
+        <v>2474500</v>
       </c>
       <c r="G679" s="2" t="inlineStr"/>
       <c r="H679" s="2" t="inlineStr">
         <is>
-          <t>05.07.26</t>
+          <t>01.07.26</t>
         </is>
       </c>
       <c r="I679" s="2" t="inlineStr">
         <is>
-          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
+          <t>Trillium Price List 01.07.26.pdf</t>
         </is>
       </c>
       <c r="J679" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:57:26</t>
+          <t>2026-07-08T16:56:32</t>
         </is>
       </c>
     </row>
     <row r="680">
       <c r="A680" s="2" t="inlineStr">
         <is>
-          <t>W6 - Fulham Reach</t>
+          <t>W2 - Trillium</t>
         </is>
       </c>
       <c r="B680" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>I.18.02</t>
         </is>
       </c>
       <c r="C680" s="2" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D680" s="2" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E680" s="2" t="inlineStr">
         <is>
-          <t>N,W</t>
-        </is>
-      </c>
-      <c r="F680" s="3" t="n">
-        <v>617500</v>
-      </c>
+          <t>South/East</t>
+        </is>
+      </c>
+      <c r="F680" s="2" t="n"/>
       <c r="G680" s="2" t="inlineStr"/>
       <c r="H680" s="2" t="inlineStr">
         <is>
-          <t>05.07.26</t>
+          <t>01.07.26</t>
         </is>
       </c>
       <c r="I680" s="2" t="inlineStr">
         <is>
-          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
+          <t>Trillium Price List 01.07.26.pdf</t>
         </is>
       </c>
       <c r="J680" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:57:26</t>
+          <t>2026-07-08T16:56:32</t>
         </is>
       </c>
     </row>
     <row r="681">
       <c r="A681" s="2" t="inlineStr">
         <is>
-          <t>W6 - Fulham Reach</t>
+          <t>W2 - Trillium</t>
         </is>
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>I.18.05</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D681" s="2" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>K</t>
         </is>
       </c>
       <c r="E681" s="2" t="inlineStr">
         <is>
-          <t>N,W</t>
-        </is>
-      </c>
-      <c r="F681" s="3" t="n">
-        <v>623000</v>
-      </c>
+          <t>South/West</t>
+        </is>
+      </c>
+      <c r="F681" s="2" t="n"/>
       <c r="G681" s="2" t="inlineStr"/>
       <c r="H681" s="2" t="inlineStr">
         <is>
-          <t>05.07.26</t>
+          <t>01.07.26</t>
         </is>
       </c>
       <c r="I681" s="2" t="inlineStr">
         <is>
-          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
+          <t>Trillium Price List 01.07.26.pdf</t>
         </is>
       </c>
       <c r="J681" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:57:26</t>
+          <t>2026-07-08T16:56:32</t>
         </is>
       </c>
     </row>
     <row r="682">
       <c r="A682" s="2" t="inlineStr">
         <is>
-          <t>W6 - Fulham Reach</t>
+          <t>W2 - Trillium</t>
         </is>
       </c>
       <c r="B682" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>I.19.03</t>
         </is>
       </c>
       <c r="C682" s="2" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D682" s="2" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E682" s="2" t="inlineStr">
         <is>
-          <t>N,W</t>
+          <t>South</t>
         </is>
       </c>
       <c r="F682" s="3" t="n">
-        <v>623000</v>
+        <v>1238000</v>
       </c>
       <c r="G682" s="2" t="inlineStr"/>
       <c r="H682" s="2" t="inlineStr">
         <is>
-          <t>05.07.26</t>
+          <t>01.07.26</t>
         </is>
       </c>
       <c r="I682" s="2" t="inlineStr">
         <is>
-          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
+          <t>Trillium Price List 01.07.26.pdf</t>
         </is>
       </c>
       <c r="J682" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:57:26</t>
+          <t>2026-07-08T16:56:32</t>
         </is>
       </c>
     </row>
     <row r="683">
       <c r="A683" s="2" t="inlineStr">
         <is>
-          <t>W6 - Fulham Reach</t>
+          <t>W2 - Trillium</t>
         </is>
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>I.20.06</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D683" s="2" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E683" s="2" t="inlineStr">
         <is>
-          <t>N,W</t>
+          <t>North/West</t>
         </is>
       </c>
       <c r="F683" s="3" t="n">
-        <v>623000</v>
+        <v>2505000</v>
       </c>
       <c r="G683" s="2" t="inlineStr"/>
       <c r="H683" s="2" t="inlineStr">
         <is>
-          <t>05.07.26</t>
+          <t>01.07.26</t>
         </is>
       </c>
       <c r="I683" s="2" t="inlineStr">
         <is>
-          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
+          <t>Trillium Price List 01.07.26.pdf</t>
         </is>
       </c>
       <c r="J683" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:57:26</t>
+          <t>2026-07-08T16:56:32</t>
         </is>
       </c>
     </row>
     <row r="684">
       <c r="A684" s="2" t="inlineStr">
         <is>
-          <t>W6 - Fulham Reach</t>
+          <t>W2 - Trillium</t>
         </is>
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>I.21.03</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D684" s="2" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E684" s="2" t="inlineStr">
         <is>
-          <t>N,W</t>
+          <t>South</t>
         </is>
       </c>
       <c r="F684" s="3" t="n">
-        <v>623000</v>
+        <v>1288500</v>
       </c>
       <c r="G684" s="2" t="inlineStr"/>
       <c r="H684" s="2" t="inlineStr">
         <is>
-          <t>05.07.26</t>
+          <t>01.07.26</t>
         </is>
       </c>
       <c r="I684" s="2" t="inlineStr">
         <is>
-          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
+          <t>Trillium Price List 01.07.26.pdf</t>
         </is>
       </c>
       <c r="J684" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:57:26</t>
+          <t>2026-07-08T16:56:32</t>
         </is>
       </c>
     </row>
@@ -42354,12 +42464,12 @@
       </c>
       <c r="B685" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>658</t>
         </is>
       </c>
       <c r="C685" s="2" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>GF</t>
         </is>
       </c>
       <c r="D685" s="2" t="inlineStr">
@@ -42373,7 +42483,7 @@
         </is>
       </c>
       <c r="F685" s="3" t="n">
-        <v>598000</v>
+        <v>597000</v>
       </c>
       <c r="G685" s="2" t="inlineStr"/>
       <c r="H685" s="2" t="inlineStr">
@@ -42395,58 +42505,58 @@
     <row r="686">
       <c r="A686" s="2" t="inlineStr">
         <is>
-          <t>WC1X - Postmark, Farringdon</t>
+          <t>W6 - Fulham Reach</t>
         </is>
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>H1.01.01</t>
+          <t>660</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>GF</t>
         </is>
       </c>
       <c r="D686" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E686" s="2" t="inlineStr">
         <is>
-          <t>SE&amp;NW</t>
+          <t>N,W</t>
         </is>
       </c>
       <c r="F686" s="3" t="n">
-        <v>1395000</v>
+        <v>598000</v>
       </c>
       <c r="G686" s="2" t="inlineStr"/>
       <c r="H686" s="2" t="inlineStr">
         <is>
-          <t>04.07.26</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="I686" s="2" t="inlineStr">
         <is>
-          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
         </is>
       </c>
       <c r="J686" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:41</t>
+          <t>2026-07-08T16:57:26</t>
         </is>
       </c>
     </row>
     <row r="687">
       <c r="A687" s="2" t="inlineStr">
         <is>
-          <t>WC1X - Postmark, Farringdon</t>
+          <t>W6 - Fulham Reach</t>
         </is>
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>H1.01.02</t>
+          <t>662</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
@@ -42456,43 +42566,43 @@
       </c>
       <c r="D687" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E687" s="2" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>N,W</t>
         </is>
       </c>
       <c r="F687" s="3" t="n">
-        <v>1410000</v>
+        <v>584000</v>
       </c>
       <c r="G687" s="2" t="inlineStr"/>
       <c r="H687" s="2" t="inlineStr">
         <is>
-          <t>04.07.26</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="I687" s="2" t="inlineStr">
         <is>
-          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
         </is>
       </c>
       <c r="J687" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:41</t>
+          <t>2026-07-08T16:57:26</t>
         </is>
       </c>
     </row>
     <row r="688">
       <c r="A688" s="2" t="inlineStr">
         <is>
-          <t>WC1X - Postmark, Farringdon</t>
+          <t>W6 - Fulham Reach</t>
         </is>
       </c>
       <c r="B688" s="2" t="inlineStr">
         <is>
-          <t>H1.01.03</t>
+          <t>664</t>
         </is>
       </c>
       <c r="C688" s="2" t="inlineStr">
@@ -42502,87 +42612,89 @@
       </c>
       <c r="D688" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E688" s="2" t="inlineStr">
         <is>
-          <t>SW&amp;NE</t>
-        </is>
-      </c>
-      <c r="F688" s="2" t="n"/>
+          <t>N,W</t>
+        </is>
+      </c>
+      <c r="F688" s="3" t="n">
+        <v>604500</v>
+      </c>
       <c r="G688" s="2" t="inlineStr"/>
       <c r="H688" s="2" t="inlineStr">
         <is>
-          <t>04.07.26</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="I688" s="2" t="inlineStr">
         <is>
-          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
         </is>
       </c>
       <c r="J688" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:41</t>
+          <t>2026-07-08T16:57:26</t>
         </is>
       </c>
     </row>
     <row r="689">
       <c r="A689" s="2" t="inlineStr">
         <is>
-          <t>WC1X - Postmark, Farringdon</t>
+          <t>W6 - Fulham Reach</t>
         </is>
       </c>
       <c r="B689" s="2" t="inlineStr">
         <is>
-          <t>H3.00.01</t>
+          <t>665</t>
         </is>
       </c>
       <c r="C689" s="2" t="inlineStr">
         <is>
-          <t>Ground</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="D689" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E689" s="2" t="inlineStr">
         <is>
-          <t>SE&amp;NW</t>
+          <t>N,W</t>
         </is>
       </c>
       <c r="F689" s="3" t="n">
-        <v>1450000</v>
+        <v>604500</v>
       </c>
       <c r="G689" s="2" t="inlineStr"/>
       <c r="H689" s="2" t="inlineStr">
         <is>
-          <t>04.07.26</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="I689" s="2" t="inlineStr">
         <is>
-          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
         </is>
       </c>
       <c r="J689" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:41</t>
+          <t>2026-07-08T16:57:26</t>
         </is>
       </c>
     </row>
     <row r="690">
       <c r="A690" s="2" t="inlineStr">
         <is>
-          <t>WC1X - Postmark, Farringdon</t>
+          <t>W6 - Fulham Reach</t>
         </is>
       </c>
       <c r="B690" s="2" t="inlineStr">
         <is>
-          <t>H3.01.01</t>
+          <t>674</t>
         </is>
       </c>
       <c r="C690" s="2" t="inlineStr">
@@ -42592,402 +42704,1044 @@
       </c>
       <c r="D690" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E690" s="2" t="inlineStr">
         <is>
-          <t>SE&amp;NW</t>
+          <t>N,W</t>
         </is>
       </c>
       <c r="F690" s="3" t="n">
-        <v>995000</v>
+        <v>584000</v>
       </c>
       <c r="G690" s="2" t="inlineStr"/>
       <c r="H690" s="2" t="inlineStr">
         <is>
-          <t>04.07.26</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="I690" s="2" t="inlineStr">
         <is>
-          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
         </is>
       </c>
       <c r="J690" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:41</t>
+          <t>2026-07-08T16:57:26</t>
         </is>
       </c>
     </row>
     <row r="691">
       <c r="A691" s="2" t="inlineStr">
         <is>
-          <t>WC1X - Postmark, Farringdon</t>
+          <t>W6 - Fulham Reach</t>
         </is>
       </c>
       <c r="B691" s="2" t="inlineStr">
         <is>
-          <t>H3.03.03</t>
+          <t>676</t>
         </is>
       </c>
       <c r="C691" s="2" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="D691" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E691" s="2" t="inlineStr">
         <is>
-          <t>SE&amp;NW</t>
-        </is>
-      </c>
-      <c r="F691" s="2" t="n"/>
+          <t>N,W</t>
+        </is>
+      </c>
+      <c r="F691" s="3" t="n">
+        <v>610000</v>
+      </c>
       <c r="G691" s="2" t="inlineStr"/>
       <c r="H691" s="2" t="inlineStr">
         <is>
-          <t>04.07.26</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="I691" s="2" t="inlineStr">
         <is>
-          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
         </is>
       </c>
       <c r="J691" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:41</t>
+          <t>2026-07-08T16:57:26</t>
         </is>
       </c>
     </row>
     <row r="692">
       <c r="A692" s="2" t="inlineStr">
         <is>
-          <t>WC1X - Postmark, Farringdon</t>
+          <t>W6 - Fulham Reach</t>
         </is>
       </c>
       <c r="B692" s="2" t="inlineStr">
         <is>
-          <t>H4.00.02</t>
+          <t>677</t>
         </is>
       </c>
       <c r="C692" s="2" t="inlineStr">
         <is>
-          <t>Ground</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="D692" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E692" s="2" t="inlineStr">
         <is>
-          <t>SE&amp;NW</t>
+          <t>N,W</t>
         </is>
       </c>
       <c r="F692" s="3" t="n">
-        <v>1450000</v>
+        <v>610000</v>
       </c>
       <c r="G692" s="2" t="inlineStr"/>
       <c r="H692" s="2" t="inlineStr">
         <is>
-          <t>04.07.26</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="I692" s="2" t="inlineStr">
         <is>
-          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
         </is>
       </c>
       <c r="J692" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:41</t>
+          <t>2026-07-08T16:57:26</t>
         </is>
       </c>
     </row>
     <row r="693">
       <c r="A693" s="2" t="inlineStr">
         <is>
-          <t>WC1X - Postmark, Farringdon</t>
+          <t>W6 - Fulham Reach</t>
         </is>
       </c>
       <c r="B693" s="2" t="inlineStr">
         <is>
-          <t>H5.00.01</t>
+          <t>691</t>
         </is>
       </c>
       <c r="C693" s="2" t="inlineStr">
         <is>
-          <t>Ground</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="D693" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E693" s="2" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>N,W</t>
         </is>
       </c>
       <c r="F693" s="3" t="n">
-        <v>1315000</v>
+        <v>617500</v>
       </c>
       <c r="G693" s="2" t="inlineStr"/>
       <c r="H693" s="2" t="inlineStr">
         <is>
-          <t>04.07.26</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="I693" s="2" t="inlineStr">
         <is>
-          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
         </is>
       </c>
       <c r="J693" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:41</t>
+          <t>2026-07-08T16:57:26</t>
         </is>
       </c>
     </row>
     <row r="694">
       <c r="A694" s="2" t="inlineStr">
         <is>
-          <t>WC1X - Postmark, Farringdon</t>
+          <t>W6 - Fulham Reach</t>
         </is>
       </c>
       <c r="B694" s="2" t="inlineStr">
         <is>
-          <t>H5.00.02</t>
+          <t>703</t>
         </is>
       </c>
       <c r="C694" s="2" t="inlineStr">
         <is>
-          <t>Ground</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="D694" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E694" s="2" t="inlineStr">
         <is>
-          <t>NW</t>
+          <t>N,W</t>
         </is>
       </c>
       <c r="F694" s="3" t="n">
-        <v>1315000</v>
+        <v>617500</v>
       </c>
       <c r="G694" s="2" t="inlineStr"/>
       <c r="H694" s="2" t="inlineStr">
         <is>
-          <t>04.07.26</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="I694" s="2" t="inlineStr">
         <is>
-          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
         </is>
       </c>
       <c r="J694" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:41</t>
+          <t>2026-07-08T16:57:26</t>
         </is>
       </c>
     </row>
     <row r="695">
       <c r="A695" s="2" t="inlineStr">
         <is>
-          <t>WC1X - Postmark, Farringdon</t>
+          <t>W6 - Fulham Reach</t>
         </is>
       </c>
       <c r="B695" s="2" t="inlineStr">
         <is>
-          <t>H5.00.03</t>
+          <t>704</t>
         </is>
       </c>
       <c r="C695" s="2" t="inlineStr">
         <is>
-          <t>Ground</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="D695" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E695" s="2" t="inlineStr">
         <is>
-          <t>SE&amp;NE</t>
+          <t>N,W</t>
         </is>
       </c>
       <c r="F695" s="3" t="n">
-        <v>1015000</v>
+        <v>623000</v>
       </c>
       <c r="G695" s="2" t="inlineStr"/>
       <c r="H695" s="2" t="inlineStr">
         <is>
-          <t>04.07.26</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="I695" s="2" t="inlineStr">
         <is>
-          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
         </is>
       </c>
       <c r="J695" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:41</t>
+          <t>2026-07-08T16:57:26</t>
         </is>
       </c>
     </row>
     <row r="696">
       <c r="A696" s="2" t="inlineStr">
         <is>
-          <t>WC1X - Postmark, Farringdon</t>
+          <t>W6 - Fulham Reach</t>
         </is>
       </c>
       <c r="B696" s="2" t="inlineStr">
         <is>
-          <t>H7.00.02</t>
+          <t>705</t>
         </is>
       </c>
       <c r="C696" s="2" t="inlineStr">
         <is>
-          <t>Ground</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="D696" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E696" s="2" t="inlineStr">
         <is>
-          <t>SE&amp;NW</t>
+          <t>N,W</t>
         </is>
       </c>
       <c r="F696" s="3" t="n">
-        <v>1875000</v>
+        <v>623000</v>
       </c>
       <c r="G696" s="2" t="inlineStr"/>
       <c r="H696" s="2" t="inlineStr">
         <is>
-          <t>04.07.26</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="I696" s="2" t="inlineStr">
         <is>
-          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
         </is>
       </c>
       <c r="J696" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:41</t>
+          <t>2026-07-08T16:57:26</t>
         </is>
       </c>
     </row>
     <row r="697">
       <c r="A697" s="2" t="inlineStr">
         <is>
-          <t>WC1X - Postmark, Farringdon</t>
+          <t>W6 - Fulham Reach</t>
         </is>
       </c>
       <c r="B697" s="2" t="inlineStr">
         <is>
-          <t>J1.00.01</t>
+          <t>706</t>
         </is>
       </c>
       <c r="C697" s="2" t="inlineStr">
         <is>
-          <t>Ground</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="D697" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E697" s="2" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>N,W</t>
         </is>
       </c>
       <c r="F697" s="3" t="n">
-        <v>950000</v>
+        <v>623000</v>
       </c>
       <c r="G697" s="2" t="inlineStr"/>
       <c r="H697" s="2" t="inlineStr">
         <is>
-          <t>04.07.26</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="I697" s="2" t="inlineStr">
         <is>
-          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
         </is>
       </c>
       <c r="J697" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:41</t>
+          <t>2026-07-08T16:57:26</t>
         </is>
       </c>
     </row>
     <row r="698">
       <c r="A698" s="2" t="inlineStr">
         <is>
-          <t>WC1X - Postmark, Farringdon</t>
+          <t>W6 - Fulham Reach</t>
         </is>
       </c>
       <c r="B698" s="2" t="inlineStr">
         <is>
-          <t>J1.00.04</t>
+          <t>707</t>
         </is>
       </c>
       <c r="C698" s="2" t="inlineStr">
         <is>
-          <t>Ground</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="D698" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E698" s="2" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>N,W</t>
         </is>
       </c>
       <c r="F698" s="3" t="n">
-        <v>965000</v>
+        <v>623000</v>
       </c>
       <c r="G698" s="2" t="inlineStr"/>
       <c r="H698" s="2" t="inlineStr">
         <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="I698" s="2" t="inlineStr">
+        <is>
+          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
+        </is>
+      </c>
+      <c r="J698" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:57:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="2" t="inlineStr">
+        <is>
+          <t>W6 - Fulham Reach</t>
+        </is>
+      </c>
+      <c r="B699" s="2" t="inlineStr">
+        <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="C699" s="2" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="D699" s="2" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
+        </is>
+      </c>
+      <c r="E699" s="2" t="inlineStr">
+        <is>
+          <t>N,W</t>
+        </is>
+      </c>
+      <c r="F699" s="3" t="n">
+        <v>598000</v>
+      </c>
+      <c r="G699" s="2" t="inlineStr"/>
+      <c r="H699" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="I699" s="2" t="inlineStr">
+        <is>
+          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
+        </is>
+      </c>
+      <c r="J699" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:57:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="2" t="inlineStr">
+        <is>
+          <t>WC1X - Postmark, Farringdon</t>
+        </is>
+      </c>
+      <c r="B700" s="2" t="inlineStr">
+        <is>
+          <t>H1.01.01</t>
+        </is>
+      </c>
+      <c r="C700" s="2" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="D700" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E700" s="2" t="inlineStr">
+        <is>
+          <t>SE&amp;NW</t>
+        </is>
+      </c>
+      <c r="F700" s="3" t="n">
+        <v>1395000</v>
+      </c>
+      <c r="G700" s="2" t="inlineStr"/>
+      <c r="H700" s="2" t="inlineStr">
+        <is>
           <t>04.07.26</t>
         </is>
       </c>
-      <c r="I698" s="2" t="inlineStr">
+      <c r="I700" s="2" t="inlineStr">
         <is>
           <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
         </is>
       </c>
-      <c r="J698" s="2" t="inlineStr">
+      <c r="J700" s="2" t="inlineStr">
         <is>
           <t>2026-07-08T17:01:41</t>
         </is>
       </c>
     </row>
+    <row r="701">
+      <c r="A701" s="2" t="inlineStr">
+        <is>
+          <t>WC1X - Postmark, Farringdon</t>
+        </is>
+      </c>
+      <c r="B701" s="2" t="inlineStr">
+        <is>
+          <t>H1.01.02</t>
+        </is>
+      </c>
+      <c r="C701" s="2" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="D701" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E701" s="2" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+      <c r="F701" s="3" t="n">
+        <v>1410000</v>
+      </c>
+      <c r="G701" s="2" t="inlineStr"/>
+      <c r="H701" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26</t>
+        </is>
+      </c>
+      <c r="I701" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+        </is>
+      </c>
+      <c r="J701" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:01:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="2" t="inlineStr">
+        <is>
+          <t>WC1X - Postmark, Farringdon</t>
+        </is>
+      </c>
+      <c r="B702" s="2" t="inlineStr">
+        <is>
+          <t>H1.01.03</t>
+        </is>
+      </c>
+      <c r="C702" s="2" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="D702" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E702" s="2" t="inlineStr">
+        <is>
+          <t>SW&amp;NE</t>
+        </is>
+      </c>
+      <c r="F702" s="2" t="n"/>
+      <c r="G702" s="2" t="inlineStr"/>
+      <c r="H702" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26</t>
+        </is>
+      </c>
+      <c r="I702" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+        </is>
+      </c>
+      <c r="J702" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:01:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="2" t="inlineStr">
+        <is>
+          <t>WC1X - Postmark, Farringdon</t>
+        </is>
+      </c>
+      <c r="B703" s="2" t="inlineStr">
+        <is>
+          <t>H3.00.01</t>
+        </is>
+      </c>
+      <c r="C703" s="2" t="inlineStr">
+        <is>
+          <t>Ground</t>
+        </is>
+      </c>
+      <c r="D703" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E703" s="2" t="inlineStr">
+        <is>
+          <t>SE&amp;NW</t>
+        </is>
+      </c>
+      <c r="F703" s="3" t="n">
+        <v>1450000</v>
+      </c>
+      <c r="G703" s="2" t="inlineStr"/>
+      <c r="H703" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26</t>
+        </is>
+      </c>
+      <c r="I703" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+        </is>
+      </c>
+      <c r="J703" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:01:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="2" t="inlineStr">
+        <is>
+          <t>WC1X - Postmark, Farringdon</t>
+        </is>
+      </c>
+      <c r="B704" s="2" t="inlineStr">
+        <is>
+          <t>H3.01.01</t>
+        </is>
+      </c>
+      <c r="C704" s="2" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="D704" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E704" s="2" t="inlineStr">
+        <is>
+          <t>SE&amp;NW</t>
+        </is>
+      </c>
+      <c r="F704" s="3" t="n">
+        <v>995000</v>
+      </c>
+      <c r="G704" s="2" t="inlineStr"/>
+      <c r="H704" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26</t>
+        </is>
+      </c>
+      <c r="I704" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+        </is>
+      </c>
+      <c r="J704" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:01:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="2" t="inlineStr">
+        <is>
+          <t>WC1X - Postmark, Farringdon</t>
+        </is>
+      </c>
+      <c r="B705" s="2" t="inlineStr">
+        <is>
+          <t>H3.03.03</t>
+        </is>
+      </c>
+      <c r="C705" s="2" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="D705" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E705" s="2" t="inlineStr">
+        <is>
+          <t>SE&amp;NW</t>
+        </is>
+      </c>
+      <c r="F705" s="2" t="n"/>
+      <c r="G705" s="2" t="inlineStr"/>
+      <c r="H705" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26</t>
+        </is>
+      </c>
+      <c r="I705" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+        </is>
+      </c>
+      <c r="J705" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:01:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="2" t="inlineStr">
+        <is>
+          <t>WC1X - Postmark, Farringdon</t>
+        </is>
+      </c>
+      <c r="B706" s="2" t="inlineStr">
+        <is>
+          <t>H4.00.02</t>
+        </is>
+      </c>
+      <c r="C706" s="2" t="inlineStr">
+        <is>
+          <t>Ground</t>
+        </is>
+      </c>
+      <c r="D706" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E706" s="2" t="inlineStr">
+        <is>
+          <t>SE&amp;NW</t>
+        </is>
+      </c>
+      <c r="F706" s="3" t="n">
+        <v>1450000</v>
+      </c>
+      <c r="G706" s="2" t="inlineStr"/>
+      <c r="H706" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26</t>
+        </is>
+      </c>
+      <c r="I706" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+        </is>
+      </c>
+      <c r="J706" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:01:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="2" t="inlineStr">
+        <is>
+          <t>WC1X - Postmark, Farringdon</t>
+        </is>
+      </c>
+      <c r="B707" s="2" t="inlineStr">
+        <is>
+          <t>H5.00.01</t>
+        </is>
+      </c>
+      <c r="C707" s="2" t="inlineStr">
+        <is>
+          <t>Ground</t>
+        </is>
+      </c>
+      <c r="D707" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E707" s="2" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+      <c r="F707" s="3" t="n">
+        <v>1315000</v>
+      </c>
+      <c r="G707" s="2" t="inlineStr"/>
+      <c r="H707" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26</t>
+        </is>
+      </c>
+      <c r="I707" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+        </is>
+      </c>
+      <c r="J707" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:01:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="2" t="inlineStr">
+        <is>
+          <t>WC1X - Postmark, Farringdon</t>
+        </is>
+      </c>
+      <c r="B708" s="2" t="inlineStr">
+        <is>
+          <t>H5.00.02</t>
+        </is>
+      </c>
+      <c r="C708" s="2" t="inlineStr">
+        <is>
+          <t>Ground</t>
+        </is>
+      </c>
+      <c r="D708" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E708" s="2" t="inlineStr">
+        <is>
+          <t>NW</t>
+        </is>
+      </c>
+      <c r="F708" s="3" t="n">
+        <v>1315000</v>
+      </c>
+      <c r="G708" s="2" t="inlineStr"/>
+      <c r="H708" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26</t>
+        </is>
+      </c>
+      <c r="I708" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+        </is>
+      </c>
+      <c r="J708" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:01:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="2" t="inlineStr">
+        <is>
+          <t>WC1X - Postmark, Farringdon</t>
+        </is>
+      </c>
+      <c r="B709" s="2" t="inlineStr">
+        <is>
+          <t>H5.00.03</t>
+        </is>
+      </c>
+      <c r="C709" s="2" t="inlineStr">
+        <is>
+          <t>Ground</t>
+        </is>
+      </c>
+      <c r="D709" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E709" s="2" t="inlineStr">
+        <is>
+          <t>SE&amp;NE</t>
+        </is>
+      </c>
+      <c r="F709" s="3" t="n">
+        <v>1015000</v>
+      </c>
+      <c r="G709" s="2" t="inlineStr"/>
+      <c r="H709" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26</t>
+        </is>
+      </c>
+      <c r="I709" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+        </is>
+      </c>
+      <c r="J709" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:01:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="2" t="inlineStr">
+        <is>
+          <t>WC1X - Postmark, Farringdon</t>
+        </is>
+      </c>
+      <c r="B710" s="2" t="inlineStr">
+        <is>
+          <t>H7.00.02</t>
+        </is>
+      </c>
+      <c r="C710" s="2" t="inlineStr">
+        <is>
+          <t>Ground</t>
+        </is>
+      </c>
+      <c r="D710" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E710" s="2" t="inlineStr">
+        <is>
+          <t>SE&amp;NW</t>
+        </is>
+      </c>
+      <c r="F710" s="3" t="n">
+        <v>1875000</v>
+      </c>
+      <c r="G710" s="2" t="inlineStr"/>
+      <c r="H710" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26</t>
+        </is>
+      </c>
+      <c r="I710" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+        </is>
+      </c>
+      <c r="J710" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:01:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="2" t="inlineStr">
+        <is>
+          <t>WC1X - Postmark, Farringdon</t>
+        </is>
+      </c>
+      <c r="B711" s="2" t="inlineStr">
+        <is>
+          <t>J1.00.01</t>
+        </is>
+      </c>
+      <c r="C711" s="2" t="inlineStr">
+        <is>
+          <t>Ground</t>
+        </is>
+      </c>
+      <c r="D711" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E711" s="2" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+      <c r="F711" s="3" t="n">
+        <v>950000</v>
+      </c>
+      <c r="G711" s="2" t="inlineStr"/>
+      <c r="H711" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26</t>
+        </is>
+      </c>
+      <c r="I711" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+        </is>
+      </c>
+      <c r="J711" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:01:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="2" t="inlineStr">
+        <is>
+          <t>WC1X - Postmark, Farringdon</t>
+        </is>
+      </c>
+      <c r="B712" s="2" t="inlineStr">
+        <is>
+          <t>J1.00.04</t>
+        </is>
+      </c>
+      <c r="C712" s="2" t="inlineStr">
+        <is>
+          <t>Ground</t>
+        </is>
+      </c>
+      <c r="D712" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E712" s="2" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="F712" s="3" t="n">
+        <v>965000</v>
+      </c>
+      <c r="G712" s="2" t="inlineStr"/>
+      <c r="H712" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26</t>
+        </is>
+      </c>
+      <c r="I712" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+        </is>
+      </c>
+      <c r="J712" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:01:41</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J698"/>
+  <autoFilter ref="A1:J712"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -45723,7 +46477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F153"/>
+  <dimension ref="A1:F155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -45769,156 +46523,156 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Marleigh Park</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Marleigh Apartments Franklin and Kestrel Price List - 22.05.2026.pdf</t>
+          <t>WCL - Ready to move - Solaris One 27.06.26.pdf</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Marleigh Apartments Franklin and Kestrel Price List - 22.05.2026</t>
+          <t>WCL - Ready to move - Solaris One 27.06.26</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:04:25</t>
+          <t>2026-07-09T09:53:11</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Marleigh Park</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Marleigh Apartments Franklin and Kestrel Price List 01.07.2026.pdf</t>
+          <t>WCL-Ready to Move In- Solaris One 02.07.26.pdf</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Marleigh Apartments Franklin and Kestrel Price List 01.07.2026</t>
+          <t>WCL-Ready to Move In- Solaris One 02.07.26</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:04:25</t>
+          <t>2026-07-09T09:53:11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Hartmere</t>
+          <t>Marleigh Park</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Hartmere Freehold Houses Price List - 22.05.2026.pdf</t>
+          <t>Marleigh Apartments Franklin and Kestrel Price List - 22.05.2026.pdf</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Hartmere Freehold Houses Price List - 22.05.2026</t>
+          <t>Marleigh Apartments Franklin and Kestrel Price List - 22.05.2026</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:04:19</t>
+          <t>2026-07-08T17:04:25</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Hartmere</t>
+          <t>Marleigh Park</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Hartmere Price List- Freehold Houses 01.07.2026.pdf</t>
+          <t>Marleigh Apartments Franklin and Kestrel Price List 01.07.2026.pdf</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Hartmere Price List- Freehold Houses 01.07.2026</t>
+          <t>Marleigh Apartments Franklin and Kestrel Price List 01.07.2026</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:04:19</t>
+          <t>2026-07-08T17:04:25</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>City Reach</t>
+          <t>Hartmere</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>City Reach Florence Court Price List - 22.05.2026.pdf</t>
+          <t>Hartmere Freehold Houses Price List - 22.05.2026.pdf</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>City Reach Florence Court Price List - 22.05.2026</t>
+          <t>Hartmere Freehold Houses Price List - 22.05.2026</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:04:14</t>
+          <t>2026-07-08T17:04:19</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>City Reach</t>
+          <t>Hartmere</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>City Reach Florence Court Price List 01.07.2026.pdf</t>
+          <t>Hartmere Price List- Freehold Houses 01.07.2026.pdf</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>City Reach Florence Court Price List 01.07.2026</t>
+          <t>Hartmere Price List- Freehold Houses 01.07.2026</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:04:14</t>
+          <t>2026-07-08T17:04:19</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
     </row>
@@ -45930,21 +46684,21 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>City Reach Ida Court Price List - 22.05.2026.pdf</t>
+          <t>City Reach Florence Court Price List - 22.05.2026.pdf</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>City Reach Ida Court Price List - 22.05.2026</t>
+          <t>City Reach Florence Court Price List - 22.05.2026</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:04:10</t>
+          <t>2026-07-08T17:04:14</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
     </row>
@@ -45956,135 +46710,135 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>City Reach Ida Court Price List 01.07.2026.pdf</t>
+          <t>City Reach Florence Court Price List 01.07.2026.pdf</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>City Reach Ida Court Price List 01.07.2026</t>
+          <t>City Reach Florence Court Price List 01.07.2026</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:04:10</t>
+          <t>2026-07-08T17:04:14</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>W14 - 50 Brook Green (London Square)</t>
+          <t>City Reach</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Fifty Brook Green - Price List - 15.06.2026.pdf</t>
+          <t>City Reach Ida Court Price List - 22.05.2026.pdf</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Fifty Brook Green - Price List - 15.06.2026</t>
+          <t>City Reach Ida Court Price List - 22.05.2026</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:04:04</t>
+          <t>2026-07-08T17:04:10</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>W14 - 50 Brook Green (London Square)</t>
+          <t>City Reach</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Fifty Brook Green - Price List - 29.06.2026.pdf</t>
+          <t>City Reach Ida Court Price List 01.07.2026.pdf</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Fifty Brook Green - Price List - 29.06.2026</t>
+          <t>City Reach Ida Court Price List 01.07.2026</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:04:04</t>
+          <t>2026-07-08T17:04:10</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SW6 - Chelsea Waterfront Tower East</t>
+          <t>W14 - 50 Brook Green (London Square)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Tower East  Pricelist  29th June 2026.pdf</t>
+          <t>Fifty Brook Green - Price List - 15.06.2026.pdf</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Tower East  Pricelist  29th June 2026</t>
+          <t>Fifty Brook Green - Price List - 15.06.2026</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:03:17</t>
+          <t>2026-07-08T17:04:04</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="F12" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>SW6 - Chelsea Waterfront Tower East</t>
+          <t>W14 - 50 Brook Green (London Square)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Tower East  Pricelist 8th June 2026.pdf</t>
+          <t>Fifty Brook Green - Price List - 29.06.2026.pdf</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Tower East  Pricelist 8th June 2026</t>
+          <t>Fifty Brook Green - Price List - 29.06.2026</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:03:17</t>
+          <t>2026-07-08T17:04:04</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="F13" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -46094,27 +46848,23 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Powerhouse Pricelist  29th June 2026.pdf</t>
+          <t>Tower East  Pricelist  29th June 2026.pdf</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Powerhouse Pricelist  29th June 2026</t>
+          <t>Tower East  Pricelist  29th June 2026</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:03:08</t>
+          <t>2026-07-08T17:03:17</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -46124,27 +46874,23 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Powerhouse Pricelist 8th June 2026.pdf</t>
+          <t>Tower East  Pricelist 8th June 2026.pdf</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Powerhouse Pricelist 8th June 2026</t>
+          <t>Tower East  Pricelist 8th June 2026</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:03:08</t>
+          <t>2026-07-08T17:03:17</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -46154,17 +46900,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Water Gardens Pricelist  29th June 2026.pdf</t>
+          <t>Powerhouse Pricelist  29th June 2026.pdf</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Water Gardens Pricelist  29th June 2026</t>
+          <t>Powerhouse Pricelist  29th June 2026</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:03:01</t>
+          <t>2026-07-08T17:03:08</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
@@ -46184,17 +46930,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Water Gardens Pricelist 8th June 2026.pdf</t>
+          <t>Powerhouse Pricelist 8th June 2026.pdf</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Water Gardens Pricelist 8th June 2026</t>
+          <t>Powerhouse Pricelist 8th June 2026</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:03:01</t>
+          <t>2026-07-08T17:03:08</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
@@ -46214,23 +46960,27 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Tower West Pricelist  29th June 2026.pdf</t>
+          <t>Water Gardens Pricelist  29th June 2026.pdf</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Tower West Pricelist  29th June 2026</t>
+          <t>Water Gardens Pricelist  29th June 2026</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:57</t>
+          <t>2026-07-08T17:03:01</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="F18" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -46240,73 +46990,77 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Tower West Pricelist 8th June 2026.pdf</t>
+          <t>Water Gardens Pricelist 8th June 2026.pdf</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Tower West Pricelist 8th June 2026</t>
+          <t>Water Gardens Pricelist 8th June 2026</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:57</t>
+          <t>2026-07-08T17:03:01</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>KT1 - County Hall Kingston (London Square)</t>
+          <t>SW6 - Chelsea Waterfront Tower East</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>County Hall Kingston - Heritage Collection - Customer Price List 10.06.2026.pdf</t>
+          <t>Tower West Pricelist  29th June 2026.pdf</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>County Hall Kingston - Heritage Collection - Customer Price List 10.06.2026</t>
+          <t>Tower West Pricelist  29th June 2026</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:50</t>
+          <t>2026-07-08T17:02:57</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>KT1 - County Hall Kingston (London Square)</t>
+          <t>SW6 - Chelsea Waterfront Tower East</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>County Hall Kingston - Heritage Collection - Customer Price List 22.06.2026.pdf</t>
+          <t>Tower West Pricelist 8th June 2026.pdf</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>County Hall Kingston - Heritage Collection - Customer Price List 22.06.2026</t>
+          <t>Tower West Pricelist 8th June 2026</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:50</t>
+          <t>2026-07-08T17:02:57</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
     </row>
@@ -46318,21 +47072,21 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>County Hall Kingston - New Build - Customer Price List 02.06.2026.pdf</t>
+          <t>County Hall Kingston - Heritage Collection - Customer Price List 10.06.2026.pdf</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>County Hall Kingston - New Build - Customer Price List 02.06.2026</t>
+          <t>County Hall Kingston - Heritage Collection - Customer Price List 10.06.2026</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:43</t>
+          <t>2026-07-08T17:02:50</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
     </row>
@@ -46344,103 +47098,95 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>County Hall Kingston - New Build - Customer Price List 22.06.2026.pdf</t>
+          <t>County Hall Kingston - Heritage Collection - Customer Price List 22.06.2026.pdf</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>County Hall Kingston - New Build - Customer Price List 22.06.2026</t>
+          <t>County Hall Kingston - Heritage Collection - Customer Price List 22.06.2026</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:43</t>
+          <t>2026-07-08T17:02:50</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TW2 - Twickenham Green (London Square)</t>
+          <t>KT1 - County Hall Kingston (London Square)</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Twickenham Green Price List 16.06.26.pdf</t>
+          <t>County Hall Kingston - New Build - Customer Price List 02.06.2026.pdf</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Twickenham Green Price List 16.06.26</t>
+          <t>County Hall Kingston - New Build - Customer Price List 02.06.2026</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:37</t>
+          <t>2026-07-08T17:02:43</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>TW2 - Twickenham Green (London Square)</t>
+          <t>KT1 - County Hall Kingston (London Square)</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Twickenham Green Price List 28.06.26.pdf</t>
+          <t>County Hall Kingston - New Build - Customer Price List 22.06.2026.pdf</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Twickenham Green Price List 28.06.26</t>
+          <t>County Hall Kingston - New Build - Customer Price List 22.06.2026</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:37</t>
+          <t>2026-07-08T17:02:43</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>TW1 - Twickenham Square (London Square)</t>
+          <t>TW2 - Twickenham Green (London Square)</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Twickenham Square Price List 16.06.26.pdf</t>
+          <t>Twickenham Green Price List 16.06.26.pdf</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Twickenham Square Price List 16.06.26</t>
+          <t>Twickenham Green Price List 16.06.26</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:32</t>
+          <t>2026-07-08T17:02:37</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
@@ -46455,22 +47201,22 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>TW1 - Twickenham Square (London Square)</t>
+          <t>TW2 - Twickenham Green (London Square)</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Twickenham Square Price List 29.06.26.pdf</t>
+          <t>Twickenham Green Price List 28.06.26.pdf</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Twickenham Square Price List 29.06.26</t>
+          <t>Twickenham Green Price List 28.06.26</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:32</t>
+          <t>2026-07-08T17:02:37</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
@@ -46485,528 +47231,536 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>SW19 - Wimbledon Bridge House (London Square)</t>
+          <t>TW1 - Twickenham Square (London Square)</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Wimbledon Bridge House - Price List - 15.06.26.pdf</t>
+          <t>Twickenham Square Price List 16.06.26.pdf</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Wimbledon Bridge House - Price List - 15.06.26</t>
+          <t>Twickenham Square Price List 16.06.26</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:25</t>
+          <t>2026-07-08T17:02:32</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="F28" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>SW19 - Wimbledon Bridge House (London Square)</t>
+          <t>TW1 - Twickenham Square (London Square)</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Wimbledon Bridge House - Price List - 29.06.26.pdf</t>
+          <t>Twickenham Square Price List 29.06.26.pdf</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Wimbledon Bridge House - Price List - 29.06.26</t>
+          <t>Twickenham Square Price List 29.06.26</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:25</t>
+          <t>2026-07-08T17:02:32</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="F29" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>SW11 - Ransomes Wharf (London Square)</t>
+          <t>SW19 - Wimbledon Bridge House (London Square)</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Ransomes Wharf - Customer Price List - 15.06.2026.pdf</t>
+          <t>Wimbledon Bridge House - Price List - 15.06.26.pdf</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Ransomes Wharf - Customer Price List - 15.06.2026</t>
+          <t>Wimbledon Bridge House - Price List - 15.06.26</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:18</t>
+          <t>2026-07-08T17:02:25</t>
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>SW11 - Ransomes Wharf (London Square)</t>
+          <t>SW19 - Wimbledon Bridge House (London Square)</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Ransomes Wharf - Customer Price List - 27.06.2026.pdf</t>
+          <t>Wimbledon Bridge House - Price List - 29.06.26.pdf</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Ransomes Wharf - Customer Price List - 27.06.2026</t>
+          <t>Wimbledon Bridge House - Price List - 29.06.26</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:18</t>
+          <t>2026-07-08T17:02:25</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>SE18 - Woolwich (London Square)</t>
+          <t>SW11 - Ransomes Wharf (London Square)</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Woolwich Price List 15.06.2026.pdf</t>
+          <t>Ransomes Wharf - Customer Price List - 15.06.2026.pdf</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Woolwich Price List 15.06.2026</t>
+          <t>Ransomes Wharf - Customer Price List - 15.06.2026</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:10</t>
+          <t>2026-07-08T17:02:18</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>SE18 - Woolwich (London Square)</t>
+          <t>SW11 - Ransomes Wharf (London Square)</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Woolwich Price List 29.06.2026.pdf</t>
+          <t>Ransomes Wharf - Customer Price List - 27.06.2026.pdf</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Woolwich Price List 29.06.2026</t>
+          <t>Ransomes Wharf - Customer Price List - 27.06.2026</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:10</t>
+          <t>2026-07-08T17:02:18</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>SE1 - Bermondsey (London Square)</t>
+          <t>SE18 - Woolwich (London Square)</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Bermondsey Price List 16.06.26.pdf</t>
+          <t>Woolwich Price List 15.06.2026.pdf</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Bermondsey Price List 16.06.26</t>
+          <t>Woolwich Price List 15.06.2026</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:05</t>
+          <t>2026-07-08T17:02:10</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>SE1 - Bermondsey (London Square)</t>
+          <t>SE18 - Woolwich (London Square)</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Bermondsey Price List 29.06.26.pdf</t>
+          <t>Woolwich Price List 29.06.2026.pdf</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Bermondsey Price List 29.06.26</t>
+          <t>Woolwich Price List 29.06.2026</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:05</t>
+          <t>2026-07-08T17:02:10</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>SE17 - The Wilderly</t>
+          <t>SE1 - Bermondsey (London Square)</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>The Wilderly Tower Availability List July 2026.pdf</t>
+          <t>Bermondsey Price List 16.06.26.pdf</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>The Wilderly Tower Availability List July 2026</t>
+          <t>Bermondsey Price List 16.06.26</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:00</t>
+          <t>2026-07-08T17:02:05</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>SE17 - The Wilderly</t>
+          <t>SE1 - Bermondsey (London Square)</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>The Wilderly Tower Availability List May 2026.pdf</t>
+          <t>Bermondsey Price List 29.06.26.pdf</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>The Wilderly Tower Availability List May 2026</t>
+          <t>Bermondsey Price List 29.06.26</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:00</t>
+          <t>2026-07-08T17:02:05</t>
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>E14 - Goodluck Hope</t>
+          <t>SE17 - The Wilderly</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Goodluck Hope Price List 12th June 2026.pdf</t>
+          <t>The Wilderly Tower Availability List July 2026.pdf</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Goodluck Hope Price List 12th June 2026</t>
+          <t>The Wilderly Tower Availability List July 2026</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:52</t>
+          <t>2026-07-08T17:02:00</t>
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>E14 - Goodluck Hope</t>
+          <t>SE17 - The Wilderly</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Goodluck Hope Price List 30th June 2026.pdf</t>
+          <t>The Wilderly Tower Availability List May 2026.pdf</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Goodluck Hope Price List 30th June 2026</t>
+          <t>The Wilderly Tower Availability List May 2026</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:52</t>
+          <t>2026-07-08T17:02:00</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>WC1X - Postmark, Farringdon</t>
+          <t>E14 - Goodluck Hope</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+          <t>Goodluck Hope Price List 12th June 2026.pdf</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>04.07.26 - Monograph Square - Price List Block H</t>
+          <t>Goodluck Hope Price List 12th June 2026</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:41</t>
+          <t>2026-07-08T17:01:52</t>
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>WC1X - Postmark, Farringdon</t>
+          <t>E14 - Goodluck Hope</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>20.06.26 - Monograph Square - Price List Block H.pdf</t>
+          <t>Goodluck Hope Price List 30th June 2026.pdf</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>20.06.26 - Monograph Square - Price List Block H</t>
+          <t>Goodluck Hope Price List 30th June 2026</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:41</t>
+          <t>2026-07-08T17:01:52</t>
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>SE1 - Westminster Tower (London Square)</t>
+          <t>WC1X - Postmark, Farringdon</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Westminster Tower Price List - 05.07.2026.pdf</t>
+          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Westminster Tower Price List - 05.07.2026</t>
+          <t>04.07.26 - Monograph Square - Price List Block H</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:36</t>
+          <t>2026-07-08T17:01:41</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>SE1 - Westminster Tower (London Square)</t>
+          <t>WC1X - Postmark, Farringdon</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Westminster Tower Price List - 15.06.2026.pdf</t>
+          <t>20.06.26 - Monograph Square - Price List Block H.pdf</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Westminster Tower Price List - 15.06.2026</t>
+          <t>20.06.26 - Monograph Square - Price List Block H</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:36</t>
+          <t>2026-07-08T17:01:41</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>CR0 - Croydon (London Square)</t>
+          <t>SE1 - Westminster Tower (London Square)</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Croydon Price List - 15 June 26.pdf</t>
+          <t>Westminster Tower Price List - 05.07.2026.pdf</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Croydon Price List - 15 June 26</t>
+          <t>Westminster Tower Price List - 05.07.2026</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:30</t>
+          <t>2026-07-08T17:01:36</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="F44" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>CR0 - Croydon (London Square)</t>
+          <t>SE1 - Westminster Tower (London Square)</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Croydon Price List - 29 June 26.pdf</t>
+          <t>Westminster Tower Price List - 15.06.2026.pdf</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Croydon Price List - 29 June 26</t>
+          <t>Westminster Tower Price List - 15.06.2026</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:30</t>
+          <t>2026-07-08T17:01:36</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="F45" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>W12 - White City Living</t>
+          <t>CR0 - Croydon (London Square)</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>WCL - Solaris Two 02.07.26.pdf</t>
+          <t>Croydon Price List - 15 June 26.pdf</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>WCL - Solaris Two 02.07.26</t>
+          <t>Croydon Price List - 15 June 26</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-08T17:01:30</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>W12 - White City Living</t>
+          <t>CR0 - Croydon (London Square)</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>WCL - Solaris Two 27.06.26.pdf</t>
+          <t>Croydon Price List - 29 June 26.pdf</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>WCL - Solaris Two 27.06.26</t>
+          <t>Croydon Price List - 29 June 26</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-08T17:01:30</t>
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
     </row>
@@ -47018,21 +47772,21 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>WCL - Cascades Three price list - 02.07.26.pdf</t>
+          <t>WCL - Solaris Two 02.07.26.pdf</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>WCL - Cascades Three price list - 02.07.26</t>
+          <t>WCL - Solaris Two 02.07.26</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:16</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
     </row>
@@ -47044,281 +47798,281 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>WCL - Cascades Three price list - 27.06.26.pdf</t>
+          <t>WCL - Solaris Two 27.06.26.pdf</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>WCL - Cascades Three price list - 27.06.26</t>
+          <t>WCL - Solaris Two 27.06.26</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:16</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>SW18 - Wandsworth Mills</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>CN - WM_ The Artisan Price list - 05.07.26.pdf</t>
+          <t>WCL - Cascades Three price list - 02.07.26.pdf</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>CN - WM_ The Artisan Price list - 05.07.26</t>
+          <t>WCL - Cascades Three price list - 02.07.26</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:05</t>
+          <t>2026-07-08T17:01:16</t>
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>SW18 - Wandsworth Mills</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>CN - WM_ The Artisan Price list 27.06.26.pdf</t>
+          <t>WCL - Cascades Three price list - 27.06.26.pdf</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>CN - WM_ The Artisan Price list 27.06.26</t>
+          <t>WCL - Cascades Three price list - 27.06.26</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:05</t>
+          <t>2026-07-08T17:01:16</t>
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>UB1 - The Green Quarter</t>
+          <t>SW18 - Wandsworth Mills</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>CN-The Green Quarter - Brickfields Customer Pricelist -05.07.26.pdf</t>
+          <t>CN - WM_ The Artisan Price list - 05.07.26.pdf</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>CN-The Green Quarter - Brickfields Customer Pricelist -05.07.26</t>
+          <t>CN - WM_ The Artisan Price list - 05.07.26</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:58</t>
+          <t>2026-07-08T17:01:05</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>UB1 - The Green Quarter</t>
+          <t>SW18 - Wandsworth Mills</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>The Green Quarter - Brickfields Customer Pricelist -28.06.26.pdf</t>
+          <t>CN - WM_ The Artisan Price list 27.06.26.pdf</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>The Green Quarter - Brickfields Customer Pricelist -28.06.26</t>
+          <t>CN - WM_ The Artisan Price list 27.06.26</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:58</t>
+          <t>2026-07-08T17:01:05</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>SM1 - Sutton Garden Square</t>
+          <t>UB1 - The Green Quarter</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Sutton Garden Square Exclusive Preview Price List 05.07.26.pdf</t>
+          <t>CN-The Green Quarter - Brickfields Customer Pricelist -05.07.26.pdf</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Sutton Garden Square Exclusive Preview Price List 05.07.26</t>
+          <t>CN-The Green Quarter - Brickfields Customer Pricelist -05.07.26</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:50</t>
+          <t>2026-07-08T17:00:58</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>SM1 - Sutton Garden Square</t>
+          <t>UB1 - The Green Quarter</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Sutton Garden Square Exclusive Preview Price List 28.06.26.pdf</t>
+          <t>The Green Quarter - Brickfields Customer Pricelist -28.06.26.pdf</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Sutton Garden Square Exclusive Preview Price List 28.06.26</t>
+          <t>The Green Quarter - Brickfields Customer Pricelist -28.06.26</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:50</t>
+          <t>2026-07-08T17:00:58</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>E2 - Regent's View</t>
+          <t>SM1 - Sutton Garden Square</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>RV-Ready to Move in-Wright Building 06.07.2026.pdf</t>
+          <t>Sutton Garden Square Exclusive Preview Price List 05.07.26.pdf</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>RV-Ready to Move in-Wright Building 06.07.2026</t>
+          <t>Sutton Garden Square Exclusive Preview Price List 05.07.26</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:29</t>
+          <t>2026-07-08T17:00:50</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>E2 - Regent's View</t>
+          <t>SM1 - Sutton Garden Square</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>RV-Ready to move in - Wright Building 29.06.2026.pdf</t>
+          <t>Sutton Garden Square Exclusive Preview Price List 28.06.26.pdf</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>RV-Ready to move in - Wright Building 29.06.2026</t>
+          <t>Sutton Garden Square Exclusive Preview Price List 28.06.26</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:29</t>
+          <t>2026-07-08T17:00:50</t>
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Oakhill</t>
+          <t>E2 - Regent's View</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Oakhill - House 04.07.2026.pdf</t>
+          <t>RV-Ready to Move in-Wright Building 06.07.2026.pdf</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Oakhill - House 04.07.2026</t>
+          <t>RV-Ready to Move in-Wright Building 06.07.2026</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:22</t>
+          <t>2026-07-08T17:00:29</t>
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Oakhill</t>
+          <t>E2 - Regent's View</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Oakhill - House 26.06.2026.pdf</t>
+          <t>RV-Ready to move in - Wright Building 29.06.2026.pdf</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Oakhill - House 26.06.2026</t>
+          <t>RV-Ready to move in - Wright Building 29.06.2026</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:22</t>
+          <t>2026-07-08T17:00:29</t>
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
     </row>
@@ -47330,21 +48084,21 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Oakhill - Apartments 04.07.2026.pdf</t>
+          <t>Oakhill - House 04.07.2026.pdf</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Oakhill - Apartments 04.07.2026</t>
+          <t>Oakhill - House 04.07.2026</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:19</t>
+          <t>2026-07-08T17:00:22</t>
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
     </row>
@@ -47356,73 +48110,73 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Oakhill - Apartments 26.06.2026.pdf</t>
+          <t>Oakhill - House 26.06.2026.pdf</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Oakhill - Apartments 26.06.2026</t>
+          <t>Oakhill - House 26.06.2026</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:19</t>
+          <t>2026-07-08T17:00:22</t>
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>E1 - London Dock</t>
+          <t>Oakhill</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Saffron Private Price list June 05.07.26.pdf</t>
+          <t>Oakhill - Apartments 04.07.2026.pdf</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Saffron Private Price list June 05.07.26</t>
+          <t>Oakhill - Apartments 04.07.2026</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:14</t>
+          <t>2026-07-08T17:00:19</t>
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>E1 - London Dock</t>
+          <t>Oakhill</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Saffron Private Price list June 28.06.26.pdf</t>
+          <t>Oakhill - Apartments 26.06.2026.pdf</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Saffron Private Price list June 28.06.26</t>
+          <t>Oakhill - Apartments 26.06.2026</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:14</t>
+          <t>2026-07-08T17:00:19</t>
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
     </row>
@@ -47434,21 +48188,21 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>London Dock G4 - Chime Gardens 05.07.26.pdf</t>
+          <t>Saffron Private Price list June 05.07.26.pdf</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>London Dock G4 - Chime Gardens 05.07.26</t>
+          <t>Saffron Private Price list June 05.07.26</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:10</t>
+          <t>2026-07-08T17:00:14</t>
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
     </row>
@@ -47460,21 +48214,21 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>London Dock G4 - Chime Gardens 28.06.26.pdf</t>
+          <t>Saffron Private Price list June 28.06.26.pdf</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>London Dock G4 - Chime Gardens 28.06.26</t>
+          <t>Saffron Private Price list June 28.06.26</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:10</t>
+          <t>2026-07-08T17:00:14</t>
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
     </row>
@@ -47486,21 +48240,21 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>London Dock G3 - Imperial Tower - 05.07.26.pdf</t>
+          <t>London Dock G4 - Chime Gardens 05.07.26.pdf</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>London Dock G3 - Imperial Tower - 05.07.26</t>
+          <t>London Dock G4 - Chime Gardens 05.07.26</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:03</t>
+          <t>2026-07-08T17:00:10</t>
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
     </row>
@@ -47512,21 +48266,21 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>London Dock G3 - Imperial Tower - 28.06.26.pdf</t>
+          <t>London Dock G4 - Chime Gardens 28.06.26.pdf</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>London Dock G3 - Imperial Tower - 28.06.26</t>
+          <t>London Dock G4 - Chime Gardens 28.06.26</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:03</t>
+          <t>2026-07-08T17:00:10</t>
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
     </row>
@@ -47538,21 +48292,21 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>London Dock G2 - Kingfisher Court - 05.07.26.pdf</t>
+          <t>London Dock G3 - Imperial Tower - 05.07.26.pdf</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>London Dock G2 - Kingfisher Court - 05.07.26</t>
+          <t>London Dock G3 - Imperial Tower - 05.07.26</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:59:56</t>
+          <t>2026-07-08T17:00:03</t>
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
     </row>
@@ -47564,21 +48318,21 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>London Dock G2 - Kingfisher Court - 28.06.26.pdf</t>
+          <t>London Dock G3 - Imperial Tower - 28.06.26.pdf</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>London Dock G2 - Kingfisher Court - 28.06.26</t>
+          <t>London Dock G3 - Imperial Tower - 28.06.26</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:59:56</t>
+          <t>2026-07-08T17:00:03</t>
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
     </row>
@@ -47590,21 +48344,21 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>London Dock G1 - Tranquillity Place - 05.07.26.pdf</t>
+          <t>London Dock G2 - Kingfisher Court - 05.07.26.pdf</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>London Dock G1 - Tranquillity Place - 05.07.26</t>
+          <t>London Dock G2 - Kingfisher Court - 05.07.26</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:59:48</t>
+          <t>2026-07-08T16:59:56</t>
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
     </row>
@@ -47616,73 +48370,73 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>London Dock G1 - Tranquillity Place - 28.06.26.pdf</t>
+          <t>London Dock G2 - Kingfisher Court - 28.06.26.pdf</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>London Dock G1 - Tranquillity Place - 28.06.26</t>
+          <t>London Dock G2 - Kingfisher Court - 28.06.26</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:59:48</t>
+          <t>2026-07-08T16:59:56</t>
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Leighwood Fields</t>
+          <t>E1 - London Dock</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Leighwood Fields - Phase 3.2 The Orchards 04.07.26.pdf</t>
+          <t>London Dock G1 - Tranquillity Place - 05.07.26.pdf</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Leighwood Fields - Phase 3.2 The Orchards 04.07.26</t>
+          <t>London Dock G1 - Tranquillity Place - 05.07.26</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:59:41</t>
+          <t>2026-07-08T16:59:48</t>
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Leighwood Fields</t>
+          <t>E1 - London Dock</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Leighwood Fields - Phase 3.2 The Orchards 27.06.26.pdf</t>
+          <t>London Dock G1 - Tranquillity Place - 28.06.26.pdf</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Leighwood Fields - Phase 3.2 The Orchards 27.06.26</t>
+          <t>London Dock G1 - Tranquillity Place - 28.06.26</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:59:41</t>
+          <t>2026-07-08T16:59:48</t>
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
     </row>
@@ -47694,21 +48448,21 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Leighwood Fields - Phase 3.2 Luxury Apartment - Leighwood Manor 04.07.26.pdf</t>
+          <t>Leighwood Fields - Phase 3.2 The Orchards 04.07.26.pdf</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Leighwood Fields - Phase 3.2 Luxury Apartment - Leighwood Manor 04.07.26</t>
+          <t>Leighwood Fields - Phase 3.2 The Orchards 04.07.26</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:59:36</t>
+          <t>2026-07-08T16:59:41</t>
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
     </row>
@@ -47720,73 +48474,73 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Leighwood Fields - Phase 3.2 Luxury Apartment - Leighwood Manor 27.06.26.pdf</t>
+          <t>Leighwood Fields - Phase 3.2 The Orchards 27.06.26.pdf</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Leighwood Fields - Phase 3.2 Luxury Apartment - Leighwood Manor 27.06.26</t>
+          <t>Leighwood Fields - Phase 3.2 The Orchards 27.06.26</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:59:36</t>
+          <t>2026-07-08T16:59:41</t>
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Hartland Village</t>
+          <t>Leighwood Fields</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Hartland Village - Phase 3.2 Pinewood Green West 02.07.26.pdf</t>
+          <t>Leighwood Fields - Phase 3.2 Luxury Apartment - Leighwood Manor 04.07.26.pdf</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Hartland Village - Phase 3.2 Pinewood Green West 02.07.26</t>
+          <t>Leighwood Fields - Phase 3.2 Luxury Apartment - Leighwood Manor 04.07.26</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:59:31</t>
+          <t>2026-07-08T16:59:36</t>
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Hartland Village</t>
+          <t>Leighwood Fields</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Hartland Village - Phase 3.2 Pinewood Green West 27.06.26.pdf</t>
+          <t>Leighwood Fields - Phase 3.2 Luxury Apartment - Leighwood Manor 27.06.26.pdf</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Hartland Village - Phase 3.2 Pinewood Green West 27.06.26</t>
+          <t>Leighwood Fields - Phase 3.2 Luxury Apartment - Leighwood Manor 27.06.26</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:59:31</t>
+          <t>2026-07-08T16:59:36</t>
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
     </row>
@@ -47798,21 +48552,21 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Hartland Village - Phase 3.1 Pinewood Green East 02.07.26.pdf</t>
+          <t>Hartland Village - Phase 3.2 Pinewood Green West 02.07.26.pdf</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Hartland Village - Phase 3.1 Pinewood Green East 02.07.26</t>
+          <t>Hartland Village - Phase 3.2 Pinewood Green West 02.07.26</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:59:25</t>
+          <t>2026-07-08T16:59:31</t>
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
     </row>
@@ -47824,21 +48578,21 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Hartland Village - Phase 3.1 Pinewood Green East 27.06.26.pdf</t>
+          <t>Hartland Village - Phase 3.2 Pinewood Green West 27.06.26.pdf</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Hartland Village - Phase 3.1 Pinewood Green East 27.06.26</t>
+          <t>Hartland Village - Phase 3.2 Pinewood Green West 27.06.26</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:59:25</t>
+          <t>2026-07-08T16:59:31</t>
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
     </row>
@@ -47850,17 +48604,17 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Hartland Village - Phase 3.1 Apartment - Camellia Court 02.07.26.pdf</t>
+          <t>Hartland Village - Phase 3.1 Pinewood Green East 02.07.26.pdf</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Hartland Village - Phase 3.1 Apartment - Camellia Court 02.07.26</t>
+          <t>Hartland Village - Phase 3.1 Pinewood Green East 02.07.26</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:59:19</t>
+          <t>2026-07-08T16:59:25</t>
         </is>
       </c>
       <c r="E80" s="2" t="n">
@@ -47876,17 +48630,17 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Hartland Village - Phase 3.1 Apartment - Camellia Court 27.06.26.pdf</t>
+          <t>Hartland Village - Phase 3.1 Pinewood Green East 27.06.26.pdf</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Hartland Village - Phase 3.1 Apartment - Camellia Court 27.06.26</t>
+          <t>Hartland Village - Phase 3.1 Pinewood Green East 27.06.26</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:59:19</t>
+          <t>2026-07-08T16:59:25</t>
         </is>
       </c>
       <c r="E81" s="2" t="n">
@@ -47897,52 +48651,52 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Hareshill</t>
+          <t>Hartland Village</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Hareshill - Phase 3.3 Grove Collection 01.07.26.pdf</t>
+          <t>Hartland Village - Phase 3.1 Apartment - Camellia Court 02.07.26.pdf</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Hareshill - Phase 3.3 Grove Collection 01.07.26</t>
+          <t>Hartland Village - Phase 3.1 Apartment - Camellia Court 02.07.26</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:59:12</t>
+          <t>2026-07-08T16:59:19</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Hareshill</t>
+          <t>Hartland Village</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Hareshill - Phase 3.3 Grove Collection 23.06.26.pdf</t>
+          <t>Hartland Village - Phase 3.1 Apartment - Camellia Court 27.06.26.pdf</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Hareshill - Phase 3.3 Grove Collection 23.06.26</t>
+          <t>Hartland Village - Phase 3.1 Apartment - Camellia Court 27.06.26</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:59:12</t>
+          <t>2026-07-08T16:59:19</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
     </row>
@@ -47954,21 +48708,21 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Hareshill - Phase 3.2 Bloom Collection 01.07.26.pdf</t>
+          <t>Hareshill - Phase 3.3 Grove Collection 01.07.26.pdf</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Hareshill - Phase 3.2 Bloom Collection 01.07.26</t>
+          <t>Hareshill - Phase 3.3 Grove Collection 01.07.26</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:59:05</t>
+          <t>2026-07-08T16:59:12</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F84" s="2" t="inlineStr"/>
     </row>
@@ -47980,135 +48734,135 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Hareshill - Phase 3.2 Bloom Collection 23.06.26.pdf</t>
+          <t>Hareshill - Phase 3.3 Grove Collection 23.06.26.pdf</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Hareshill - Phase 3.2 Bloom Collection 23.06.26</t>
+          <t>Hareshill - Phase 3.3 Grove Collection 23.06.26</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:59:05</t>
+          <t>2026-07-08T16:59:12</t>
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>HA0 - Grand Union</t>
+          <t>Hareshill</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>CN Grand Union - Peninsula House Price List - 05.07.26.pdf</t>
+          <t>Hareshill - Phase 3.2 Bloom Collection 01.07.26.pdf</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>CN Grand Union - Peninsula House Price List - 05.07.26</t>
+          <t>Hareshill - Phase 3.2 Bloom Collection 01.07.26</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:58:58</t>
+          <t>2026-07-08T16:59:05</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>HA0 - Grand Union</t>
+          <t>Hareshill</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>CN Grand Union - Peninsula House Price List - 28.06.26.pdf</t>
+          <t>Hareshill - Phase 3.2 Bloom Collection 23.06.26.pdf</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>CN Grand Union - Peninsula House Price List - 28.06.26</t>
+          <t>Hareshill - Phase 3.2 Bloom Collection 23.06.26</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:58:58</t>
+          <t>2026-07-08T16:59:05</t>
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>B4 - Glasswater Locks</t>
+          <t>HA0 - Grand Union</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>(CN Agent) Glasswater Locks Phase 1 Price List - 10.06.26.pdf</t>
+          <t>CN Grand Union - Peninsula House Price List - 05.07.26.pdf</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>(CN Agent) Glasswater Locks Phase 1 Price List - 10.06.26</t>
+          <t>CN Grand Union - Peninsula House Price List - 05.07.26</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:58:54</t>
+          <t>2026-07-08T16:58:58</t>
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="F88" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>B4 - Glasswater Locks</t>
+          <t>HA0 - Grand Union</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Glasswater Locks Phase 1 Price List - 04.07.26.pdf</t>
+          <t>CN Grand Union - Peninsula House Price List - 28.06.26.pdf</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Glasswater Locks Phase 1 Price List - 04.07.26</t>
+          <t>CN Grand Union - Peninsula House Price List - 28.06.26</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:58:54</t>
+          <t>2026-07-08T16:58:58</t>
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="F89" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -48118,21 +48872,21 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Glasswater Locks Brindley Collection- 04.07.26.pdf</t>
+          <t>(CN Agent) Glasswater Locks Phase 1 Price List - 10.06.26.pdf</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Glasswater Locks Brindley Collection- 04.07.26</t>
+          <t>(CN Agent) Glasswater Locks Phase 1 Price List - 10.06.26</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:58:43</t>
+          <t>2026-07-08T16:58:54</t>
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
     </row>
@@ -48144,177 +48898,177 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Glasswater Locks Brindley Collection- 13.06.26.pdf</t>
+          <t>Glasswater Locks Phase 1 Price List - 04.07.26.pdf</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Glasswater Locks Brindley Collection- 13.06.26</t>
+          <t>Glasswater Locks Phase 1 Price List - 04.07.26</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:58:43</t>
+          <t>2026-07-08T16:58:54</t>
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>W6 - Fulham Reach</t>
+          <t>B4 - Glasswater Locks</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
+          <t>Glasswater Locks Brindley Collection- 04.07.26.pdf</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26</t>
+          <t>Glasswater Locks Brindley Collection- 04.07.26</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:57:26</t>
+          <t>2026-07-08T16:58:43</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>W6 - Fulham Reach</t>
+          <t>B4 - Glasswater Locks</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Fulham Reach Palmer House - CN Agent use only - 24.06.26.pdf</t>
+          <t>Glasswater Locks Brindley Collection- 13.06.26.pdf</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Fulham Reach Palmer House - CN Agent use only - 24.06.26</t>
+          <t>Glasswater Locks Brindley Collection- 13.06.26</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:57:26</t>
+          <t>2026-07-08T16:58:43</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Foal Hurst Green</t>
+          <t>W6 - Fulham Reach</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Foal Hurst Green - Phase 2.1 _ 2.2 Meadow Rise 06.07.2026.pdf</t>
+          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Foal Hurst Green - Phase 2.1 _ 2.2 Meadow Rise 06.07.2026</t>
+          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:57:10</t>
+          <t>2026-07-08T16:57:26</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Foal Hurst Green</t>
+          <t>W6 - Fulham Reach</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Foal Hurst Green - Phase 2.1 _ 2.2 Meadow Rise 25.06.2026.pdf</t>
+          <t>Fulham Reach Palmer House - CN Agent use only - 24.06.26.pdf</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Foal Hurst Green - Phase 2.1 _ 2.2 Meadow Rise 25.06.2026</t>
+          <t>Fulham Reach Palmer House - CN Agent use only - 24.06.26</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:57:10</t>
+          <t>2026-07-08T16:57:26</t>
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>RM9 - Eastbrook Village</t>
+          <t>Foal Hurst Green</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>EBV Mater Price List - 03.07.2026.pdf</t>
+          <t>Foal Hurst Green - Phase 2.1 _ 2.2 Meadow Rise 06.07.2026.pdf</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>EBV Mater Price List - 03.07.2026</t>
+          <t>Foal Hurst Green - Phase 2.1 _ 2.2 Meadow Rise 06.07.2026</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:57:06</t>
+          <t>2026-07-08T16:57:10</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="F96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>RM9 - Eastbrook Village</t>
+          <t>Foal Hurst Green</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>EBV Mater Price List - 24.06.2026.pdf</t>
+          <t>Foal Hurst Green - Phase 2.1 _ 2.2 Meadow Rise 25.06.2026.pdf</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>EBV Mater Price List - 24.06.2026</t>
+          <t>Foal Hurst Green - Phase 2.1 _ 2.2 Meadow Rise 25.06.2026</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:57:06</t>
+          <t>2026-07-08T16:57:10</t>
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
     </row>
@@ -48326,21 +49080,21 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Beech Apartments Price List  - 03.07.26.pdf</t>
+          <t>EBV Mater Price List - 03.07.2026.pdf</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Beech Apartments Price List  - 03.07.26</t>
+          <t>EBV Mater Price List - 03.07.2026</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:56</t>
+          <t>2026-07-08T16:57:06</t>
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="F98" s="2" t="inlineStr"/>
     </row>
@@ -48352,73 +49106,73 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Beech Apartments Price List  - 29.04.26.pdf</t>
+          <t>EBV Mater Price List - 24.06.2026.pdf</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Beech Apartments Price List  - 29.04.26</t>
+          <t>EBV Mater Price List - 24.06.2026</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:56</t>
+          <t>2026-07-08T16:57:06</t>
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="F99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>NW1 - Camden Goods Yard</t>
+          <t>RM9 - Eastbrook Village</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>CN Camden Goods Yard - The Regent  - Pricelist 05.07.26.pdf</t>
+          <t>Beech Apartments Price List  - 03.07.26.pdf</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>CN Camden Goods Yard - The Regent  - Pricelist 05.07.26</t>
+          <t>Beech Apartments Price List  - 03.07.26</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:52</t>
+          <t>2026-07-08T16:56:56</t>
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>NW1 - Camden Goods Yard</t>
+          <t>RM9 - Eastbrook Village</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>CN Camden Goods Yard - The Regent  - Pricelist 28.06.26.pdf</t>
+          <t>Beech Apartments Price List  - 29.04.26.pdf</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>CN Camden Goods Yard - The Regent  - Pricelist 28.06.26</t>
+          <t>Beech Apartments Price List  - 29.04.26</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:52</t>
+          <t>2026-07-08T16:56:56</t>
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F101" s="2" t="inlineStr"/>
     </row>
@@ -48430,21 +49184,21 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Camden Goods Yard - CN The Gallery - Pricelist - 05.07.26.pdf</t>
+          <t>CN Camden Goods Yard - The Regent  - Pricelist 05.07.26.pdf</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Camden Goods Yard - CN The Gallery - Pricelist - 05.07.26</t>
+          <t>CN Camden Goods Yard - The Regent  - Pricelist 05.07.26</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:44</t>
+          <t>2026-07-08T16:56:52</t>
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F102" s="2" t="inlineStr"/>
     </row>
@@ -48456,403 +49210,395 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Camden Goods Yard - The Gallery - Pricelist - 28.06.26.pdf</t>
+          <t>CN Camden Goods Yard - The Regent  - Pricelist 28.06.26.pdf</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Camden Goods Yard - The Gallery - Pricelist - 28.06.26</t>
+          <t>CN Camden Goods Yard - The Regent  - Pricelist 28.06.26</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:44</t>
+          <t>2026-07-08T16:56:52</t>
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>E3 - Bow Green</t>
+          <t>NW1 - Camden Goods Yard</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Bow Green - ready to move in Core B Pricelist.pdf</t>
+          <t>Camden Goods Yard - CN The Gallery - Pricelist - 05.07.26.pdf</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Bow Green - ready to move in Core B Pricelist</t>
+          <t>Camden Goods Yard - CN The Gallery - Pricelist - 05.07.26</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:38</t>
+          <t>2026-07-08T16:56:44</t>
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>E3 - Bow Green</t>
+          <t>NW1 - Camden Goods Yard</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Bow Green Ready to Move In_Core B Pricelist.pdf</t>
+          <t>Camden Goods Yard - The Gallery - Pricelist - 28.06.26.pdf</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Bow Green Ready to Move In_Core B Pricelist</t>
+          <t>Camden Goods Yard - The Gallery - Pricelist - 28.06.26</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:38</t>
+          <t>2026-07-08T16:56:44</t>
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>E3 - Bow Green</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Trillium Price List 01.07.26.pdf</t>
+          <t>Bow Green - ready to move in Core B Pricelist.pdf</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Trillium Price List 01.07.26</t>
+          <t>Bow Green - ready to move in Core B Pricelist</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:32</t>
+          <t>2026-07-08T16:56:38</t>
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>E3 - Bow Green</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Trillium Price List 05.07.26.pdf</t>
+          <t>Bow Green Ready to Move In_Core B Pricelist.pdf</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Trillium Price List 05.07.26</t>
+          <t>Bow Green Ready to Move In_Core B Pricelist</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:32</t>
+          <t>2026-07-08T16:56:38</t>
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>SE11 - Oval Village</t>
+          <t>W2 - Trillium</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Oval Village - The Pinnacle Pricelist  - 05.07.2026 updated.pdf</t>
+          <t>Trillium Price List 01.07.26.pdf</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Oval Village - The Pinnacle Pricelist  - 05.07.2026 updated</t>
+          <t>Trillium Price List 01.07.26</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:24</t>
+          <t>2026-07-08T16:56:32</t>
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>SE11 - Oval Village</t>
+          <t>W2 - Trillium</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Oval Village - The Pinnacle Pricelist  - 05.07.2026.pdf</t>
+          <t>Trillium Price List 05.07.26.pdf</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Oval Village - The Pinnacle Pricelist  - 05.07.2026</t>
+          <t>Trillium Price List 05.07.26</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:24</t>
+          <t>2026-07-08T16:56:32</t>
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Eden Grove</t>
+          <t>SE11 - Oval Village</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Eden Grove - 05.07.26  - Customer Price List.pdf</t>
+          <t>Oval Village - The Pinnacle Pricelist  - 05.07.2026 updated.pdf</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Eden Grove - 05.07.26  - Customer Price List</t>
+          <t>Oval Village - The Pinnacle Pricelist  - 05.07.2026 updated</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:14</t>
+          <t>2026-07-08T16:56:24</t>
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Eden Grove</t>
+          <t>SE11 - Oval Village</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Eden Grove - 12.07.26  - Customer Price List.pdf</t>
+          <t>Oval Village - The Pinnacle Pricelist  - 05.07.2026.pdf</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Eden Grove - 12.07.26  - Customer Price List</t>
+          <t>Oval Village - The Pinnacle Pricelist  - 05.07.2026</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:14</t>
+          <t>2026-07-08T16:56:24</t>
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Bankside Gardens</t>
+          <t>Eden Grove</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Bankside Gardens - Customer Pricelist 05.07.2026.pdf</t>
+          <t>Eden Grove - 05.07.26  - Customer Price List.pdf</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Bankside Gardens - Customer Pricelist 05.07.2026</t>
+          <t>Eden Grove - 05.07.26  - Customer Price List</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:09</t>
+          <t>2026-07-08T16:56:14</t>
         </is>
       </c>
       <c r="E112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Bankside Gardens</t>
+          <t>Eden Grove</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Bankside Gardens - Customer Pricelist 13.07.2026.pdf</t>
+          <t>Eden Grove - 12.07.26  - Customer Price List.pdf</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Bankside Gardens - Customer Pricelist 13.07.2026</t>
+          <t>Eden Grove - 12.07.26  - Customer Price List</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:09</t>
+          <t>2026-07-08T16:56:14</t>
         </is>
       </c>
       <c r="E113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>Bankside Gardens</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Trillium Price List 05.07.26.pdf</t>
+          <t>Bankside Gardens - Customer Pricelist 05.07.2026.pdf</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Trillium Price List 05.07.26</t>
+          <t>Bankside Gardens - Customer Pricelist 05.07.2026</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:04</t>
+          <t>2026-07-08T16:56:09</t>
         </is>
       </c>
       <c r="E114" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="F114" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>Bankside Gardens</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Trillium Price List 28.06.26.pdf</t>
+          <t>Bankside Gardens - Customer Pricelist 13.07.2026.pdf</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Trillium Price List 28.06.26</t>
+          <t>Bankside Gardens - Customer Pricelist 13.07.2026</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:04</t>
+          <t>2026-07-08T16:56:09</t>
         </is>
       </c>
       <c r="E115" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F115" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>WD17 - The Exchange Watford</t>
+          <t>W2 - Trillium</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>The Exchange Union Court Pricelist - 05.07.2026.pdf</t>
+          <t>Trillium Price List 05.07.26.pdf</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>The Exchange Union Court Pricelist - 05.07.2026</t>
+          <t>Trillium Price List 05.07.26</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:55:56</t>
+          <t>2026-07-08T16:56:04</t>
         </is>
       </c>
       <c r="E116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>WD17 - The Exchange Watford</t>
+          <t>W2 - Trillium</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>The Exchange Union Court Pricelist - 28.06.2026.pdf</t>
+          <t>Trillium Price List 28.06.26.pdf</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>The Exchange Union Court Pricelist - 28.06.2026</t>
+          <t>Trillium Price List 28.06.26</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:55:56</t>
+          <t>2026-07-08T16:56:04</t>
         </is>
       </c>
       <c r="E117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -48862,17 +49608,17 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>The Exchange Dart House Price List  05.07.2026.pdf</t>
+          <t>The Exchange Union Court Pricelist - 05.07.2026.pdf</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>The Exchange Dart House Price List  05.07.2026</t>
+          <t>The Exchange Union Court Pricelist - 05.07.2026</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:55:52</t>
+          <t>2026-07-08T16:55:56</t>
         </is>
       </c>
       <c r="E118" s="2" t="n">
@@ -48892,17 +49638,17 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>The Exchange Dart House Price List  28.06.2026.pdf</t>
+          <t>The Exchange Union Court Pricelist - 28.06.2026.pdf</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>The Exchange Dart House Price List  28.06.2026</t>
+          <t>The Exchange Union Court Pricelist - 28.06.2026</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:55:52</t>
+          <t>2026-07-08T16:55:56</t>
         </is>
       </c>
       <c r="E119" s="2" t="n">
@@ -48917,22 +49663,22 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>SE18 - Royal Arsenal Riverside</t>
+          <t>WD17 - The Exchange Watford</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>The Maribor at Royal Arsenal Riverside - Daily Price List - 06.07.26.pdf</t>
+          <t>The Exchange Dart House Price List  05.07.2026.pdf</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>The Maribor at Royal Arsenal Riverside - Daily Price List - 06.07.26</t>
+          <t>The Exchange Dart House Price List  05.07.2026</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:55:44</t>
+          <t>2026-07-08T16:55:52</t>
         </is>
       </c>
       <c r="E120" s="2" t="n">
@@ -48947,22 +49693,22 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>SE18 - Royal Arsenal Riverside</t>
+          <t>WD17 - The Exchange Watford</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>The Maribor at Royal Arsenal Riverside - Daily Price List - 29.06.26.pdf</t>
+          <t>The Exchange Dart House Price List  28.06.2026.pdf</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>The Maribor at Royal Arsenal Riverside - Daily Price List - 29.06.26</t>
+          <t>The Exchange Dart House Price List  28.06.2026</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:55:44</t>
+          <t>2026-07-08T16:55:52</t>
         </is>
       </c>
       <c r="E121" s="2" t="n">
@@ -48982,23 +49728,27 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>RAR _ Ready_to_Move_In Homes - Daily Price List - 06.07.26.pdf</t>
+          <t>The Maribor at Royal Arsenal Riverside - Daily Price List - 06.07.26.pdf</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>RAR _ Ready_to_Move_In Homes - Daily Price List - 06.07.26</t>
+          <t>The Maribor at Royal Arsenal Riverside - Daily Price List - 06.07.26</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:55:35</t>
+          <t>2026-07-08T16:55:44</t>
         </is>
       </c>
       <c r="E122" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F122" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -49008,23 +49758,27 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>RAR _ Ready_to_Move_In Homes - Daily Price List - 29.06.26.pdf</t>
+          <t>The Maribor at Royal Arsenal Riverside - Daily Price List - 29.06.26.pdf</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>RAR _ Ready_to_Move_In Homes - Daily Price List - 29.06.26</t>
+          <t>The Maribor at Royal Arsenal Riverside - Daily Price List - 29.06.26</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:55:35</t>
+          <t>2026-07-08T16:55:44</t>
         </is>
       </c>
       <c r="E123" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F123" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -49034,27 +49788,23 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>RAR Lantern Wharf - Daily Price List - 06.07.26.pdf</t>
+          <t>RAR _ Ready_to_Move_In Homes - Daily Price List - 06.07.26.pdf</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>RAR Lantern Wharf - Daily Price List - 06.07.26</t>
+          <t>RAR _ Ready_to_Move_In Homes - Daily Price List - 06.07.26</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:55:26</t>
+          <t>2026-07-08T16:55:35</t>
         </is>
       </c>
       <c r="E124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -49064,79 +49814,83 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>RAR Lantern Wharf - Daily Price List - 29.06.26.pdf</t>
+          <t>RAR _ Ready_to_Move_In Homes - Daily Price List - 29.06.26.pdf</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>RAR Lantern Wharf - Daily Price List - 29.06.26</t>
+          <t>RAR _ Ready_to_Move_In Homes - Daily Price List - 29.06.26</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:55:26</t>
+          <t>2026-07-08T16:55:35</t>
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>SE11 - Oval Village</t>
+          <t>SE18 - Royal Arsenal Riverside</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Oval Village The Halo - The Residences - Price list - 05.07.2026.pdf</t>
+          <t>RAR Lantern Wharf - Daily Price List - 06.07.26.pdf</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Oval Village The Halo - The Residences - Price list - 05.07.2026</t>
+          <t>RAR Lantern Wharf - Daily Price List - 06.07.26</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:55:19</t>
+          <t>2026-07-08T16:55:26</t>
         </is>
       </c>
       <c r="E126" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F126" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>SE11 - Oval Village</t>
+          <t>SE18 - Royal Arsenal Riverside</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Oval Village The Halo - The Residences - Price list - 28.06.2026.pdf</t>
+          <t>RAR Lantern Wharf - Daily Price List - 29.06.26.pdf</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Oval Village The Halo - The Residences - Price list - 28.06.2026</t>
+          <t>RAR Lantern Wharf - Daily Price List - 29.06.26</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:55:19</t>
+          <t>2026-07-08T16:55:26</t>
         </is>
       </c>
       <c r="E127" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F127" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -49146,21 +49900,21 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Oval Village - The Pinnacle Pricelist  - 05.07.2026.pdf</t>
+          <t>Oval Village The Halo - The Residences - Price list - 05.07.2026.pdf</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Oval Village - The Pinnacle Pricelist  - 05.07.2026</t>
+          <t>Oval Village The Halo - The Residences - Price list - 05.07.2026</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:55:12</t>
+          <t>2026-07-08T16:55:19</t>
         </is>
       </c>
       <c r="E128" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F128" s="2" t="inlineStr"/>
     </row>
@@ -49172,73 +49926,73 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Oval Village - The Pinnacle Pricelist  - 28.06.2026.pdf</t>
+          <t>Oval Village The Halo - The Residences - Price list - 28.06.2026.pdf</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Oval Village - The Pinnacle Pricelist  - 28.06.2026</t>
+          <t>Oval Village The Halo - The Residences - Price list - 28.06.2026</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:55:12</t>
+          <t>2026-07-08T16:55:19</t>
         </is>
       </c>
       <c r="E129" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>SW19 - Lombard Square</t>
+          <t>SE11 - Oval Village</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Rosa House - Daily  Price List 06.07.2026.pdf</t>
+          <t>Oval Village - The Pinnacle Pricelist  - 05.07.2026.pdf</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Rosa House - Daily  Price List 06.07.2026</t>
+          <t>Oval Village - The Pinnacle Pricelist  - 05.07.2026</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:55:01</t>
+          <t>2026-07-08T16:55:12</t>
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>SW19 - Lombard Square</t>
+          <t>SE11 - Oval Village</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Rosa House - Daily  Price List 29.06.2026.pdf</t>
+          <t>Oval Village - The Pinnacle Pricelist  - 28.06.2026.pdf</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Rosa House - Daily  Price List 29.06.2026</t>
+          <t>Oval Village - The Pinnacle Pricelist  - 28.06.2026</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:55:01</t>
+          <t>2026-07-08T16:55:12</t>
         </is>
       </c>
       <c r="E131" s="2" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F131" s="2" t="inlineStr"/>
     </row>
@@ -49250,27 +50004,23 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Opal House  Daily Price List 06.07.2026.pdf</t>
+          <t>Rosa House - Daily  Price List 06.07.2026.pdf</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Opal House  Daily Price List 06.07.2026</t>
+          <t>Rosa House - Daily  Price List 06.07.2026</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:54:51</t>
+          <t>2026-07-08T16:55:01</t>
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -49280,27 +50030,23 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Opal House  Daily Price List 29.06.2026.pdf</t>
+          <t>Rosa House - Daily  Price List 29.06.2026.pdf</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Opal House  Daily Price List 29.06.2026</t>
+          <t>Rosa House - Daily  Price List 29.06.2026</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:54:51</t>
+          <t>2026-07-08T16:55:01</t>
         </is>
       </c>
       <c r="E133" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F133" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F133" s="2" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -49310,17 +50056,17 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Myro House Daily Price List 06.07.2026.pdf</t>
+          <t>Opal House  Daily Price List 06.07.2026.pdf</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Myro House Daily Price List 06.07.2026</t>
+          <t>Opal House  Daily Price List 06.07.2026</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:54:34</t>
+          <t>2026-07-08T16:54:51</t>
         </is>
       </c>
       <c r="E134" s="2" t="n">
@@ -49340,17 +50086,17 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Myro House Daily Price List 29.06.2026.pdf</t>
+          <t>Opal House  Daily Price List 29.06.2026.pdf</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Myro House Daily Price List 29.06.2026</t>
+          <t>Opal House  Daily Price List 29.06.2026</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:54:34</t>
+          <t>2026-07-08T16:54:51</t>
         </is>
       </c>
       <c r="E135" s="2" t="n">
@@ -49370,17 +50116,17 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Fero House - Daily Pricelist 06.07.2026.pdf</t>
+          <t>Myro House Daily Price List 06.07.2026.pdf</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Fero House - Daily Pricelist 06.07.2026</t>
+          <t>Myro House Daily Price List 06.07.2026</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:53:56</t>
+          <t>2026-07-08T16:54:34</t>
         </is>
       </c>
       <c r="E136" s="2" t="n">
@@ -49400,17 +50146,17 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Fero House - Daily Pricelist 29.06.2026.pdf</t>
+          <t>Myro House Daily Price List 29.06.2026.pdf</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Fero House - Daily Pricelist 29.06.2026</t>
+          <t>Myro House Daily Price List 29.06.2026</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:53:56</t>
+          <t>2026-07-08T16:54:34</t>
         </is>
       </c>
       <c r="E137" s="2" t="n">
@@ -49425,54 +50171,62 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>SW6 - King's Road Park</t>
+          <t>SW19 - Lombard Square</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>OKRP- 1 _ 2 -  Bed Price List - 28.06.2026.pdf</t>
+          <t>Fero House - Daily Pricelist 06.07.2026.pdf</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>OKRP- 1 _ 2 -  Bed Price List - 28.06.2026</t>
+          <t>Fero House - Daily Pricelist 06.07.2026</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:53:47</t>
+          <t>2026-07-08T16:53:56</t>
         </is>
       </c>
       <c r="E138" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="F138" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>SW6 - King's Road Park</t>
+          <t>SW19 - Lombard Square</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>OKRP- 1 _ 2 -  Bed Price List 05.07.2026.pdf</t>
+          <t>Fero House - Daily Pricelist 29.06.2026.pdf</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>OKRP- 1 _ 2 -  Bed Price List 05.07.2026</t>
+          <t>Fero House - Daily Pricelist 29.06.2026</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:53:47</t>
+          <t>2026-07-08T16:53:56</t>
         </is>
       </c>
       <c r="E139" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="F139" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -49482,21 +50236,21 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>OKRP - 3 Bed - Price List - 05.07.2026.pdf</t>
+          <t>OKRP- 1 _ 2 -  Bed Price List - 28.06.2026.pdf</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>OKRP - 3 Bed - Price List - 05.07.2026</t>
+          <t>OKRP- 1 _ 2 -  Bed Price List - 28.06.2026</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:53:41</t>
+          <t>2026-07-08T16:53:47</t>
         </is>
       </c>
       <c r="E140" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F140" s="2" t="inlineStr"/>
     </row>
@@ -49508,21 +50262,21 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>OKRP - 3 Bed - Price List - 28.06.2026.pdf</t>
+          <t>OKRP- 1 _ 2 -  Bed Price List 05.07.2026.pdf</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>OKRP - 3 Bed - Price List - 28.06.2026</t>
+          <t>OKRP- 1 _ 2 -  Bed Price List 05.07.2026</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:53:41</t>
+          <t>2026-07-08T16:53:47</t>
         </is>
       </c>
       <c r="E141" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F141" s="2" t="inlineStr"/>
     </row>
@@ -49534,21 +50288,21 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>King_s Road Park - The Charlton - 1 _ 2 Bed Price List  - 05.07.2026.pdf</t>
+          <t>OKRP - 3 Bed - Price List - 05.07.2026.pdf</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>King_s Road Park - The Charlton - 1 _ 2 Bed Price List  - 05.07.2026</t>
+          <t>OKRP - 3 Bed - Price List - 05.07.2026</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:53:34</t>
+          <t>2026-07-08T16:53:41</t>
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F142" s="2" t="inlineStr"/>
     </row>
@@ -49560,83 +50314,75 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>King_s Road Park - The Charlton - 1 _ 2 Bed Price List  - 28.06.2026.pdf</t>
+          <t>OKRP - 3 Bed - Price List - 28.06.2026.pdf</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>King_s Road Park - The Charlton - 1 _ 2 Bed Price List  - 28.06.2026</t>
+          <t>OKRP - 3 Bed - Price List - 28.06.2026</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:53:34</t>
+          <t>2026-07-08T16:53:41</t>
         </is>
       </c>
       <c r="E143" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>SE3 - Kidbrooke Village</t>
+          <t>SW6 - King's Road Park</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Townhouses Price List - 06.07.2026.pdf</t>
+          <t>King_s Road Park - The Charlton - 1 _ 2 Bed Price List  - 05.07.2026.pdf</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Townhouses Price List - 06.07.2026</t>
+          <t>King_s Road Park - The Charlton - 1 _ 2 Bed Price List  - 05.07.2026</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:53:30</t>
+          <t>2026-07-08T16:53:34</t>
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>SE3 - Kidbrooke Village</t>
+          <t>SW6 - King's Road Park</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Townhouses Price List - 29.06.2026.pdf</t>
+          <t>King_s Road Park - The Charlton - 1 _ 2 Bed Price List  - 28.06.2026.pdf</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Townhouses Price List - 29.06.2026</t>
+          <t>King_s Road Park - The Charlton - 1 _ 2 Bed Price List  - 28.06.2026</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:53:30</t>
+          <t>2026-07-08T16:53:34</t>
         </is>
       </c>
       <c r="E145" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F145" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F145" s="2" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -49646,17 +50392,17 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Skyview Gardens - Daily Price List 06.07.2026.pdf</t>
+          <t>Townhouses Price List - 06.07.2026.pdf</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Skyview Gardens - Daily Price List 06.07.2026</t>
+          <t>Townhouses Price List - 06.07.2026</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:53:19</t>
+          <t>2026-07-08T16:53:30</t>
         </is>
       </c>
       <c r="E146" s="2" t="n">
@@ -49676,17 +50422,17 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Skyview Gardens - Daily Price List 29.06.2026.pdf</t>
+          <t>Townhouses Price List - 29.06.2026.pdf</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Skyview Gardens - Daily Price List 29.06.2026</t>
+          <t>Townhouses Price List - 29.06.2026</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:53:19</t>
+          <t>2026-07-08T16:53:30</t>
         </is>
       </c>
       <c r="E147" s="2" t="n">
@@ -49706,23 +50452,27 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>KV Ready-to-Move-In Price List - Master - 06.07.26.pdf</t>
+          <t>Skyview Gardens - Daily Price List 06.07.2026.pdf</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>KV Ready-to-Move-In Price List - Master - 06.07.26</t>
+          <t>Skyview Gardens - Daily Price List 06.07.2026</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:53:11</t>
+          <t>2026-07-08T16:53:19</t>
         </is>
       </c>
       <c r="E148" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F148" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -49732,23 +50482,27 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>KV Ready-to-Move-In Price List - Master - 29.06.26.pdf</t>
+          <t>Skyview Gardens - Daily Price List 29.06.2026.pdf</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>KV Ready-to-Move-In Price List - Master - 29.06.26</t>
+          <t>Skyview Gardens - Daily Price List 29.06.2026</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:53:11</t>
+          <t>2026-07-08T16:53:19</t>
         </is>
       </c>
       <c r="E149" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F149" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -49758,27 +50512,23 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>KV - Lily Residences Daily Pricelist 06.07.2026.pdf</t>
+          <t>KV Ready-to-Move-In Price List - Master - 06.07.26.pdf</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>KV - Lily Residences Daily Pricelist 06.07.2026</t>
+          <t>KV Ready-to-Move-In Price List - Master - 06.07.26</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:53:00</t>
+          <t>2026-07-08T16:53:11</t>
         </is>
       </c>
       <c r="E150" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -49788,82 +50538,138 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>KV - Lily Residences Daily Pricelist 29.06.2026.pdf</t>
+          <t>KV Ready-to-Move-In Price List - Master - 29.06.26.pdf</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>KV - Lily Residences Daily Pricelist 29.06.2026</t>
+          <t>KV Ready-to-Move-In Price List - Master - 29.06.26</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:53:00</t>
+          <t>2026-07-08T16:53:11</t>
         </is>
       </c>
       <c r="E151" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F151" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F151" s="2" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>SE1 - Bermondsey Place</t>
+          <t>SE3 - Kidbrooke Village</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>04.07.2026 Bermondsey Place Distribution Price List.pdf</t>
+          <t>KV - Lily Residences Daily Pricelist 06.07.2026.pdf</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>04.07.2026 Bermondsey Place Distribution Price List</t>
+          <t>KV - Lily Residences Daily Pricelist 06.07.2026</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:52:52</t>
+          <t>2026-07-08T16:53:00</t>
         </is>
       </c>
       <c r="E152" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="F152" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>SE3 - Kidbrooke Village</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>KV - Lily Residences Daily Pricelist 29.06.2026.pdf</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>KV - Lily Residences Daily Pricelist 29.06.2026</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:53:00</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
           <t>SE1 - Bermondsey Place</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>04.07.2026 Bermondsey Place Distribution Price List.pdf</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>04.07.2026 Bermondsey Place Distribution Price List</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:52:52</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="F154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>SE1 - Bermondsey Place</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>25.06.2026 Bermondsey Place Distribution Price List.pdf</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
         <is>
           <t>25.06.2026 Bermondsey Place Distribution Price List</t>
         </is>
       </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>2026-07-08T16:52:52</t>
         </is>
       </c>
-      <c r="E153" s="2" t="n">
+      <c r="E155" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="F153" s="2" t="inlineStr"/>
+      <c r="F155" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F153"/>
+  <autoFilter ref="A1:F155"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/weekly_unit_change_database.xlsx
+++ b/outputs/weekly_unit_change_database.xlsx
@@ -17,12 +17,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'房源变化'!$A$1:$N$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'房源变化'!$A$1:$N$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'降价房源'!$A$1:$N$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'新增房源'!$A$1:$N$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'售出房源'!$A$1:$N$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'其他变化'!$A$1:$N$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'当前房源数据库'!$A$1:$J$712</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'新增房源'!$A$1:$N$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'售出房源'!$A$1:$N$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'其他变化'!$A$1:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'当前房源数据库'!$A$1:$J$716</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'价单导入情况'!$A$1:$I$77</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'版本记录'!$A$1:$F$155</definedName>
   </definedNames>
@@ -448,13 +448,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N111"/>
+  <dimension ref="A1:N115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
@@ -5041,22 +5041,22 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>257</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>2 Bed 2.5 Bath</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>N &amp; W</t>
+          <t>2 Bed 2 Bath</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Balcony</t>
+          <t>S &amp; E</t>
         </is>
       </c>
       <c r="F85" s="2" t="n"/>
@@ -5066,7 +5066,7 @@
         </is>
       </c>
       <c r="H85" s="3" t="n">
-        <v>2350</v>
+        <v>545000</v>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
       <c r="M85" s="2" t="n"/>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:58</t>
+          <t>2026-07-09T11:09:36</t>
         </is>
       </c>
     </row>
@@ -5095,34 +5095,32 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>261</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
           <t>2 Bed 2.5 Bath</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>N &amp; W</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>Balcony</t>
-        </is>
-      </c>
-      <c r="F86" s="3" t="n">
-        <v>1850</v>
-      </c>
+      <c r="F86" s="2" t="n"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
           <t>28.06.26</t>
         </is>
       </c>
       <c r="H86" s="3" t="n">
-        <v>2375</v>
+        <v>555000</v>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
@@ -5131,17 +5129,15 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>PRICE_INCREASE</t>
+          <t>NEW_RELEASE</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr"/>
-      <c r="M86" s="2" t="n">
-        <v>525</v>
-      </c>
+      <c r="M86" s="2" t="n"/>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:58</t>
+          <t>2026-07-09T11:09:36</t>
         </is>
       </c>
     </row>
@@ -5153,34 +5149,32 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>269</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
           <t>2 Bed 2.5 Bath</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>N &amp; W</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>Balcony</t>
-        </is>
-      </c>
-      <c r="F87" s="3" t="n">
-        <v>1875</v>
-      </c>
+      <c r="F87" s="2" t="n"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
           <t>28.06.26</t>
         </is>
       </c>
       <c r="H87" s="3" t="n">
-        <v>2400</v>
+        <v>565000</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
@@ -5189,245 +5183,247 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>PRICE_INCREASE</t>
+          <t>NEW_RELEASE</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr"/>
-      <c r="M87" s="2" t="n">
-        <v>525</v>
-      </c>
+      <c r="M87" s="2" t="n"/>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:58</t>
+          <t>2026-07-09T11:09:36</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>W12 - White City Living</t>
+          <t>UB1 - The Green Quarter</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>V18.02</t>
+          <t>285</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>3+Study</t>
+          <t>2 Bed 2.5 Bath</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>South/West/North</t>
-        </is>
-      </c>
-      <c r="F88" s="3" t="n">
-        <v>2850000</v>
-      </c>
+          <t>N &amp; W</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="n"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>27.06.26</t>
+          <t>28.06.26</t>
         </is>
       </c>
       <c r="H88" s="3" t="n">
-        <v>2815000</v>
+        <v>575000</v>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>02.07.26</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>PRICE_DROP</t>
+          <t>NEW_RELEASE</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr"/>
-      <c r="M88" s="2" t="n">
-        <v>-35000</v>
-      </c>
+      <c r="M88" s="2" t="n"/>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:53:11</t>
+          <t>2026-07-09T11:09:36</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>W12 - White City Living</t>
+          <t>UB1 - The Green Quarter</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>W.14.03</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>North/East</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="n"/>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>400000</v>
+      </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>27.06.26</t>
-        </is>
-      </c>
-      <c r="H89" s="3" t="n">
-        <v>775000</v>
-      </c>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="n"/>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>02.07.26</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>NEW_RELEASE</t>
+          <t>RESERVED</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr"/>
-      <c r="L89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>ON HOLD</t>
+        </is>
+      </c>
       <c r="M89" s="2" t="n"/>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-09T11:09:36</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>W12 - White City Living</t>
+          <t>UB1 - The Green Quarter</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>W.30.01</t>
+          <t>291</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>30/31</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Penthouse</t>
+          <t>1 Bed</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>South/West/North</t>
-        </is>
-      </c>
-      <c r="F90" s="3" t="n">
-        <v>4000000</v>
-      </c>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="n"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>27.06.26</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="n">
-        <v>3990000</v>
-      </c>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="n"/>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>02.07.26</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>PRICE_DROP</t>
-        </is>
-      </c>
-      <c r="K90" s="2" t="inlineStr"/>
-      <c r="L90" s="2" t="inlineStr"/>
-      <c r="M90" s="2" t="n">
-        <v>-10000</v>
-      </c>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>RESERVED</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n"/>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-09T11:09:36</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>W12 - White City Living</t>
+          <t>UB1 - The Green Quarter</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>W.30.02</t>
+          <t>308</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>30/31</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Penthouse</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>South/East/North</t>
-        </is>
-      </c>
-      <c r="F91" s="3" t="n">
-        <v>4000000</v>
-      </c>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="n"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>27.06.26</t>
-        </is>
-      </c>
-      <c r="H91" s="3" t="n">
-        <v>3990000</v>
-      </c>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="n"/>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>02.07.26</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>PRICE_DROP</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr"/>
-      <c r="L91" s="2" t="inlineStr"/>
-      <c r="M91" s="2" t="n">
-        <v>-10000</v>
-      </c>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>RESERVED</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n"/>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-09T11:09:36</t>
         </is>
       </c>
     </row>
@@ -5439,33 +5435,35 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>W.08.01</t>
+          <t>V18.02</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3+Study</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
+          <t>South/West/North</t>
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>775000</v>
+        <v>2850000</v>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
           <t>27.06.26</t>
         </is>
       </c>
-      <c r="H92" s="2" t="n"/>
+      <c r="H92" s="3" t="n">
+        <v>2815000</v>
+      </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
           <t>02.07.26</t>
@@ -5473,19 +5471,17 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>SOLD</t>
+          <t>PRICE_DROP</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
-      <c r="L92" s="2" t="inlineStr">
-        <is>
-          <t>缺失</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="n"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="n">
+        <v>-35000</v>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-09T09:53:11</t>
         </is>
       </c>
     </row>
@@ -5497,7 +5493,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>W.14.01</t>
+          <t>W.14.03</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5512,7 +5508,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
+          <t>North/East</t>
         </is>
       </c>
       <c r="F93" s="2" t="n"/>
@@ -5521,7 +5517,9 @@
           <t>27.06.26</t>
         </is>
       </c>
-      <c r="H93" s="2" t="n"/>
+      <c r="H93" s="3" t="n">
+        <v>775000</v>
+      </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
           <t>02.07.26</t>
@@ -5529,15 +5527,11 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>SOLD</t>
+          <t>NEW_RELEASE</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
-      <c r="L93" s="2" t="inlineStr">
-        <is>
-          <t>缺失</t>
-        </is>
-      </c>
+      <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="n"/>
       <c r="N93" s="2" t="inlineStr">
         <is>
@@ -5548,126 +5542,138 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>I.01.07</t>
+          <t>W.30.01</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30/31</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>Penthouse</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="n"/>
+          <t>South/West/North</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>4000000</v>
+      </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>28.06.26</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="n"/>
+          <t>27.06.26</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="n">
+        <v>3990000</v>
+      </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>05.07.26</t>
+          <t>02.07.26</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>NEW_RELEASE</t>
+          <t>PRICE_DROP</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
-      <c r="M94" s="2" t="n"/>
+      <c r="M94" s="2" t="n">
+        <v>-10000</v>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:04</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>I.08.05</t>
+          <t>W.30.02</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30/31</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Penthouse</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>South/West</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="n"/>
+          <t>South/East/North</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>4000000</v>
+      </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>28.06.26</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="n"/>
+          <t>27.06.26</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="n">
+        <v>3990000</v>
+      </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>05.07.26</t>
+          <t>02.07.26</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>NEW_RELEASE</t>
+          <t>PRICE_DROP</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
-      <c r="M95" s="2" t="n"/>
+      <c r="M95" s="2" t="n">
+        <v>-10000</v>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:04</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>I.10.07</t>
+          <t>W.08.01</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -5675,41 +5681,47 @@
           <t>North/West</t>
         </is>
       </c>
-      <c r="F96" s="2" t="n"/>
+      <c r="F96" s="3" t="n">
+        <v>775000</v>
+      </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>28.06.26</t>
+          <t>27.06.26</t>
         </is>
       </c>
       <c r="H96" s="2" t="n"/>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>05.07.26</t>
+          <t>02.07.26</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>NEW_RELEASE</t>
+          <t>SOLD</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
-      <c r="L96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
       <c r="M96" s="2" t="n"/>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:04</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>I.14.01</t>
+          <t>W.14.01</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -5719,39 +5731,41 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>North/East</t>
+          <t>North/West</t>
         </is>
       </c>
       <c r="F97" s="2" t="n"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>28.06.26</t>
-        </is>
-      </c>
-      <c r="H97" s="3" t="n">
-        <v>1598500</v>
-      </c>
+          <t>27.06.26</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="n"/>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>05.07.26</t>
+          <t>02.07.26</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>NEW_RELEASE</t>
+          <t>SOLD</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
-      <c r="L97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
       <c r="M97" s="2" t="n"/>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:04</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
     </row>
@@ -5763,22 +5777,22 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>I.14.06</t>
+          <t>I.01.07</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>North/West</t>
         </is>
       </c>
       <c r="F98" s="2" t="n"/>
@@ -5815,22 +5829,22 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>I.17.03</t>
+          <t>I.08.05</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>South/West</t>
         </is>
       </c>
       <c r="F99" s="2" t="n"/>
@@ -5867,12 +5881,12 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>I.20.06</t>
+          <t>I.10.07</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -5891,9 +5905,7 @@
           <t>28.06.26</t>
         </is>
       </c>
-      <c r="H100" s="3" t="n">
-        <v>2505000</v>
-      </c>
+      <c r="H100" s="2" t="n"/>
       <c r="I100" s="2" t="inlineStr">
         <is>
           <t>05.07.26</t>
@@ -5921,33 +5933,33 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>I.02.05</t>
+          <t>I.14.01</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>South/ West</t>
-        </is>
-      </c>
-      <c r="F101" s="3" t="n">
-        <v>1350000</v>
-      </c>
+          <t>North/East</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="n"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
           <t>28.06.26</t>
         </is>
       </c>
-      <c r="H101" s="2" t="n"/>
+      <c r="H101" s="3" t="n">
+        <v>1598500</v>
+      </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
           <t>05.07.26</t>
@@ -5955,15 +5967,11 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>SOLD</t>
+          <t>NEW_RELEASE</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr"/>
-      <c r="L101" s="2" t="inlineStr">
-        <is>
-          <t>缺失</t>
-        </is>
-      </c>
+      <c r="L101" s="2" t="inlineStr"/>
       <c r="M101" s="2" t="n"/>
       <c r="N101" s="2" t="inlineStr">
         <is>
@@ -5979,22 +5987,22 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>I.02.07</t>
+          <t>I.14.06</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
+          <t>West</t>
         </is>
       </c>
       <c r="F102" s="2" t="n"/>
@@ -6011,15 +6019,11 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>SOLD</t>
+          <t>NEW_RELEASE</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr"/>
-      <c r="L102" s="2" t="inlineStr">
-        <is>
-          <t>缺失</t>
-        </is>
-      </c>
+      <c r="L102" s="2" t="inlineStr"/>
       <c r="M102" s="2" t="n"/>
       <c r="N102" s="2" t="inlineStr">
         <is>
@@ -6035,27 +6039,25 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>I.07.07</t>
+          <t>I.17.03</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
-        </is>
-      </c>
-      <c r="F103" s="3" t="n">
-        <v>2005000</v>
-      </c>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="n"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
           <t>28.06.26</t>
@@ -6069,15 +6071,11 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>SOLD</t>
+          <t>NEW_RELEASE</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr"/>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>缺失</t>
-        </is>
-      </c>
+      <c r="L103" s="2" t="inlineStr"/>
       <c r="M103" s="2" t="n"/>
       <c r="N103" s="2" t="inlineStr">
         <is>
@@ -6093,22 +6091,22 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>I.13.01</t>
+          <t>I.20.06</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>North/East</t>
+          <t>North/West</t>
         </is>
       </c>
       <c r="F104" s="2" t="n"/>
@@ -6117,7 +6115,9 @@
           <t>28.06.26</t>
         </is>
       </c>
-      <c r="H104" s="2" t="n"/>
+      <c r="H104" s="3" t="n">
+        <v>2505000</v>
+      </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
           <t>05.07.26</t>
@@ -6125,15 +6125,11 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>SOLD</t>
+          <t>NEW_RELEASE</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr"/>
-      <c r="L104" s="2" t="inlineStr">
-        <is>
-          <t>缺失</t>
-        </is>
-      </c>
+      <c r="L104" s="2" t="inlineStr"/>
       <c r="M104" s="2" t="n"/>
       <c r="N104" s="2" t="inlineStr">
         <is>
@@ -6149,26 +6145,26 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>I.13.07</t>
+          <t>I.02.05</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
+          <t>South/ West</t>
         </is>
       </c>
       <c r="F105" s="3" t="n">
-        <v>2181500</v>
+        <v>1350000</v>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
@@ -6207,27 +6203,25 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>I.15.03</t>
+          <t>I.02.07</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="F106" s="3" t="n">
-        <v>1199000</v>
-      </c>
+          <t>North/West</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="n"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
           <t>28.06.26</t>
@@ -6265,25 +6259,27 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>I.15.05</t>
+          <t>I.07.07</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>South/West</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="n"/>
+          <t>North/West</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>2005000</v>
+      </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
           <t>28.06.26</t>
@@ -6321,27 +6317,25 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>I.17.04</t>
+          <t>I.13.01</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="F108" s="3" t="n">
-        <v>1115000</v>
-      </c>
+          <t>North/East</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="n"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
           <t>28.06.26</t>
@@ -6379,26 +6373,26 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>I.20.01</t>
+          <t>I.13.07</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>North/East</t>
+          <t>North/West</t>
         </is>
       </c>
       <c r="F109" s="3" t="n">
-        <v>1845000</v>
+        <v>2181500</v>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
@@ -6437,26 +6431,26 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>I.22.01</t>
+          <t>I.15.03</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>North/East</t>
+          <t>South</t>
         </is>
       </c>
       <c r="F110" s="3" t="n">
-        <v>1897000</v>
+        <v>1199000</v>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
@@ -6495,27 +6489,25 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>I.22.04*</t>
+          <t>I.15.05</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>K</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="F111" s="3" t="n">
-        <v>1205000</v>
-      </c>
+          <t>South/West</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="n"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
           <t>28.06.26</t>
@@ -6545,8 +6537,240 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>W2 - Trillium</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>I.17.04</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>1115000</v>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="n"/>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="n"/>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>W2 - Trillium</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>I.20.01</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>North/East</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>1845000</v>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="n"/>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="n"/>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>W2 - Trillium</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>I.22.01</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>North/East</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>1897000</v>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="n"/>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="n"/>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>W2 - Trillium</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>I.22.04*</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>1205000</v>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="n"/>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="n"/>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N111"/>
+  <autoFilter ref="A1:N115"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7624,13 +7848,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N53"/>
+  <dimension ref="A1:N56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
@@ -10001,22 +10225,22 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>257</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2 Bed 2.5 Bath</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>N &amp; W</t>
+          <t>2 Bed 2 Bath</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Balcony</t>
+          <t>S &amp; E</t>
         </is>
       </c>
       <c r="F45" s="2" t="n"/>
@@ -10026,7 +10250,7 @@
         </is>
       </c>
       <c r="H45" s="3" t="n">
-        <v>2350</v>
+        <v>545000</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
@@ -10043,48 +10267,48 @@
       <c r="M45" s="2" t="n"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:58</t>
+          <t>2026-07-09T11:09:36</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>W12 - White City Living</t>
+          <t>UB1 - The Green Quarter</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>W.14.03</t>
+          <t>261</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2 Bed 2.5 Bath</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>North/East</t>
+          <t>N &amp; W</t>
         </is>
       </c>
       <c r="F46" s="2" t="n"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>27.06.26</t>
+          <t>28.06.26</t>
         </is>
       </c>
       <c r="H46" s="3" t="n">
-        <v>775000</v>
+        <v>555000</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>02.07.26</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -10097,34 +10321,34 @@
       <c r="M46" s="2" t="n"/>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-09T11:09:36</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>UB1 - The Green Quarter</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>I.01.07</t>
+          <t>269</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>2 Bed 2.5 Bath</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
+          <t>N &amp; W</t>
         </is>
       </c>
       <c r="F47" s="2" t="n"/>
@@ -10133,7 +10357,9 @@
           <t>28.06.26</t>
         </is>
       </c>
-      <c r="H47" s="2" t="n"/>
+      <c r="H47" s="3" t="n">
+        <v>565000</v>
+      </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
           <t>05.07.26</t>
@@ -10149,34 +10375,34 @@
       <c r="M47" s="2" t="n"/>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:04</t>
+          <t>2026-07-09T11:09:36</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>UB1 - The Green Quarter</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>I.08.05</t>
+          <t>285</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>2 Bed 2.5 Bath</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>South/West</t>
+          <t>N &amp; W</t>
         </is>
       </c>
       <c r="F48" s="2" t="n"/>
@@ -10185,7 +10411,9 @@
           <t>28.06.26</t>
         </is>
       </c>
-      <c r="H48" s="2" t="n"/>
+      <c r="H48" s="3" t="n">
+        <v>575000</v>
+      </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
           <t>05.07.26</t>
@@ -10201,46 +10429,48 @@
       <c r="M48" s="2" t="n"/>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:04</t>
+          <t>2026-07-09T11:09:36</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>I.10.07</t>
+          <t>W.14.03</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
+          <t>North/East</t>
         </is>
       </c>
       <c r="F49" s="2" t="n"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>28.06.26</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="n"/>
+          <t>27.06.26</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>775000</v>
+      </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>05.07.26</t>
+          <t>02.07.26</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -10253,7 +10483,7 @@
       <c r="M49" s="2" t="n"/>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:04</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
     </row>
@@ -10265,22 +10495,22 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>I.14.01</t>
+          <t>I.01.07</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>North/East</t>
+          <t>North/West</t>
         </is>
       </c>
       <c r="F50" s="2" t="n"/>
@@ -10289,9 +10519,7 @@
           <t>28.06.26</t>
         </is>
       </c>
-      <c r="H50" s="3" t="n">
-        <v>1598500</v>
-      </c>
+      <c r="H50" s="2" t="n"/>
       <c r="I50" s="2" t="inlineStr">
         <is>
           <t>05.07.26</t>
@@ -10319,22 +10547,22 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>I.14.06</t>
+          <t>I.08.05</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>South/West</t>
         </is>
       </c>
       <c r="F51" s="2" t="n"/>
@@ -10371,22 +10599,22 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>I.17.03</t>
+          <t>I.10.07</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North/West</t>
         </is>
       </c>
       <c r="F52" s="2" t="n"/>
@@ -10423,22 +10651,22 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>I.20.06</t>
+          <t>I.14.01</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
+          <t>North/East</t>
         </is>
       </c>
       <c r="F53" s="2" t="n"/>
@@ -10448,7 +10676,7 @@
         </is>
       </c>
       <c r="H53" s="3" t="n">
-        <v>2505000</v>
+        <v>1598500</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
@@ -10469,8 +10697,166 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>W2 - Trillium</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>I.14.06</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="n"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="n"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>W2 - Trillium</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>I.17.03</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="n"/>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="n"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="n"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>W2 - Trillium</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>I.20.06</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>North/West</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>2505000</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>NEW_RELEASE</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="n"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N53"/>
+  <autoFilter ref="A1:N56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10481,7 +10867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -11835,97 +12221,97 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>W12 - White City Living</t>
+          <t>UB1 - The Green Quarter</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>W.08.01</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
+          <t>W</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>775000</v>
+        <v>400000</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>27.06.26</t>
+          <t>28.06.26</t>
         </is>
       </c>
       <c r="H24" s="2" t="n"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>02.07.26</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>SOLD</t>
+          <t>RESERVED</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>ON HOLD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-09T11:09:36</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>W12 - White City Living</t>
+          <t>UB1 - The Green Quarter</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>W.14.01</t>
+          <t>291</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 Bed</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
+          <t>W</t>
         </is>
       </c>
       <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>27.06.26</t>
+          <t>28.06.26</t>
         </is>
       </c>
       <c r="H25" s="2" t="n"/>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>02.07.26</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11933,7 +12319,11 @@
           <t>SOLD</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>RESERVED</t>
+        </is>
+      </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
           <t>缺失</t>
@@ -11942,39 +12332,37 @@
       <c r="M25" s="2" t="n"/>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-09T11:09:36</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>UB1 - The Green Quarter</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>I.02.05</t>
+          <t>308</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>South/ West</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>1350000</v>
-      </c>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
           <t>28.06.26</t>
@@ -11991,7 +12379,11 @@
           <t>SOLD</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>RESERVED</t>
+        </is>
+      </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
           <t>缺失</t>
@@ -12000,29 +12392,29 @@
       <c r="M26" s="2" t="n"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:04</t>
+          <t>2026-07-09T11:09:36</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>I.02.07</t>
+          <t>W.08.01</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -12030,16 +12422,18 @@
           <t>North/West</t>
         </is>
       </c>
-      <c r="F27" s="2" t="n"/>
+      <c r="F27" s="3" t="n">
+        <v>775000</v>
+      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>28.06.26</t>
+          <t>27.06.26</t>
         </is>
       </c>
       <c r="H27" s="2" t="n"/>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>05.07.26</t>
+          <t>02.07.26</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12056,29 +12450,29 @@
       <c r="M27" s="2" t="n"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:04</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>I.07.07</t>
+          <t>W.14.01</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -12086,18 +12480,16 @@
           <t>North/West</t>
         </is>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>2005000</v>
-      </c>
+      <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>28.06.26</t>
+          <t>27.06.26</t>
         </is>
       </c>
       <c r="H28" s="2" t="n"/>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>05.07.26</t>
+          <t>02.07.26</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12114,7 +12506,7 @@
       <c r="M28" s="2" t="n"/>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:04</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
     </row>
@@ -12126,25 +12518,27 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>I.13.01</t>
+          <t>I.02.05</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>North/East</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="n"/>
+          <t>South/ West</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>1350000</v>
+      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
           <t>28.06.26</t>
@@ -12182,12 +12576,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>I.13.07</t>
+          <t>I.02.07</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -12200,9 +12594,7 @@
           <t>North/West</t>
         </is>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>2181500</v>
-      </c>
+      <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
           <t>28.06.26</t>
@@ -12240,26 +12632,26 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>I.15.03</t>
+          <t>I.07.07</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North/West</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1199000</v>
+        <v>2005000</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
@@ -12298,22 +12690,22 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>I.15.05</t>
+          <t>I.13.01</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>South/West</t>
+          <t>North/East</t>
         </is>
       </c>
       <c r="F32" s="2" t="n"/>
@@ -12354,26 +12746,26 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>I.17.04</t>
+          <t>I.13.07</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North/West</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1115000</v>
+        <v>2181500</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
@@ -12412,26 +12804,26 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>I.20.01</t>
+          <t>I.15.03</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>North/East</t>
+          <t>South</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1845000</v>
+        <v>1199000</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
@@ -12470,27 +12862,25 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>I.22.01</t>
+          <t>I.15.05</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>K</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>North/East</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>1897000</v>
-      </c>
+          <t>South/West</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
           <t>28.06.26</t>
@@ -12528,12 +12918,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>I.22.04*</t>
+          <t>I.17.04</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -12547,7 +12937,7 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1205000</v>
+        <v>1115000</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
@@ -12578,8 +12968,182 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>W2 - Trillium</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>I.20.01</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>North/East</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>1845000</v>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>W2 - Trillium</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>I.22.01</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>North/East</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>1897000</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>W2 - Trillium</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>I.22.04*</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>1205000</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="n"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>05.07.26</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T16:56:04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N36"/>
+  <autoFilter ref="A1:N39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12590,12 +13154,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -12847,124 +13411,8 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>UB1 - The Green Quarter</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2 Bed 2.5 Bath</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>N &amp; W</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Balcony</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>1850</v>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>28.06.26</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>2375</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>05.07.26</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>PRICE_INCREASE</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="n">
-        <v>525</v>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-08T17:00:58</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>UB1 - The Green Quarter</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2 Bed 2.5 Bath</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>N &amp; W</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Balcony</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>1875</v>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>28.06.26</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>2400</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>05.07.26</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>PRICE_INCREASE</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="n">
-        <v>525</v>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-08T17:00:58</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N6"/>
+  <autoFilter ref="A1:N4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12975,12 +13423,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J712"/>
+  <dimension ref="A1:J716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -39600,26 +40048,26 @@
       </c>
       <c r="B622" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="C622" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C622" s="2" t="inlineStr">
-        <is>
-          <t>2 Bed 2 Bath</t>
-        </is>
-      </c>
       <c r="D622" s="2" t="inlineStr">
         <is>
-          <t>S &amp; E</t>
+          <t>2 Bed 2.5 Bath</t>
         </is>
       </c>
       <c r="E622" s="2" t="inlineStr">
         <is>
-          <t>Balcony</t>
+          <t>N &amp; W</t>
         </is>
       </c>
       <c r="F622" s="3" t="n">
-        <v>2350</v>
+        <v>550000</v>
       </c>
       <c r="G622" s="2" t="inlineStr"/>
       <c r="H622" s="2" t="inlineStr">
@@ -39634,7 +40082,7 @@
       </c>
       <c r="J622" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:58</t>
+          <t>2026-07-09T11:09:35</t>
         </is>
       </c>
     </row>
@@ -39646,26 +40094,26 @@
       </c>
       <c r="B623" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>257</t>
         </is>
       </c>
       <c r="C623" s="2" t="inlineStr">
         <is>
-          <t>2 Bed 2.5 Bath</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D623" s="2" t="inlineStr">
         <is>
-          <t>N &amp; W</t>
+          <t>2 Bed 2 Bath</t>
         </is>
       </c>
       <c r="E623" s="2" t="inlineStr">
         <is>
-          <t>Balcony</t>
+          <t>S &amp; E</t>
         </is>
       </c>
       <c r="F623" s="3" t="n">
-        <v>2350</v>
+        <v>545000</v>
       </c>
       <c r="G623" s="2" t="inlineStr"/>
       <c r="H623" s="2" t="inlineStr">
@@ -39680,7 +40128,7 @@
       </c>
       <c r="J623" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:58</t>
+          <t>2026-07-09T11:09:35</t>
         </is>
       </c>
     </row>
@@ -39692,26 +40140,26 @@
       </c>
       <c r="B624" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>261</t>
         </is>
       </c>
       <c r="C624" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D624" s="2" t="inlineStr">
+        <is>
           <t>2 Bed 2.5 Bath</t>
         </is>
       </c>
-      <c r="D624" s="2" t="inlineStr">
+      <c r="E624" s="2" t="inlineStr">
         <is>
           <t>N &amp; W</t>
         </is>
       </c>
-      <c r="E624" s="2" t="inlineStr">
-        <is>
-          <t>Balcony</t>
-        </is>
-      </c>
       <c r="F624" s="3" t="n">
-        <v>2375</v>
+        <v>555000</v>
       </c>
       <c r="G624" s="2" t="inlineStr"/>
       <c r="H624" s="2" t="inlineStr">
@@ -39726,7 +40174,7 @@
       </c>
       <c r="J624" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:58</t>
+          <t>2026-07-09T11:09:35</t>
         </is>
       </c>
     </row>
@@ -39738,26 +40186,26 @@
       </c>
       <c r="B625" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>269</t>
         </is>
       </c>
       <c r="C625" s="2" t="inlineStr">
         <is>
-          <t>2 Bed 2 Bath</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D625" s="2" t="inlineStr">
         <is>
-          <t>S &amp; E</t>
+          <t>2 Bed 2.5 Bath</t>
         </is>
       </c>
       <c r="E625" s="2" t="inlineStr">
         <is>
-          <t>Balcony</t>
+          <t>N &amp; W</t>
         </is>
       </c>
       <c r="F625" s="3" t="n">
-        <v>2375</v>
+        <v>565000</v>
       </c>
       <c r="G625" s="2" t="inlineStr"/>
       <c r="H625" s="2" t="inlineStr">
@@ -39772,7 +40220,7 @@
       </c>
       <c r="J625" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:58</t>
+          <t>2026-07-09T11:09:35</t>
         </is>
       </c>
     </row>
@@ -39784,28 +40232,30 @@
       </c>
       <c r="B626" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>275</t>
         </is>
       </c>
       <c r="C626" s="2" t="inlineStr">
         <is>
-          <t>2 Bed 2.5 Bath</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D626" s="2" t="inlineStr">
         <is>
-          <t>N &amp; W</t>
+          <t>1 Bed</t>
         </is>
       </c>
       <c r="E626" s="2" t="inlineStr">
         <is>
-          <t>Balcony</t>
-        </is>
-      </c>
-      <c r="F626" s="3" t="n">
-        <v>2400</v>
-      </c>
-      <c r="G626" s="2" t="inlineStr"/>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="F626" s="2" t="n"/>
+      <c r="G626" s="2" t="inlineStr">
+        <is>
+          <t>RESERVED</t>
+        </is>
+      </c>
       <c r="H626" s="2" t="inlineStr">
         <is>
           <t>05.07.26</t>
@@ -39818,7 +40268,7 @@
       </c>
       <c r="J626" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:58</t>
+          <t>2026-07-09T11:09:35</t>
         </is>
       </c>
     </row>
@@ -39830,26 +40280,26 @@
       </c>
       <c r="B627" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>281</t>
         </is>
       </c>
       <c r="C627" s="2" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D627" s="2" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>2 Bed 2 Bath</t>
         </is>
       </c>
       <c r="E627" s="2" t="inlineStr">
         <is>
-          <t>Balcony</t>
+          <t>S &amp; E</t>
         </is>
       </c>
       <c r="F627" s="3" t="n">
-        <v>1600</v>
+        <v>565000</v>
       </c>
       <c r="G627" s="2" t="inlineStr"/>
       <c r="H627" s="2" t="inlineStr">
@@ -39864,7 +40314,7 @@
       </c>
       <c r="J627" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:58</t>
+          <t>2026-07-09T11:09:35</t>
         </is>
       </c>
     </row>
@@ -39876,26 +40326,26 @@
       </c>
       <c r="B628" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>285</t>
         </is>
       </c>
       <c r="C628" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D628" s="2" t="inlineStr">
+        <is>
           <t>2 Bed 2.5 Bath</t>
         </is>
       </c>
-      <c r="D628" s="2" t="inlineStr">
+      <c r="E628" s="2" t="inlineStr">
         <is>
           <t>N &amp; W</t>
         </is>
       </c>
-      <c r="E628" s="2" t="inlineStr">
-        <is>
-          <t>Balcony</t>
-        </is>
-      </c>
       <c r="F628" s="3" t="n">
-        <v>2425</v>
+        <v>575000</v>
       </c>
       <c r="G628" s="2" t="inlineStr"/>
       <c r="H628" s="2" t="inlineStr">
@@ -39910,191 +40360,197 @@
       </c>
       <c r="J628" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:58</t>
+          <t>2026-07-09T11:09:35</t>
         </is>
       </c>
     </row>
     <row r="629">
       <c r="A629" s="2" t="inlineStr">
         <is>
-          <t>W12 - White City Living</t>
+          <t>UB1 - The Green Quarter</t>
         </is>
       </c>
       <c r="B629" s="2" t="inlineStr">
         <is>
-          <t>P1.01</t>
+          <t>292</t>
         </is>
       </c>
       <c r="C629" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D629" s="2" t="inlineStr">
         <is>
-          <t>2 Bed</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E629" s="2" t="inlineStr">
         <is>
-          <t>North West</t>
-        </is>
-      </c>
-      <c r="F629" s="3" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="G629" s="2" t="inlineStr"/>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="F629" s="2" t="n"/>
+      <c r="G629" s="2" t="inlineStr">
+        <is>
+          <t>RESERVED</t>
+        </is>
+      </c>
       <c r="H629" s="2" t="inlineStr">
         <is>
-          <t>02.07.26</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="I629" s="2" t="inlineStr">
         <is>
-          <t>WCL - Cascades Three price list - 02.07.26.pdf</t>
+          <t>CN-The Green Quarter - Brickfields Customer Pricelist -05.07.26.pdf</t>
         </is>
       </c>
       <c r="J629" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:16</t>
+          <t>2026-07-09T11:09:35</t>
         </is>
       </c>
     </row>
     <row r="630">
       <c r="A630" s="2" t="inlineStr">
         <is>
-          <t>W12 - White City Living</t>
+          <t>UB1 - The Green Quarter</t>
         </is>
       </c>
       <c r="B630" s="2" t="inlineStr">
         <is>
-          <t>P1.02</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C630" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D630" s="2" t="inlineStr">
         <is>
-          <t>1 Bed</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E630" s="2" t="inlineStr">
         <is>
-          <t>North East</t>
-        </is>
-      </c>
-      <c r="F630" s="3" t="n">
-        <v>745000</v>
-      </c>
-      <c r="G630" s="2" t="inlineStr"/>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="F630" s="2" t="n"/>
+      <c r="G630" s="2" t="inlineStr">
+        <is>
+          <t>ON HOLD</t>
+        </is>
+      </c>
       <c r="H630" s="2" t="inlineStr">
         <is>
-          <t>02.07.26</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="I630" s="2" t="inlineStr">
         <is>
-          <t>WCL - Cascades Three price list - 02.07.26.pdf</t>
+          <t>CN-The Green Quarter - Brickfields Customer Pricelist -05.07.26.pdf</t>
         </is>
       </c>
       <c r="J630" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:16</t>
+          <t>2026-07-09T11:09:35</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="A631" s="2" t="inlineStr">
         <is>
-          <t>W12 - White City Living</t>
+          <t>UB1 - The Green Quarter</t>
         </is>
       </c>
       <c r="B631" s="2" t="inlineStr">
         <is>
-          <t>P17.03</t>
+          <t>301</t>
         </is>
       </c>
       <c r="C631" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D631" s="2" t="inlineStr">
         <is>
-          <t>2+1 Bed</t>
+          <t>2 Bed 2.5 Bath</t>
         </is>
       </c>
       <c r="E631" s="2" t="inlineStr">
         <is>
-          <t>South West</t>
+          <t>N &amp; W</t>
         </is>
       </c>
       <c r="F631" s="3" t="n">
-        <v>1550000</v>
+        <v>585000</v>
       </c>
       <c r="G631" s="2" t="inlineStr"/>
       <c r="H631" s="2" t="inlineStr">
         <is>
-          <t>02.07.26</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="I631" s="2" t="inlineStr">
         <is>
-          <t>WCL - Cascades Three price list - 02.07.26.pdf</t>
+          <t>CN-The Green Quarter - Brickfields Customer Pricelist -05.07.26.pdf</t>
         </is>
       </c>
       <c r="J631" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:16</t>
+          <t>2026-07-09T11:09:35</t>
         </is>
       </c>
     </row>
     <row r="632">
       <c r="A632" s="2" t="inlineStr">
         <is>
-          <t>W12 - White City Living</t>
+          <t>UB1 - The Green Quarter</t>
         </is>
       </c>
       <c r="B632" s="2" t="inlineStr">
         <is>
-          <t>P18.02</t>
+          <t>304</t>
         </is>
       </c>
       <c r="C632" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D632" s="2" t="inlineStr">
         <is>
-          <t>3 Bed</t>
+          <t>1 Bed</t>
         </is>
       </c>
       <c r="E632" s="2" t="inlineStr">
         <is>
-          <t>South East</t>
-        </is>
-      </c>
-      <c r="F632" s="3" t="n">
-        <v>1720000</v>
-      </c>
-      <c r="G632" s="2" t="inlineStr"/>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="F632" s="2" t="n"/>
+      <c r="G632" s="2" t="inlineStr">
+        <is>
+          <t>RESERVED</t>
+        </is>
+      </c>
       <c r="H632" s="2" t="inlineStr">
         <is>
-          <t>02.07.26</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="I632" s="2" t="inlineStr">
         <is>
-          <t>WCL - Cascades Three price list - 02.07.26.pdf</t>
+          <t>CN-The Green Quarter - Brickfields Customer Pricelist -05.07.26.pdf</t>
         </is>
       </c>
       <c r="J632" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:16</t>
+          <t>2026-07-09T11:09:35</t>
         </is>
       </c>
     </row>
@@ -40106,17 +40562,17 @@
       </c>
       <c r="B633" s="2" t="inlineStr">
         <is>
-          <t>P4.01</t>
+          <t>P1.01</t>
         </is>
       </c>
       <c r="C633" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D633" s="2" t="inlineStr">
         <is>
-          <t>1 Bed</t>
+          <t>2 Bed</t>
         </is>
       </c>
       <c r="E633" s="2" t="inlineStr">
@@ -40125,7 +40581,7 @@
         </is>
       </c>
       <c r="F633" s="3" t="n">
-        <v>770000</v>
+        <v>1000000</v>
       </c>
       <c r="G633" s="2" t="inlineStr"/>
       <c r="H633" s="2" t="inlineStr">
@@ -40152,12 +40608,12 @@
       </c>
       <c r="B634" s="2" t="inlineStr">
         <is>
-          <t>P4.06</t>
+          <t>P1.02</t>
         </is>
       </c>
       <c r="C634" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D634" s="2" t="inlineStr">
@@ -40167,10 +40623,12 @@
       </c>
       <c r="E634" s="2" t="inlineStr">
         <is>
-          <t>North West</t>
-        </is>
-      </c>
-      <c r="F634" s="2" t="n"/>
+          <t>North East</t>
+        </is>
+      </c>
+      <c r="F634" s="3" t="n">
+        <v>745000</v>
+      </c>
       <c r="G634" s="2" t="inlineStr"/>
       <c r="H634" s="2" t="inlineStr">
         <is>
@@ -40196,26 +40654,26 @@
       </c>
       <c r="B635" s="2" t="inlineStr">
         <is>
-          <t>P5.03</t>
+          <t>P17.03</t>
         </is>
       </c>
       <c r="C635" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D635" s="2" t="inlineStr">
         <is>
-          <t>1 Bed</t>
+          <t>2+1 Bed</t>
         </is>
       </c>
       <c r="E635" s="2" t="inlineStr">
         <is>
-          <t>South East</t>
+          <t>South West</t>
         </is>
       </c>
       <c r="F635" s="3" t="n">
-        <v>785000</v>
+        <v>1550000</v>
       </c>
       <c r="G635" s="2" t="inlineStr"/>
       <c r="H635" s="2" t="inlineStr">
@@ -40242,26 +40700,26 @@
       </c>
       <c r="B636" s="2" t="inlineStr">
         <is>
-          <t>P6.06</t>
+          <t>P18.02</t>
         </is>
       </c>
       <c r="C636" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D636" s="2" t="inlineStr">
         <is>
-          <t>1 Bed</t>
+          <t>3 Bed</t>
         </is>
       </c>
       <c r="E636" s="2" t="inlineStr">
         <is>
-          <t>North West</t>
+          <t>South East</t>
         </is>
       </c>
       <c r="F636" s="3" t="n">
-        <v>785000</v>
+        <v>1720000</v>
       </c>
       <c r="G636" s="2" t="inlineStr"/>
       <c r="H636" s="2" t="inlineStr">
@@ -40288,25 +40746,27 @@
       </c>
       <c r="B637" s="2" t="inlineStr">
         <is>
-          <t>P8.03</t>
+          <t>P4.01</t>
         </is>
       </c>
       <c r="C637" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D637" s="2" t="inlineStr">
         <is>
-          <t>2 Bed</t>
+          <t>1 Bed</t>
         </is>
       </c>
       <c r="E637" s="2" t="inlineStr">
         <is>
-          <t>South West</t>
-        </is>
-      </c>
-      <c r="F637" s="2" t="n"/>
+          <t>North West</t>
+        </is>
+      </c>
+      <c r="F637" s="3" t="n">
+        <v>770000</v>
+      </c>
       <c r="G637" s="2" t="inlineStr"/>
       <c r="H637" s="2" t="inlineStr">
         <is>
@@ -40332,17 +40792,17 @@
       </c>
       <c r="B638" s="2" t="inlineStr">
         <is>
-          <t>P8.04</t>
+          <t>P4.06</t>
         </is>
       </c>
       <c r="C638" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D638" s="2" t="inlineStr">
         <is>
-          <t>2 Bed</t>
+          <t>1 Bed</t>
         </is>
       </c>
       <c r="E638" s="2" t="inlineStr">
@@ -40350,9 +40810,7 @@
           <t>North West</t>
         </is>
       </c>
-      <c r="F638" s="3" t="n">
-        <v>1100000</v>
-      </c>
+      <c r="F638" s="2" t="n"/>
       <c r="G638" s="2" t="inlineStr"/>
       <c r="H638" s="2" t="inlineStr">
         <is>
@@ -40378,26 +40836,26 @@
       </c>
       <c r="B639" s="2" t="inlineStr">
         <is>
-          <t>P9.01</t>
+          <t>P5.03</t>
         </is>
       </c>
       <c r="C639" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D639" s="2" t="inlineStr">
         <is>
-          <t>2 Bed</t>
+          <t>1 Bed</t>
         </is>
       </c>
       <c r="E639" s="2" t="inlineStr">
         <is>
-          <t>North East</t>
+          <t>South East</t>
         </is>
       </c>
       <c r="F639" s="3" t="n">
-        <v>1160000</v>
+        <v>785000</v>
       </c>
       <c r="G639" s="2" t="inlineStr"/>
       <c r="H639" s="2" t="inlineStr">
@@ -40424,26 +40882,26 @@
       </c>
       <c r="B640" s="2" t="inlineStr">
         <is>
-          <t>V10.02</t>
+          <t>P6.06</t>
         </is>
       </c>
       <c r="C640" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D640" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 Bed</t>
         </is>
       </c>
       <c r="E640" s="2" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>North West</t>
         </is>
       </c>
       <c r="F640" s="3" t="n">
-        <v>762500</v>
+        <v>785000</v>
       </c>
       <c r="G640" s="2" t="inlineStr"/>
       <c r="H640" s="2" t="inlineStr">
@@ -40453,12 +40911,12 @@
       </c>
       <c r="I640" s="2" t="inlineStr">
         <is>
-          <t>WCL-Ready to Move In- Solaris One 02.07.26.pdf</t>
+          <t>WCL - Cascades Three price list - 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J640" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:53:11</t>
+          <t>2026-07-08T17:01:16</t>
         </is>
       </c>
     </row>
@@ -40470,27 +40928,25 @@
       </c>
       <c r="B641" s="2" t="inlineStr">
         <is>
-          <t>V11.01</t>
+          <t>P8.03</t>
         </is>
       </c>
       <c r="C641" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D641" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2 Bed</t>
         </is>
       </c>
       <c r="E641" s="2" t="inlineStr">
         <is>
-          <t>South/East/North</t>
-        </is>
-      </c>
-      <c r="F641" s="3" t="n">
-        <v>1800000</v>
-      </c>
+          <t>South West</t>
+        </is>
+      </c>
+      <c r="F641" s="2" t="n"/>
       <c r="G641" s="2" t="inlineStr"/>
       <c r="H641" s="2" t="inlineStr">
         <is>
@@ -40499,12 +40955,12 @@
       </c>
       <c r="I641" s="2" t="inlineStr">
         <is>
-          <t>WCL-Ready to Move In- Solaris One 02.07.26.pdf</t>
+          <t>WCL - Cascades Three price list - 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J641" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:53:11</t>
+          <t>2026-07-08T17:01:16</t>
         </is>
       </c>
     </row>
@@ -40516,26 +40972,26 @@
       </c>
       <c r="B642" s="2" t="inlineStr">
         <is>
-          <t>V12.01</t>
+          <t>P8.04</t>
         </is>
       </c>
       <c r="C642" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D642" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2 Bed</t>
         </is>
       </c>
       <c r="E642" s="2" t="inlineStr">
         <is>
-          <t>Sout/East/North</t>
+          <t>North West</t>
         </is>
       </c>
       <c r="F642" s="3" t="n">
-        <v>2080000</v>
+        <v>1100000</v>
       </c>
       <c r="G642" s="2" t="inlineStr"/>
       <c r="H642" s="2" t="inlineStr">
@@ -40545,12 +41001,12 @@
       </c>
       <c r="I642" s="2" t="inlineStr">
         <is>
-          <t>WCL-Ready to Move In- Solaris One 02.07.26.pdf</t>
+          <t>WCL - Cascades Three price list - 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J642" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:53:11</t>
+          <t>2026-07-08T17:01:16</t>
         </is>
       </c>
     </row>
@@ -40562,26 +41018,26 @@
       </c>
       <c r="B643" s="2" t="inlineStr">
         <is>
-          <t>V15.02</t>
+          <t>P9.01</t>
         </is>
       </c>
       <c r="C643" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D643" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2 Bed</t>
         </is>
       </c>
       <c r="E643" s="2" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>North East</t>
         </is>
       </c>
       <c r="F643" s="3" t="n">
-        <v>785000</v>
+        <v>1160000</v>
       </c>
       <c r="G643" s="2" t="inlineStr"/>
       <c r="H643" s="2" t="inlineStr">
@@ -40591,12 +41047,12 @@
       </c>
       <c r="I643" s="2" t="inlineStr">
         <is>
-          <t>WCL-Ready to Move In- Solaris One 02.07.26.pdf</t>
+          <t>WCL - Cascades Three price list - 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J643" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:53:11</t>
+          <t>2026-07-08T17:01:16</t>
         </is>
       </c>
     </row>
@@ -40608,12 +41064,12 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>V16.02</t>
+          <t>V10.02</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D644" s="2" t="inlineStr">
@@ -40627,7 +41083,7 @@
         </is>
       </c>
       <c r="F644" s="3" t="n">
-        <v>787500</v>
+        <v>762500</v>
       </c>
       <c r="G644" s="2" t="inlineStr"/>
       <c r="H644" s="2" t="inlineStr">
@@ -40654,26 +41110,26 @@
       </c>
       <c r="B645" s="2" t="inlineStr">
         <is>
-          <t>V18.02</t>
+          <t>V11.01</t>
         </is>
       </c>
       <c r="C645" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D645" s="2" t="inlineStr">
         <is>
-          <t>3+Study</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E645" s="2" t="inlineStr">
         <is>
-          <t>South/West/North</t>
+          <t>South/East/North</t>
         </is>
       </c>
       <c r="F645" s="3" t="n">
-        <v>2815000</v>
+        <v>1800000</v>
       </c>
       <c r="G645" s="2" t="inlineStr"/>
       <c r="H645" s="2" t="inlineStr">
@@ -40700,26 +41156,26 @@
       </c>
       <c r="B646" s="2" t="inlineStr">
         <is>
-          <t>V19.01</t>
+          <t>V12.01</t>
         </is>
       </c>
       <c r="C646" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D646" s="2" t="inlineStr">
         <is>
-          <t>3+Study</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E646" s="2" t="inlineStr">
         <is>
-          <t>South/East/North</t>
+          <t>Sout/East/North</t>
         </is>
       </c>
       <c r="F646" s="3" t="n">
-        <v>2945000</v>
+        <v>2080000</v>
       </c>
       <c r="G646" s="2" t="inlineStr"/>
       <c r="H646" s="2" t="inlineStr">
@@ -40746,26 +41202,26 @@
       </c>
       <c r="B647" s="2" t="inlineStr">
         <is>
-          <t>V4.06</t>
+          <t>V15.02</t>
         </is>
       </c>
       <c r="C647" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D647" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E647" s="2" t="inlineStr">
         <is>
-          <t>South/West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="F647" s="3" t="n">
-        <v>1065000</v>
+        <v>785000</v>
       </c>
       <c r="G647" s="2" t="inlineStr"/>
       <c r="H647" s="2" t="inlineStr">
@@ -40792,12 +41248,12 @@
       </c>
       <c r="B648" s="2" t="inlineStr">
         <is>
-          <t>V5.02</t>
+          <t>V16.02</t>
         </is>
       </c>
       <c r="C648" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D648" s="2" t="inlineStr">
@@ -40810,7 +41266,9 @@
           <t>East</t>
         </is>
       </c>
-      <c r="F648" s="2" t="n"/>
+      <c r="F648" s="3" t="n">
+        <v>787500</v>
+      </c>
       <c r="G648" s="2" t="inlineStr"/>
       <c r="H648" s="2" t="inlineStr">
         <is>
@@ -40836,25 +41294,27 @@
       </c>
       <c r="B649" s="2" t="inlineStr">
         <is>
-          <t>V6.01</t>
+          <t>V18.02</t>
         </is>
       </c>
       <c r="C649" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D649" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3+Study</t>
         </is>
       </c>
       <c r="E649" s="2" t="inlineStr">
         <is>
-          <t>West</t>
-        </is>
-      </c>
-      <c r="F649" s="2" t="n"/>
+          <t>South/West/North</t>
+        </is>
+      </c>
+      <c r="F649" s="3" t="n">
+        <v>2815000</v>
+      </c>
       <c r="G649" s="2" t="inlineStr"/>
       <c r="H649" s="2" t="inlineStr">
         <is>
@@ -40880,26 +41340,26 @@
       </c>
       <c r="B650" s="2" t="inlineStr">
         <is>
-          <t>V6.02</t>
+          <t>V19.01</t>
         </is>
       </c>
       <c r="C650" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D650" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3+Study</t>
         </is>
       </c>
       <c r="E650" s="2" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>South/East/North</t>
         </is>
       </c>
       <c r="F650" s="3" t="n">
-        <v>752500</v>
+        <v>2945000</v>
       </c>
       <c r="G650" s="2" t="inlineStr"/>
       <c r="H650" s="2" t="inlineStr">
@@ -40926,25 +41386,27 @@
       </c>
       <c r="B651" s="2" t="inlineStr">
         <is>
-          <t>V7.01</t>
+          <t>V4.06</t>
         </is>
       </c>
       <c r="C651" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D651" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E651" s="2" t="inlineStr">
         <is>
-          <t>West</t>
-        </is>
-      </c>
-      <c r="F651" s="2" t="n"/>
+          <t>South/West</t>
+        </is>
+      </c>
+      <c r="F651" s="3" t="n">
+        <v>1065000</v>
+      </c>
       <c r="G651" s="2" t="inlineStr"/>
       <c r="H651" s="2" t="inlineStr">
         <is>
@@ -40970,12 +41432,12 @@
       </c>
       <c r="B652" s="2" t="inlineStr">
         <is>
-          <t>V7.02</t>
+          <t>V5.02</t>
         </is>
       </c>
       <c r="C652" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D652" s="2" t="inlineStr">
@@ -40988,9 +41450,7 @@
           <t>East</t>
         </is>
       </c>
-      <c r="F652" s="3" t="n">
-        <v>755000</v>
-      </c>
+      <c r="F652" s="2" t="n"/>
       <c r="G652" s="2" t="inlineStr"/>
       <c r="H652" s="2" t="inlineStr">
         <is>
@@ -41016,12 +41476,12 @@
       </c>
       <c r="B653" s="2" t="inlineStr">
         <is>
-          <t>V9.02</t>
+          <t>V6.01</t>
         </is>
       </c>
       <c r="C653" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D653" s="2" t="inlineStr">
@@ -41031,12 +41491,10 @@
       </c>
       <c r="E653" s="2" t="inlineStr">
         <is>
-          <t>East</t>
-        </is>
-      </c>
-      <c r="F653" s="3" t="n">
-        <v>760000</v>
-      </c>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="F653" s="2" t="n"/>
       <c r="G653" s="2" t="inlineStr"/>
       <c r="H653" s="2" t="inlineStr">
         <is>
@@ -41062,12 +41520,12 @@
       </c>
       <c r="B654" s="2" t="inlineStr">
         <is>
-          <t>W.09.01</t>
+          <t>V6.02</t>
         </is>
       </c>
       <c r="C654" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D654" s="2" t="inlineStr">
@@ -41077,10 +41535,12 @@
       </c>
       <c r="E654" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
-        </is>
-      </c>
-      <c r="F654" s="2" t="n"/>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="F654" s="3" t="n">
+        <v>752500</v>
+      </c>
       <c r="G654" s="2" t="inlineStr"/>
       <c r="H654" s="2" t="inlineStr">
         <is>
@@ -41089,12 +41549,12 @@
       </c>
       <c r="I654" s="2" t="inlineStr">
         <is>
-          <t>WCL - Solaris Two 02.07.26.pdf</t>
+          <t>WCL-Ready to Move In- Solaris One 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J654" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-09T09:53:11</t>
         </is>
       </c>
     </row>
@@ -41106,12 +41566,12 @@
       </c>
       <c r="B655" s="2" t="inlineStr">
         <is>
-          <t>W.09.04</t>
+          <t>V7.01</t>
         </is>
       </c>
       <c r="C655" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D655" s="2" t="inlineStr">
@@ -41121,12 +41581,10 @@
       </c>
       <c r="E655" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
-        </is>
-      </c>
-      <c r="F655" s="3" t="n">
-        <v>762500</v>
-      </c>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="F655" s="2" t="n"/>
       <c r="G655" s="2" t="inlineStr"/>
       <c r="H655" s="2" t="inlineStr">
         <is>
@@ -41135,12 +41593,12 @@
       </c>
       <c r="I655" s="2" t="inlineStr">
         <is>
-          <t>WCL - Solaris Two 02.07.26.pdf</t>
+          <t>WCL-Ready to Move In- Solaris One 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J655" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-09T09:53:11</t>
         </is>
       </c>
     </row>
@@ -41152,26 +41610,26 @@
       </c>
       <c r="B656" s="2" t="inlineStr">
         <is>
-          <t>W.10.02</t>
+          <t>V7.02</t>
         </is>
       </c>
       <c r="C656" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D656" s="2" t="inlineStr">
         <is>
-          <t>3+Study</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E656" s="2" t="inlineStr">
         <is>
-          <t>North/East</t>
+          <t>East</t>
         </is>
       </c>
       <c r="F656" s="3" t="n">
-        <v>2000000</v>
+        <v>755000</v>
       </c>
       <c r="G656" s="2" t="inlineStr"/>
       <c r="H656" s="2" t="inlineStr">
@@ -41181,12 +41639,12 @@
       </c>
       <c r="I656" s="2" t="inlineStr">
         <is>
-          <t>WCL - Solaris Two 02.07.26.pdf</t>
+          <t>WCL-Ready to Move In- Solaris One 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J656" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-09T09:53:11</t>
         </is>
       </c>
     </row>
@@ -41198,25 +41656,27 @@
       </c>
       <c r="B657" s="2" t="inlineStr">
         <is>
-          <t>W.13.04</t>
+          <t>V9.02</t>
         </is>
       </c>
       <c r="C657" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D657" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E657" s="2" t="inlineStr">
         <is>
-          <t>South/East</t>
-        </is>
-      </c>
-      <c r="F657" s="2" t="n"/>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="F657" s="3" t="n">
+        <v>760000</v>
+      </c>
       <c r="G657" s="2" t="inlineStr"/>
       <c r="H657" s="2" t="inlineStr">
         <is>
@@ -41225,12 +41685,12 @@
       </c>
       <c r="I657" s="2" t="inlineStr">
         <is>
-          <t>WCL - Solaris Two 02.07.26.pdf</t>
+          <t>WCL-Ready to Move In- Solaris One 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J657" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-09T09:53:11</t>
         </is>
       </c>
     </row>
@@ -41242,12 +41702,12 @@
       </c>
       <c r="B658" s="2" t="inlineStr">
         <is>
-          <t>W.14.03</t>
+          <t>W.09.01</t>
         </is>
       </c>
       <c r="C658" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D658" s="2" t="inlineStr">
@@ -41257,12 +41717,10 @@
       </c>
       <c r="E658" s="2" t="inlineStr">
         <is>
-          <t>North/East</t>
-        </is>
-      </c>
-      <c r="F658" s="3" t="n">
-        <v>775000</v>
-      </c>
+          <t>North/West</t>
+        </is>
+      </c>
+      <c r="F658" s="2" t="n"/>
       <c r="G658" s="2" t="inlineStr"/>
       <c r="H658" s="2" t="inlineStr">
         <is>
@@ -41288,26 +41746,26 @@
       </c>
       <c r="B659" s="2" t="inlineStr">
         <is>
-          <t>W.14.04</t>
+          <t>W.09.04</t>
         </is>
       </c>
       <c r="C659" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D659" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E659" s="2" t="inlineStr">
         <is>
-          <t>South/East</t>
+          <t>North/West</t>
         </is>
       </c>
       <c r="F659" s="3" t="n">
-        <v>1005000</v>
+        <v>762500</v>
       </c>
       <c r="G659" s="2" t="inlineStr"/>
       <c r="H659" s="2" t="inlineStr">
@@ -41334,17 +41792,17 @@
       </c>
       <c r="B660" s="2" t="inlineStr">
         <is>
-          <t>W.17.02</t>
+          <t>W.10.02</t>
         </is>
       </c>
       <c r="C660" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D660" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3+Study</t>
         </is>
       </c>
       <c r="E660" s="2" t="inlineStr">
@@ -41352,7 +41810,9 @@
           <t>North/East</t>
         </is>
       </c>
-      <c r="F660" s="2" t="n"/>
+      <c r="F660" s="3" t="n">
+        <v>2000000</v>
+      </c>
       <c r="G660" s="2" t="inlineStr"/>
       <c r="H660" s="2" t="inlineStr">
         <is>
@@ -41378,12 +41838,12 @@
       </c>
       <c r="B661" s="2" t="inlineStr">
         <is>
-          <t>W.17.03</t>
+          <t>W.13.04</t>
         </is>
       </c>
       <c r="C661" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D661" s="2" t="inlineStr">
@@ -41396,9 +41856,7 @@
           <t>South/East</t>
         </is>
       </c>
-      <c r="F661" s="3" t="n">
-        <v>1020000</v>
-      </c>
+      <c r="F661" s="2" t="n"/>
       <c r="G661" s="2" t="inlineStr"/>
       <c r="H661" s="2" t="inlineStr">
         <is>
@@ -41424,26 +41882,26 @@
       </c>
       <c r="B662" s="2" t="inlineStr">
         <is>
-          <t>W.18.03</t>
+          <t>W.14.03</t>
         </is>
       </c>
       <c r="C662" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D662" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E662" s="2" t="inlineStr">
         <is>
-          <t>South/East</t>
+          <t>North/East</t>
         </is>
       </c>
       <c r="F662" s="3" t="n">
-        <v>1025000</v>
+        <v>775000</v>
       </c>
       <c r="G662" s="2" t="inlineStr"/>
       <c r="H662" s="2" t="inlineStr">
@@ -41470,12 +41928,12 @@
       </c>
       <c r="B663" s="2" t="inlineStr">
         <is>
-          <t>W.20.04</t>
+          <t>W.14.04</t>
         </is>
       </c>
       <c r="C663" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D663" s="2" t="inlineStr">
@@ -41488,7 +41946,9 @@
           <t>South/East</t>
         </is>
       </c>
-      <c r="F663" s="2" t="n"/>
+      <c r="F663" s="3" t="n">
+        <v>1005000</v>
+      </c>
       <c r="G663" s="2" t="inlineStr"/>
       <c r="H663" s="2" t="inlineStr">
         <is>
@@ -41514,12 +41974,12 @@
       </c>
       <c r="B664" s="2" t="inlineStr">
         <is>
-          <t>W.21.03</t>
+          <t>W.17.02</t>
         </is>
       </c>
       <c r="C664" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D664" s="2" t="inlineStr">
@@ -41529,12 +41989,10 @@
       </c>
       <c r="E664" s="2" t="inlineStr">
         <is>
-          <t>South/East</t>
-        </is>
-      </c>
-      <c r="F664" s="3" t="n">
-        <v>1040000</v>
-      </c>
+          <t>North/East</t>
+        </is>
+      </c>
+      <c r="F664" s="2" t="n"/>
       <c r="G664" s="2" t="inlineStr"/>
       <c r="H664" s="2" t="inlineStr">
         <is>
@@ -41560,26 +42018,26 @@
       </c>
       <c r="B665" s="2" t="inlineStr">
         <is>
-          <t>W.27.01</t>
+          <t>W.17.03</t>
         </is>
       </c>
       <c r="C665" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D665" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E665" s="2" t="inlineStr">
         <is>
-          <t>South/East/North</t>
+          <t>South/East</t>
         </is>
       </c>
       <c r="F665" s="3" t="n">
-        <v>2550000</v>
+        <v>1020000</v>
       </c>
       <c r="G665" s="2" t="inlineStr"/>
       <c r="H665" s="2" t="inlineStr">
@@ -41606,26 +42064,26 @@
       </c>
       <c r="B666" s="2" t="inlineStr">
         <is>
-          <t>W.27.02</t>
+          <t>W.18.03</t>
         </is>
       </c>
       <c r="C666" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D666" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E666" s="2" t="inlineStr">
         <is>
-          <t>South/West/North</t>
+          <t>South/East</t>
         </is>
       </c>
       <c r="F666" s="3" t="n">
-        <v>2550000</v>
+        <v>1025000</v>
       </c>
       <c r="G666" s="2" t="inlineStr"/>
       <c r="H666" s="2" t="inlineStr">
@@ -41652,27 +42110,25 @@
       </c>
       <c r="B667" s="2" t="inlineStr">
         <is>
-          <t>W.30.01</t>
+          <t>W.20.04</t>
         </is>
       </c>
       <c r="C667" s="2" t="inlineStr">
         <is>
-          <t>30/31</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D667" s="2" t="inlineStr">
         <is>
-          <t>Penthouse</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E667" s="2" t="inlineStr">
         <is>
-          <t>South/West/North</t>
-        </is>
-      </c>
-      <c r="F667" s="3" t="n">
-        <v>3990000</v>
-      </c>
+          <t>South/East</t>
+        </is>
+      </c>
+      <c r="F667" s="2" t="n"/>
       <c r="G667" s="2" t="inlineStr"/>
       <c r="H667" s="2" t="inlineStr">
         <is>
@@ -41698,26 +42154,26 @@
       </c>
       <c r="B668" s="2" t="inlineStr">
         <is>
-          <t>W.30.02</t>
+          <t>W.21.03</t>
         </is>
       </c>
       <c r="C668" s="2" t="inlineStr">
         <is>
-          <t>30/31</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D668" s="2" t="inlineStr">
         <is>
-          <t>Penthouse</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E668" s="2" t="inlineStr">
         <is>
-          <t>South/East/North</t>
+          <t>South/East</t>
         </is>
       </c>
       <c r="F668" s="3" t="n">
-        <v>3990000</v>
+        <v>1040000</v>
       </c>
       <c r="G668" s="2" t="inlineStr"/>
       <c r="H668" s="2" t="inlineStr">
@@ -41739,178 +42195,184 @@
     <row r="669">
       <c r="A669" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B669" s="2" t="inlineStr">
         <is>
-          <t>I.01.07</t>
+          <t>W.27.01</t>
         </is>
       </c>
       <c r="C669" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D669" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E669" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
-        </is>
-      </c>
-      <c r="F669" s="2" t="n"/>
+          <t>South/East/North</t>
+        </is>
+      </c>
+      <c r="F669" s="3" t="n">
+        <v>2550000</v>
+      </c>
       <c r="G669" s="2" t="inlineStr"/>
       <c r="H669" s="2" t="inlineStr">
         <is>
-          <t>01.07.26</t>
+          <t>02.07.26</t>
         </is>
       </c>
       <c r="I669" s="2" t="inlineStr">
         <is>
-          <t>Trillium Price List 01.07.26.pdf</t>
+          <t>WCL - Solaris Two 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J669" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:32</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
     </row>
     <row r="670">
       <c r="A670" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B670" s="2" t="inlineStr">
         <is>
-          <t>I.08.05</t>
+          <t>W.27.02</t>
         </is>
       </c>
       <c r="C670" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D670" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E670" s="2" t="inlineStr">
         <is>
-          <t>South/West</t>
-        </is>
-      </c>
-      <c r="F670" s="2" t="n"/>
+          <t>South/West/North</t>
+        </is>
+      </c>
+      <c r="F670" s="3" t="n">
+        <v>2550000</v>
+      </c>
       <c r="G670" s="2" t="inlineStr"/>
       <c r="H670" s="2" t="inlineStr">
         <is>
-          <t>01.07.26</t>
+          <t>02.07.26</t>
         </is>
       </c>
       <c r="I670" s="2" t="inlineStr">
         <is>
-          <t>Trillium Price List 01.07.26.pdf</t>
+          <t>WCL - Solaris Two 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J670" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:32</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
     </row>
     <row r="671">
       <c r="A671" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B671" s="2" t="inlineStr">
         <is>
-          <t>I.10.06</t>
+          <t>W.30.01</t>
         </is>
       </c>
       <c r="C671" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30/31</t>
         </is>
       </c>
       <c r="D671" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Penthouse</t>
         </is>
       </c>
       <c r="E671" s="2" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>South/West/North</t>
         </is>
       </c>
       <c r="F671" s="3" t="n">
-        <v>1016000</v>
+        <v>3990000</v>
       </c>
       <c r="G671" s="2" t="inlineStr"/>
       <c r="H671" s="2" t="inlineStr">
         <is>
-          <t>01.07.26</t>
+          <t>02.07.26</t>
         </is>
       </c>
       <c r="I671" s="2" t="inlineStr">
         <is>
-          <t>Trillium Price List 01.07.26.pdf</t>
+          <t>WCL - Solaris Two 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J671" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:32</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
     </row>
     <row r="672">
       <c r="A672" s="2" t="inlineStr">
         <is>
-          <t>W2 - Trillium</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B672" s="2" t="inlineStr">
         <is>
-          <t>I.10.07</t>
+          <t>W.30.02</t>
         </is>
       </c>
       <c r="C672" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30/31</t>
         </is>
       </c>
       <c r="D672" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>Penthouse</t>
         </is>
       </c>
       <c r="E672" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
-        </is>
-      </c>
-      <c r="F672" s="2" t="n"/>
+          <t>South/East/North</t>
+        </is>
+      </c>
+      <c r="F672" s="3" t="n">
+        <v>3990000</v>
+      </c>
       <c r="G672" s="2" t="inlineStr"/>
       <c r="H672" s="2" t="inlineStr">
         <is>
-          <t>01.07.26</t>
+          <t>02.07.26</t>
         </is>
       </c>
       <c r="I672" s="2" t="inlineStr">
         <is>
-          <t>Trillium Price List 01.07.26.pdf</t>
+          <t>WCL - Solaris Two 02.07.26.pdf</t>
         </is>
       </c>
       <c r="J672" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:56:32</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
     </row>
@@ -41922,27 +42384,25 @@
       </c>
       <c r="B673" s="2" t="inlineStr">
         <is>
-          <t>I.14.01</t>
+          <t>I.01.07</t>
         </is>
       </c>
       <c r="C673" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D673" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E673" s="2" t="inlineStr">
         <is>
-          <t>North/East</t>
-        </is>
-      </c>
-      <c r="F673" s="3" t="n">
-        <v>1598500</v>
-      </c>
+          <t>North/West</t>
+        </is>
+      </c>
+      <c r="F673" s="2" t="n"/>
       <c r="G673" s="2" t="inlineStr"/>
       <c r="H673" s="2" t="inlineStr">
         <is>
@@ -41968,22 +42428,22 @@
       </c>
       <c r="B674" s="2" t="inlineStr">
         <is>
-          <t>I.14.06</t>
+          <t>I.08.05</t>
         </is>
       </c>
       <c r="C674" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D674" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E674" s="2" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>South/West</t>
         </is>
       </c>
       <c r="F674" s="2" t="n"/>
@@ -42012,26 +42472,26 @@
       </c>
       <c r="B675" s="2" t="inlineStr">
         <is>
-          <t>I.15.01</t>
+          <t>I.10.06</t>
         </is>
       </c>
       <c r="C675" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D675" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E675" s="2" t="inlineStr">
         <is>
-          <t>North/East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="F675" s="3" t="n">
-        <v>1613500</v>
+        <v>1016000</v>
       </c>
       <c r="G675" s="2" t="inlineStr"/>
       <c r="H675" s="2" t="inlineStr">
@@ -42058,22 +42518,22 @@
       </c>
       <c r="B676" s="2" t="inlineStr">
         <is>
-          <t>I.16.05</t>
+          <t>I.10.07</t>
         </is>
       </c>
       <c r="C676" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D676" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E676" s="2" t="inlineStr">
         <is>
-          <t>South/West</t>
+          <t>North/West</t>
         </is>
       </c>
       <c r="F676" s="2" t="n"/>
@@ -42102,12 +42562,12 @@
       </c>
       <c r="B677" s="2" t="inlineStr">
         <is>
-          <t>I.17.01</t>
+          <t>I.14.01</t>
         </is>
       </c>
       <c r="C677" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D677" s="2" t="inlineStr">
@@ -42117,11 +42577,11 @@
       </c>
       <c r="E677" s="2" t="inlineStr">
         <is>
-          <t>North /East</t>
+          <t>North/East</t>
         </is>
       </c>
       <c r="F677" s="3" t="n">
-        <v>1680500</v>
+        <v>1598500</v>
       </c>
       <c r="G677" s="2" t="inlineStr"/>
       <c r="H677" s="2" t="inlineStr">
@@ -42148,22 +42608,22 @@
       </c>
       <c r="B678" s="2" t="inlineStr">
         <is>
-          <t>I.17.03</t>
+          <t>I.14.06</t>
         </is>
       </c>
       <c r="C678" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D678" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E678" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>West</t>
         </is>
       </c>
       <c r="F678" s="2" t="n"/>
@@ -42192,26 +42652,26 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>I.17.05</t>
+          <t>I.15.01</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D679" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E679" s="2" t="inlineStr">
         <is>
-          <t>South/West</t>
+          <t>North/East</t>
         </is>
       </c>
       <c r="F679" s="3" t="n">
-        <v>2474500</v>
+        <v>1613500</v>
       </c>
       <c r="G679" s="2" t="inlineStr"/>
       <c r="H679" s="2" t="inlineStr">
@@ -42238,22 +42698,22 @@
       </c>
       <c r="B680" s="2" t="inlineStr">
         <is>
-          <t>I.18.02</t>
+          <t>I.16.05</t>
         </is>
       </c>
       <c r="C680" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D680" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>K</t>
         </is>
       </c>
       <c r="E680" s="2" t="inlineStr">
         <is>
-          <t>South/East</t>
+          <t>South/West</t>
         </is>
       </c>
       <c r="F680" s="2" t="n"/>
@@ -42282,25 +42742,27 @@
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>I.18.05</t>
+          <t>I.17.01</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D681" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E681" s="2" t="inlineStr">
         <is>
-          <t>South/West</t>
-        </is>
-      </c>
-      <c r="F681" s="2" t="n"/>
+          <t>North /East</t>
+        </is>
+      </c>
+      <c r="F681" s="3" t="n">
+        <v>1680500</v>
+      </c>
       <c r="G681" s="2" t="inlineStr"/>
       <c r="H681" s="2" t="inlineStr">
         <is>
@@ -42326,12 +42788,12 @@
       </c>
       <c r="B682" s="2" t="inlineStr">
         <is>
-          <t>I.19.03</t>
+          <t>I.17.03</t>
         </is>
       </c>
       <c r="C682" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D682" s="2" t="inlineStr">
@@ -42344,9 +42806,7 @@
           <t>South</t>
         </is>
       </c>
-      <c r="F682" s="3" t="n">
-        <v>1238000</v>
-      </c>
+      <c r="F682" s="2" t="n"/>
       <c r="G682" s="2" t="inlineStr"/>
       <c r="H682" s="2" t="inlineStr">
         <is>
@@ -42372,26 +42832,26 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>I.20.06</t>
+          <t>I.17.05</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D683" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>K</t>
         </is>
       </c>
       <c r="E683" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
+          <t>South/West</t>
         </is>
       </c>
       <c r="F683" s="3" t="n">
-        <v>2505000</v>
+        <v>2474500</v>
       </c>
       <c r="G683" s="2" t="inlineStr"/>
       <c r="H683" s="2" t="inlineStr">
@@ -42418,27 +42878,25 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>I.21.03</t>
+          <t>I.18.02</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D684" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E684" s="2" t="inlineStr">
         <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="F684" s="3" t="n">
-        <v>1288500</v>
-      </c>
+          <t>South/East</t>
+        </is>
+      </c>
+      <c r="F684" s="2" t="n"/>
       <c r="G684" s="2" t="inlineStr"/>
       <c r="H684" s="2" t="inlineStr">
         <is>
@@ -42459,184 +42917,182 @@
     <row r="685">
       <c r="A685" s="2" t="inlineStr">
         <is>
-          <t>W6 - Fulham Reach</t>
+          <t>W2 - Trillium</t>
         </is>
       </c>
       <c r="B685" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>I.18.05</t>
         </is>
       </c>
       <c r="C685" s="2" t="inlineStr">
         <is>
-          <t>GF</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D685" s="2" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>K</t>
         </is>
       </c>
       <c r="E685" s="2" t="inlineStr">
         <is>
-          <t>N,W</t>
-        </is>
-      </c>
-      <c r="F685" s="3" t="n">
-        <v>597000</v>
-      </c>
+          <t>South/West</t>
+        </is>
+      </c>
+      <c r="F685" s="2" t="n"/>
       <c r="G685" s="2" t="inlineStr"/>
       <c r="H685" s="2" t="inlineStr">
         <is>
-          <t>05.07.26</t>
+          <t>01.07.26</t>
         </is>
       </c>
       <c r="I685" s="2" t="inlineStr">
         <is>
-          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
+          <t>Trillium Price List 01.07.26.pdf</t>
         </is>
       </c>
       <c r="J685" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:57:26</t>
+          <t>2026-07-08T16:56:32</t>
         </is>
       </c>
     </row>
     <row r="686">
       <c r="A686" s="2" t="inlineStr">
         <is>
-          <t>W6 - Fulham Reach</t>
+          <t>W2 - Trillium</t>
         </is>
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>I.19.03</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
         <is>
-          <t>GF</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D686" s="2" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E686" s="2" t="inlineStr">
         <is>
-          <t>N,W</t>
+          <t>South</t>
         </is>
       </c>
       <c r="F686" s="3" t="n">
-        <v>598000</v>
+        <v>1238000</v>
       </c>
       <c r="G686" s="2" t="inlineStr"/>
       <c r="H686" s="2" t="inlineStr">
         <is>
-          <t>05.07.26</t>
+          <t>01.07.26</t>
         </is>
       </c>
       <c r="I686" s="2" t="inlineStr">
         <is>
-          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
+          <t>Trillium Price List 01.07.26.pdf</t>
         </is>
       </c>
       <c r="J686" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:57:26</t>
+          <t>2026-07-08T16:56:32</t>
         </is>
       </c>
     </row>
     <row r="687">
       <c r="A687" s="2" t="inlineStr">
         <is>
-          <t>W6 - Fulham Reach</t>
+          <t>W2 - Trillium</t>
         </is>
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>I.20.06</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D687" s="2" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E687" s="2" t="inlineStr">
         <is>
-          <t>N,W</t>
+          <t>North/West</t>
         </is>
       </c>
       <c r="F687" s="3" t="n">
-        <v>584000</v>
+        <v>2505000</v>
       </c>
       <c r="G687" s="2" t="inlineStr"/>
       <c r="H687" s="2" t="inlineStr">
         <is>
-          <t>05.07.26</t>
+          <t>01.07.26</t>
         </is>
       </c>
       <c r="I687" s="2" t="inlineStr">
         <is>
-          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
+          <t>Trillium Price List 01.07.26.pdf</t>
         </is>
       </c>
       <c r="J687" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:57:26</t>
+          <t>2026-07-08T16:56:32</t>
         </is>
       </c>
     </row>
     <row r="688">
       <c r="A688" s="2" t="inlineStr">
         <is>
-          <t>W6 - Fulham Reach</t>
+          <t>W2 - Trillium</t>
         </is>
       </c>
       <c r="B688" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>I.21.03</t>
         </is>
       </c>
       <c r="C688" s="2" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D688" s="2" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E688" s="2" t="inlineStr">
         <is>
-          <t>N,W</t>
+          <t>South</t>
         </is>
       </c>
       <c r="F688" s="3" t="n">
-        <v>604500</v>
+        <v>1288500</v>
       </c>
       <c r="G688" s="2" t="inlineStr"/>
       <c r="H688" s="2" t="inlineStr">
         <is>
-          <t>05.07.26</t>
+          <t>01.07.26</t>
         </is>
       </c>
       <c r="I688" s="2" t="inlineStr">
         <is>
-          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
+          <t>Trillium Price List 01.07.26.pdf</t>
         </is>
       </c>
       <c r="J688" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:57:26</t>
+          <t>2026-07-08T16:56:32</t>
         </is>
       </c>
     </row>
@@ -42648,12 +43104,12 @@
       </c>
       <c r="B689" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>658</t>
         </is>
       </c>
       <c r="C689" s="2" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>GF</t>
         </is>
       </c>
       <c r="D689" s="2" t="inlineStr">
@@ -42667,7 +43123,7 @@
         </is>
       </c>
       <c r="F689" s="3" t="n">
-        <v>604500</v>
+        <v>597000</v>
       </c>
       <c r="G689" s="2" t="inlineStr"/>
       <c r="H689" s="2" t="inlineStr">
@@ -42694,12 +43150,12 @@
       </c>
       <c r="B690" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>660</t>
         </is>
       </c>
       <c r="C690" s="2" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>GF</t>
         </is>
       </c>
       <c r="D690" s="2" t="inlineStr">
@@ -42713,7 +43169,7 @@
         </is>
       </c>
       <c r="F690" s="3" t="n">
-        <v>584000</v>
+        <v>598000</v>
       </c>
       <c r="G690" s="2" t="inlineStr"/>
       <c r="H690" s="2" t="inlineStr">
@@ -42740,12 +43196,12 @@
       </c>
       <c r="B691" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>662</t>
         </is>
       </c>
       <c r="C691" s="2" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="D691" s="2" t="inlineStr">
@@ -42759,7 +43215,7 @@
         </is>
       </c>
       <c r="F691" s="3" t="n">
-        <v>610000</v>
+        <v>584000</v>
       </c>
       <c r="G691" s="2" t="inlineStr"/>
       <c r="H691" s="2" t="inlineStr">
@@ -42786,12 +43242,12 @@
       </c>
       <c r="B692" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>664</t>
         </is>
       </c>
       <c r="C692" s="2" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="D692" s="2" t="inlineStr">
@@ -42805,7 +43261,7 @@
         </is>
       </c>
       <c r="F692" s="3" t="n">
-        <v>610000</v>
+        <v>604500</v>
       </c>
       <c r="G692" s="2" t="inlineStr"/>
       <c r="H692" s="2" t="inlineStr">
@@ -42832,12 +43288,12 @@
       </c>
       <c r="B693" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>665</t>
         </is>
       </c>
       <c r="C693" s="2" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="D693" s="2" t="inlineStr">
@@ -42851,7 +43307,7 @@
         </is>
       </c>
       <c r="F693" s="3" t="n">
-        <v>617500</v>
+        <v>604500</v>
       </c>
       <c r="G693" s="2" t="inlineStr"/>
       <c r="H693" s="2" t="inlineStr">
@@ -42878,12 +43334,12 @@
       </c>
       <c r="B694" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>674</t>
         </is>
       </c>
       <c r="C694" s="2" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="D694" s="2" t="inlineStr">
@@ -42897,7 +43353,7 @@
         </is>
       </c>
       <c r="F694" s="3" t="n">
-        <v>617500</v>
+        <v>584000</v>
       </c>
       <c r="G694" s="2" t="inlineStr"/>
       <c r="H694" s="2" t="inlineStr">
@@ -42924,12 +43380,12 @@
       </c>
       <c r="B695" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>676</t>
         </is>
       </c>
       <c r="C695" s="2" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="D695" s="2" t="inlineStr">
@@ -42943,7 +43399,7 @@
         </is>
       </c>
       <c r="F695" s="3" t="n">
-        <v>623000</v>
+        <v>610000</v>
       </c>
       <c r="G695" s="2" t="inlineStr"/>
       <c r="H695" s="2" t="inlineStr">
@@ -42970,12 +43426,12 @@
       </c>
       <c r="B696" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>677</t>
         </is>
       </c>
       <c r="C696" s="2" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="D696" s="2" t="inlineStr">
@@ -42989,7 +43445,7 @@
         </is>
       </c>
       <c r="F696" s="3" t="n">
-        <v>623000</v>
+        <v>610000</v>
       </c>
       <c r="G696" s="2" t="inlineStr"/>
       <c r="H696" s="2" t="inlineStr">
@@ -43016,12 +43472,12 @@
       </c>
       <c r="B697" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>691</t>
         </is>
       </c>
       <c r="C697" s="2" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="D697" s="2" t="inlineStr">
@@ -43035,7 +43491,7 @@
         </is>
       </c>
       <c r="F697" s="3" t="n">
-        <v>623000</v>
+        <v>617500</v>
       </c>
       <c r="G697" s="2" t="inlineStr"/>
       <c r="H697" s="2" t="inlineStr">
@@ -43062,7 +43518,7 @@
       </c>
       <c r="B698" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>703</t>
         </is>
       </c>
       <c r="C698" s="2" t="inlineStr">
@@ -43081,7 +43537,7 @@
         </is>
       </c>
       <c r="F698" s="3" t="n">
-        <v>623000</v>
+        <v>617500</v>
       </c>
       <c r="G698" s="2" t="inlineStr"/>
       <c r="H698" s="2" t="inlineStr">
@@ -43108,7 +43564,7 @@
       </c>
       <c r="B699" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>704</t>
         </is>
       </c>
       <c r="C699" s="2" t="inlineStr">
@@ -43127,7 +43583,7 @@
         </is>
       </c>
       <c r="F699" s="3" t="n">
-        <v>598000</v>
+        <v>623000</v>
       </c>
       <c r="G699" s="2" t="inlineStr"/>
       <c r="H699" s="2" t="inlineStr">
@@ -43149,182 +43605,184 @@
     <row r="700">
       <c r="A700" s="2" t="inlineStr">
         <is>
-          <t>WC1X - Postmark, Farringdon</t>
+          <t>W6 - Fulham Reach</t>
         </is>
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>H1.01.01</t>
+          <t>705</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="D700" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E700" s="2" t="inlineStr">
         <is>
-          <t>SE&amp;NW</t>
+          <t>N,W</t>
         </is>
       </c>
       <c r="F700" s="3" t="n">
-        <v>1395000</v>
+        <v>623000</v>
       </c>
       <c r="G700" s="2" t="inlineStr"/>
       <c r="H700" s="2" t="inlineStr">
         <is>
-          <t>04.07.26</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="I700" s="2" t="inlineStr">
         <is>
-          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
         </is>
       </c>
       <c r="J700" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:41</t>
+          <t>2026-07-08T16:57:26</t>
         </is>
       </c>
     </row>
     <row r="701">
       <c r="A701" s="2" t="inlineStr">
         <is>
-          <t>WC1X - Postmark, Farringdon</t>
+          <t>W6 - Fulham Reach</t>
         </is>
       </c>
       <c r="B701" s="2" t="inlineStr">
         <is>
-          <t>H1.01.02</t>
+          <t>706</t>
         </is>
       </c>
       <c r="C701" s="2" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="D701" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E701" s="2" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>N,W</t>
         </is>
       </c>
       <c r="F701" s="3" t="n">
-        <v>1410000</v>
+        <v>623000</v>
       </c>
       <c r="G701" s="2" t="inlineStr"/>
       <c r="H701" s="2" t="inlineStr">
         <is>
-          <t>04.07.26</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="I701" s="2" t="inlineStr">
         <is>
-          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
         </is>
       </c>
       <c r="J701" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:41</t>
+          <t>2026-07-08T16:57:26</t>
         </is>
       </c>
     </row>
     <row r="702">
       <c r="A702" s="2" t="inlineStr">
         <is>
-          <t>WC1X - Postmark, Farringdon</t>
+          <t>W6 - Fulham Reach</t>
         </is>
       </c>
       <c r="B702" s="2" t="inlineStr">
         <is>
-          <t>H1.01.03</t>
+          <t>707</t>
         </is>
       </c>
       <c r="C702" s="2" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="D702" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E702" s="2" t="inlineStr">
         <is>
-          <t>SW&amp;NE</t>
-        </is>
-      </c>
-      <c r="F702" s="2" t="n"/>
+          <t>N,W</t>
+        </is>
+      </c>
+      <c r="F702" s="3" t="n">
+        <v>623000</v>
+      </c>
       <c r="G702" s="2" t="inlineStr"/>
       <c r="H702" s="2" t="inlineStr">
         <is>
-          <t>04.07.26</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="I702" s="2" t="inlineStr">
         <is>
-          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
         </is>
       </c>
       <c r="J702" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:41</t>
+          <t>2026-07-08T16:57:26</t>
         </is>
       </c>
     </row>
     <row r="703">
       <c r="A703" s="2" t="inlineStr">
         <is>
-          <t>WC1X - Postmark, Farringdon</t>
+          <t>W6 - Fulham Reach</t>
         </is>
       </c>
       <c r="B703" s="2" t="inlineStr">
         <is>
-          <t>H3.00.01</t>
+          <t>708</t>
         </is>
       </c>
       <c r="C703" s="2" t="inlineStr">
         <is>
-          <t>Ground</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="D703" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E703" s="2" t="inlineStr">
         <is>
-          <t>SE&amp;NW</t>
+          <t>N,W</t>
         </is>
       </c>
       <c r="F703" s="3" t="n">
-        <v>1450000</v>
+        <v>598000</v>
       </c>
       <c r="G703" s="2" t="inlineStr"/>
       <c r="H703" s="2" t="inlineStr">
         <is>
-          <t>04.07.26</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="I703" s="2" t="inlineStr">
         <is>
-          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+          <t>Fulham Reach Palmer House - CN Agent use only - 05.07.26.pdf</t>
         </is>
       </c>
       <c r="J703" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:41</t>
+          <t>2026-07-08T16:57:26</t>
         </is>
       </c>
     </row>
@@ -43336,7 +43794,7 @@
       </c>
       <c r="B704" s="2" t="inlineStr">
         <is>
-          <t>H3.01.01</t>
+          <t>H1.01.01</t>
         </is>
       </c>
       <c r="C704" s="2" t="inlineStr">
@@ -43346,7 +43804,7 @@
       </c>
       <c r="D704" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E704" s="2" t="inlineStr">
@@ -43355,7 +43813,7 @@
         </is>
       </c>
       <c r="F704" s="3" t="n">
-        <v>995000</v>
+        <v>1395000</v>
       </c>
       <c r="G704" s="2" t="inlineStr"/>
       <c r="H704" s="2" t="inlineStr">
@@ -43382,12 +43840,12 @@
       </c>
       <c r="B705" s="2" t="inlineStr">
         <is>
-          <t>H3.03.03</t>
+          <t>H1.01.02</t>
         </is>
       </c>
       <c r="C705" s="2" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="D705" s="2" t="inlineStr">
@@ -43397,10 +43855,12 @@
       </c>
       <c r="E705" s="2" t="inlineStr">
         <is>
-          <t>SE&amp;NW</t>
-        </is>
-      </c>
-      <c r="F705" s="2" t="n"/>
+          <t>SW</t>
+        </is>
+      </c>
+      <c r="F705" s="3" t="n">
+        <v>1410000</v>
+      </c>
       <c r="G705" s="2" t="inlineStr"/>
       <c r="H705" s="2" t="inlineStr">
         <is>
@@ -43426,12 +43886,12 @@
       </c>
       <c r="B706" s="2" t="inlineStr">
         <is>
-          <t>H4.00.02</t>
+          <t>H1.01.03</t>
         </is>
       </c>
       <c r="C706" s="2" t="inlineStr">
         <is>
-          <t>Ground</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="D706" s="2" t="inlineStr">
@@ -43441,12 +43901,10 @@
       </c>
       <c r="E706" s="2" t="inlineStr">
         <is>
-          <t>SE&amp;NW</t>
-        </is>
-      </c>
-      <c r="F706" s="3" t="n">
-        <v>1450000</v>
-      </c>
+          <t>SW&amp;NE</t>
+        </is>
+      </c>
+      <c r="F706" s="2" t="n"/>
       <c r="G706" s="2" t="inlineStr"/>
       <c r="H706" s="2" t="inlineStr">
         <is>
@@ -43472,7 +43930,7 @@
       </c>
       <c r="B707" s="2" t="inlineStr">
         <is>
-          <t>H5.00.01</t>
+          <t>H3.00.01</t>
         </is>
       </c>
       <c r="C707" s="2" t="inlineStr">
@@ -43487,11 +43945,11 @@
       </c>
       <c r="E707" s="2" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>SE&amp;NW</t>
         </is>
       </c>
       <c r="F707" s="3" t="n">
-        <v>1315000</v>
+        <v>1450000</v>
       </c>
       <c r="G707" s="2" t="inlineStr"/>
       <c r="H707" s="2" t="inlineStr">
@@ -43518,26 +43976,26 @@
       </c>
       <c r="B708" s="2" t="inlineStr">
         <is>
-          <t>H5.00.02</t>
+          <t>H3.01.01</t>
         </is>
       </c>
       <c r="C708" s="2" t="inlineStr">
         <is>
-          <t>Ground</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="D708" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E708" s="2" t="inlineStr">
         <is>
-          <t>NW</t>
+          <t>SE&amp;NW</t>
         </is>
       </c>
       <c r="F708" s="3" t="n">
-        <v>1315000</v>
+        <v>995000</v>
       </c>
       <c r="G708" s="2" t="inlineStr"/>
       <c r="H708" s="2" t="inlineStr">
@@ -43564,27 +44022,25 @@
       </c>
       <c r="B709" s="2" t="inlineStr">
         <is>
-          <t>H5.00.03</t>
+          <t>H3.03.03</t>
         </is>
       </c>
       <c r="C709" s="2" t="inlineStr">
         <is>
-          <t>Ground</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="D709" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E709" s="2" t="inlineStr">
         <is>
-          <t>SE&amp;NE</t>
-        </is>
-      </c>
-      <c r="F709" s="3" t="n">
-        <v>1015000</v>
-      </c>
+          <t>SE&amp;NW</t>
+        </is>
+      </c>
+      <c r="F709" s="2" t="n"/>
       <c r="G709" s="2" t="inlineStr"/>
       <c r="H709" s="2" t="inlineStr">
         <is>
@@ -43610,7 +44066,7 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>H7.00.02</t>
+          <t>H4.00.02</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
@@ -43620,7 +44076,7 @@
       </c>
       <c r="D710" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E710" s="2" t="inlineStr">
@@ -43629,7 +44085,7 @@
         </is>
       </c>
       <c r="F710" s="3" t="n">
-        <v>1875000</v>
+        <v>1450000</v>
       </c>
       <c r="G710" s="2" t="inlineStr"/>
       <c r="H710" s="2" t="inlineStr">
@@ -43656,7 +44112,7 @@
       </c>
       <c r="B711" s="2" t="inlineStr">
         <is>
-          <t>J1.00.01</t>
+          <t>H5.00.01</t>
         </is>
       </c>
       <c r="C711" s="2" t="inlineStr">
@@ -43666,7 +44122,7 @@
       </c>
       <c r="D711" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E711" s="2" t="inlineStr">
@@ -43675,7 +44131,7 @@
         </is>
       </c>
       <c r="F711" s="3" t="n">
-        <v>950000</v>
+        <v>1315000</v>
       </c>
       <c r="G711" s="2" t="inlineStr"/>
       <c r="H711" s="2" t="inlineStr">
@@ -43702,7 +44158,7 @@
       </c>
       <c r="B712" s="2" t="inlineStr">
         <is>
-          <t>J1.00.04</t>
+          <t>H5.00.02</t>
         </is>
       </c>
       <c r="C712" s="2" t="inlineStr">
@@ -43712,16 +44168,16 @@
       </c>
       <c r="D712" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E712" s="2" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>NW</t>
         </is>
       </c>
       <c r="F712" s="3" t="n">
-        <v>965000</v>
+        <v>1315000</v>
       </c>
       <c r="G712" s="2" t="inlineStr"/>
       <c r="H712" s="2" t="inlineStr">
@@ -43740,8 +44196,192 @@
         </is>
       </c>
     </row>
+    <row r="713">
+      <c r="A713" s="2" t="inlineStr">
+        <is>
+          <t>WC1X - Postmark, Farringdon</t>
+        </is>
+      </c>
+      <c r="B713" s="2" t="inlineStr">
+        <is>
+          <t>H5.00.03</t>
+        </is>
+      </c>
+      <c r="C713" s="2" t="inlineStr">
+        <is>
+          <t>Ground</t>
+        </is>
+      </c>
+      <c r="D713" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E713" s="2" t="inlineStr">
+        <is>
+          <t>SE&amp;NE</t>
+        </is>
+      </c>
+      <c r="F713" s="3" t="n">
+        <v>1015000</v>
+      </c>
+      <c r="G713" s="2" t="inlineStr"/>
+      <c r="H713" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26</t>
+        </is>
+      </c>
+      <c r="I713" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+        </is>
+      </c>
+      <c r="J713" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:01:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="2" t="inlineStr">
+        <is>
+          <t>WC1X - Postmark, Farringdon</t>
+        </is>
+      </c>
+      <c r="B714" s="2" t="inlineStr">
+        <is>
+          <t>H7.00.02</t>
+        </is>
+      </c>
+      <c r="C714" s="2" t="inlineStr">
+        <is>
+          <t>Ground</t>
+        </is>
+      </c>
+      <c r="D714" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E714" s="2" t="inlineStr">
+        <is>
+          <t>SE&amp;NW</t>
+        </is>
+      </c>
+      <c r="F714" s="3" t="n">
+        <v>1875000</v>
+      </c>
+      <c r="G714" s="2" t="inlineStr"/>
+      <c r="H714" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26</t>
+        </is>
+      </c>
+      <c r="I714" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+        </is>
+      </c>
+      <c r="J714" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:01:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="2" t="inlineStr">
+        <is>
+          <t>WC1X - Postmark, Farringdon</t>
+        </is>
+      </c>
+      <c r="B715" s="2" t="inlineStr">
+        <is>
+          <t>J1.00.01</t>
+        </is>
+      </c>
+      <c r="C715" s="2" t="inlineStr">
+        <is>
+          <t>Ground</t>
+        </is>
+      </c>
+      <c r="D715" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E715" s="2" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+      <c r="F715" s="3" t="n">
+        <v>950000</v>
+      </c>
+      <c r="G715" s="2" t="inlineStr"/>
+      <c r="H715" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26</t>
+        </is>
+      </c>
+      <c r="I715" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+        </is>
+      </c>
+      <c r="J715" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:01:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="2" t="inlineStr">
+        <is>
+          <t>WC1X - Postmark, Farringdon</t>
+        </is>
+      </c>
+      <c r="B716" s="2" t="inlineStr">
+        <is>
+          <t>J1.00.04</t>
+        </is>
+      </c>
+      <c r="C716" s="2" t="inlineStr">
+        <is>
+          <t>Ground</t>
+        </is>
+      </c>
+      <c r="D716" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E716" s="2" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="F716" s="3" t="n">
+        <v>965000</v>
+      </c>
+      <c r="G716" s="2" t="inlineStr"/>
+      <c r="H716" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26</t>
+        </is>
+      </c>
+      <c r="I716" s="2" t="inlineStr">
+        <is>
+          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+        </is>
+      </c>
+      <c r="J716" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:01:41</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J712"/>
+  <autoFilter ref="A1:J716"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -46523,208 +47163,208 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>W12 - White City Living</t>
+          <t>UB1 - The Green Quarter</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>WCL - Ready to move - Solaris One 27.06.26.pdf</t>
+          <t>CN-The Green Quarter - Brickfields Customer Pricelist -05.07.26.pdf</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>WCL - Ready to move - Solaris One 27.06.26</t>
+          <t>CN-The Green Quarter - Brickfields Customer Pricelist -05.07.26</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:53:11</t>
+          <t>2026-07-09T11:09:35</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>W12 - White City Living</t>
+          <t>UB1 - The Green Quarter</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>WCL-Ready to Move In- Solaris One 02.07.26.pdf</t>
+          <t>The Green Quarter - Brickfields Customer Pricelist -28.06.26.pdf</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>WCL-Ready to Move In- Solaris One 02.07.26</t>
+          <t>The Green Quarter - Brickfields Customer Pricelist -28.06.26</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:53:11</t>
+          <t>2026-07-09T11:09:35</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Marleigh Park</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Marleigh Apartments Franklin and Kestrel Price List - 22.05.2026.pdf</t>
+          <t>WCL - Ready to move - Solaris One 27.06.26.pdf</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Marleigh Apartments Franklin and Kestrel Price List - 22.05.2026</t>
+          <t>WCL - Ready to move - Solaris One 27.06.26</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:04:25</t>
+          <t>2026-07-09T09:53:11</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Marleigh Park</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Marleigh Apartments Franklin and Kestrel Price List 01.07.2026.pdf</t>
+          <t>WCL-Ready to Move In- Solaris One 02.07.26.pdf</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Marleigh Apartments Franklin and Kestrel Price List 01.07.2026</t>
+          <t>WCL-Ready to Move In- Solaris One 02.07.26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:04:25</t>
+          <t>2026-07-09T09:53:11</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Hartmere</t>
+          <t>Marleigh Park</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Hartmere Freehold Houses Price List - 22.05.2026.pdf</t>
+          <t>Marleigh Apartments Franklin and Kestrel Price List - 22.05.2026.pdf</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Hartmere Freehold Houses Price List - 22.05.2026</t>
+          <t>Marleigh Apartments Franklin and Kestrel Price List - 22.05.2026</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:04:19</t>
+          <t>2026-07-08T17:04:25</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Hartmere</t>
+          <t>Marleigh Park</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Hartmere Price List- Freehold Houses 01.07.2026.pdf</t>
+          <t>Marleigh Apartments Franklin and Kestrel Price List 01.07.2026.pdf</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Hartmere Price List- Freehold Houses 01.07.2026</t>
+          <t>Marleigh Apartments Franklin and Kestrel Price List 01.07.2026</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:04:19</t>
+          <t>2026-07-08T17:04:25</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>City Reach</t>
+          <t>Hartmere</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>City Reach Florence Court Price List - 22.05.2026.pdf</t>
+          <t>Hartmere Freehold Houses Price List - 22.05.2026.pdf</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>City Reach Florence Court Price List - 22.05.2026</t>
+          <t>Hartmere Freehold Houses Price List - 22.05.2026</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:04:14</t>
+          <t>2026-07-08T17:04:19</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>City Reach</t>
+          <t>Hartmere</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>City Reach Florence Court Price List 01.07.2026.pdf</t>
+          <t>Hartmere Price List- Freehold Houses 01.07.2026.pdf</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>City Reach Florence Court Price List 01.07.2026</t>
+          <t>Hartmere Price List- Freehold Houses 01.07.2026</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:04:14</t>
+          <t>2026-07-08T17:04:19</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
     </row>
@@ -46736,21 +47376,21 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>City Reach Ida Court Price List - 22.05.2026.pdf</t>
+          <t>City Reach Florence Court Price List - 22.05.2026.pdf</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>City Reach Ida Court Price List - 22.05.2026</t>
+          <t>City Reach Florence Court Price List - 22.05.2026</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:04:10</t>
+          <t>2026-07-08T17:04:14</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
     </row>
@@ -46762,135 +47402,135 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>City Reach Ida Court Price List 01.07.2026.pdf</t>
+          <t>City Reach Florence Court Price List 01.07.2026.pdf</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>City Reach Ida Court Price List 01.07.2026</t>
+          <t>City Reach Florence Court Price List 01.07.2026</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:04:10</t>
+          <t>2026-07-08T17:04:14</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>W14 - 50 Brook Green (London Square)</t>
+          <t>City Reach</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Fifty Brook Green - Price List - 15.06.2026.pdf</t>
+          <t>City Reach Ida Court Price List - 22.05.2026.pdf</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Fifty Brook Green - Price List - 15.06.2026</t>
+          <t>City Reach Ida Court Price List - 22.05.2026</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:04:04</t>
+          <t>2026-07-08T17:04:10</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>W14 - 50 Brook Green (London Square)</t>
+          <t>City Reach</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Fifty Brook Green - Price List - 29.06.2026.pdf</t>
+          <t>City Reach Ida Court Price List 01.07.2026.pdf</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Fifty Brook Green - Price List - 29.06.2026</t>
+          <t>City Reach Ida Court Price List 01.07.2026</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:04:04</t>
+          <t>2026-07-08T17:04:10</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>SW6 - Chelsea Waterfront Tower East</t>
+          <t>W14 - 50 Brook Green (London Square)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Tower East  Pricelist  29th June 2026.pdf</t>
+          <t>Fifty Brook Green - Price List - 15.06.2026.pdf</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Tower East  Pricelist  29th June 2026</t>
+          <t>Fifty Brook Green - Price List - 15.06.2026</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:03:17</t>
+          <t>2026-07-08T17:04:04</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="F14" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>SW6 - Chelsea Waterfront Tower East</t>
+          <t>W14 - 50 Brook Green (London Square)</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Tower East  Pricelist 8th June 2026.pdf</t>
+          <t>Fifty Brook Green - Price List - 29.06.2026.pdf</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Tower East  Pricelist 8th June 2026</t>
+          <t>Fifty Brook Green - Price List - 29.06.2026</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:03:17</t>
+          <t>2026-07-08T17:04:04</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="F15" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -46900,27 +47540,23 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Powerhouse Pricelist  29th June 2026.pdf</t>
+          <t>Tower East  Pricelist  29th June 2026.pdf</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Powerhouse Pricelist  29th June 2026</t>
+          <t>Tower East  Pricelist  29th June 2026</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:03:08</t>
+          <t>2026-07-08T17:03:17</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -46930,27 +47566,23 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Powerhouse Pricelist 8th June 2026.pdf</t>
+          <t>Tower East  Pricelist 8th June 2026.pdf</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Powerhouse Pricelist 8th June 2026</t>
+          <t>Tower East  Pricelist 8th June 2026</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:03:08</t>
+          <t>2026-07-08T17:03:17</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -46960,17 +47592,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Water Gardens Pricelist  29th June 2026.pdf</t>
+          <t>Powerhouse Pricelist  29th June 2026.pdf</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Water Gardens Pricelist  29th June 2026</t>
+          <t>Powerhouse Pricelist  29th June 2026</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:03:01</t>
+          <t>2026-07-08T17:03:08</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
@@ -46990,17 +47622,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Water Gardens Pricelist 8th June 2026.pdf</t>
+          <t>Powerhouse Pricelist 8th June 2026.pdf</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Water Gardens Pricelist 8th June 2026</t>
+          <t>Powerhouse Pricelist 8th June 2026</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:03:01</t>
+          <t>2026-07-08T17:03:08</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
@@ -47020,23 +47652,27 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Tower West Pricelist  29th June 2026.pdf</t>
+          <t>Water Gardens Pricelist  29th June 2026.pdf</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Tower West Pricelist  29th June 2026</t>
+          <t>Water Gardens Pricelist  29th June 2026</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:57</t>
+          <t>2026-07-08T17:03:01</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="F20" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -47046,73 +47682,77 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Tower West Pricelist 8th June 2026.pdf</t>
+          <t>Water Gardens Pricelist 8th June 2026.pdf</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Tower West Pricelist 8th June 2026</t>
+          <t>Water Gardens Pricelist 8th June 2026</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:57</t>
+          <t>2026-07-08T17:03:01</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="F21" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>KT1 - County Hall Kingston (London Square)</t>
+          <t>SW6 - Chelsea Waterfront Tower East</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>County Hall Kingston - Heritage Collection - Customer Price List 10.06.2026.pdf</t>
+          <t>Tower West Pricelist  29th June 2026.pdf</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>County Hall Kingston - Heritage Collection - Customer Price List 10.06.2026</t>
+          <t>Tower West Pricelist  29th June 2026</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:50</t>
+          <t>2026-07-08T17:02:57</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>KT1 - County Hall Kingston (London Square)</t>
+          <t>SW6 - Chelsea Waterfront Tower East</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>County Hall Kingston - Heritage Collection - Customer Price List 22.06.2026.pdf</t>
+          <t>Tower West Pricelist 8th June 2026.pdf</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>County Hall Kingston - Heritage Collection - Customer Price List 22.06.2026</t>
+          <t>Tower West Pricelist 8th June 2026</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:50</t>
+          <t>2026-07-08T17:02:57</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
     </row>
@@ -47124,21 +47764,21 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>County Hall Kingston - New Build - Customer Price List 02.06.2026.pdf</t>
+          <t>County Hall Kingston - Heritage Collection - Customer Price List 10.06.2026.pdf</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>County Hall Kingston - New Build - Customer Price List 02.06.2026</t>
+          <t>County Hall Kingston - Heritage Collection - Customer Price List 10.06.2026</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:43</t>
+          <t>2026-07-08T17:02:50</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
     </row>
@@ -47150,103 +47790,95 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>County Hall Kingston - New Build - Customer Price List 22.06.2026.pdf</t>
+          <t>County Hall Kingston - Heritage Collection - Customer Price List 22.06.2026.pdf</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>County Hall Kingston - New Build - Customer Price List 22.06.2026</t>
+          <t>County Hall Kingston - Heritage Collection - Customer Price List 22.06.2026</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:43</t>
+          <t>2026-07-08T17:02:50</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>TW2 - Twickenham Green (London Square)</t>
+          <t>KT1 - County Hall Kingston (London Square)</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Twickenham Green Price List 16.06.26.pdf</t>
+          <t>County Hall Kingston - New Build - Customer Price List 02.06.2026.pdf</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Twickenham Green Price List 16.06.26</t>
+          <t>County Hall Kingston - New Build - Customer Price List 02.06.2026</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:37</t>
+          <t>2026-07-08T17:02:43</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>TW2 - Twickenham Green (London Square)</t>
+          <t>KT1 - County Hall Kingston (London Square)</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Twickenham Green Price List 28.06.26.pdf</t>
+          <t>County Hall Kingston - New Build - Customer Price List 22.06.2026.pdf</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Twickenham Green Price List 28.06.26</t>
+          <t>County Hall Kingston - New Build - Customer Price List 22.06.2026</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:37</t>
+          <t>2026-07-08T17:02:43</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>TW1 - Twickenham Square (London Square)</t>
+          <t>TW2 - Twickenham Green (London Square)</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Twickenham Square Price List 16.06.26.pdf</t>
+          <t>Twickenham Green Price List 16.06.26.pdf</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Twickenham Square Price List 16.06.26</t>
+          <t>Twickenham Green Price List 16.06.26</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:32</t>
+          <t>2026-07-08T17:02:37</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
@@ -47261,22 +47893,22 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>TW1 - Twickenham Square (London Square)</t>
+          <t>TW2 - Twickenham Green (London Square)</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Twickenham Square Price List 29.06.26.pdf</t>
+          <t>Twickenham Green Price List 28.06.26.pdf</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Twickenham Square Price List 29.06.26</t>
+          <t>Twickenham Green Price List 28.06.26</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:32</t>
+          <t>2026-07-08T17:02:37</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
@@ -47291,528 +47923,536 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>SW19 - Wimbledon Bridge House (London Square)</t>
+          <t>TW1 - Twickenham Square (London Square)</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Wimbledon Bridge House - Price List - 15.06.26.pdf</t>
+          <t>Twickenham Square Price List 16.06.26.pdf</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Wimbledon Bridge House - Price List - 15.06.26</t>
+          <t>Twickenham Square Price List 16.06.26</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:25</t>
+          <t>2026-07-08T17:02:32</t>
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="F30" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>SW19 - Wimbledon Bridge House (London Square)</t>
+          <t>TW1 - Twickenham Square (London Square)</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Wimbledon Bridge House - Price List - 29.06.26.pdf</t>
+          <t>Twickenham Square Price List 29.06.26.pdf</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Wimbledon Bridge House - Price List - 29.06.26</t>
+          <t>Twickenham Square Price List 29.06.26</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:25</t>
+          <t>2026-07-08T17:02:32</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="F31" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>SW11 - Ransomes Wharf (London Square)</t>
+          <t>SW19 - Wimbledon Bridge House (London Square)</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Ransomes Wharf - Customer Price List - 15.06.2026.pdf</t>
+          <t>Wimbledon Bridge House - Price List - 15.06.26.pdf</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Ransomes Wharf - Customer Price List - 15.06.2026</t>
+          <t>Wimbledon Bridge House - Price List - 15.06.26</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:18</t>
+          <t>2026-07-08T17:02:25</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>SW11 - Ransomes Wharf (London Square)</t>
+          <t>SW19 - Wimbledon Bridge House (London Square)</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Ransomes Wharf - Customer Price List - 27.06.2026.pdf</t>
+          <t>Wimbledon Bridge House - Price List - 29.06.26.pdf</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Ransomes Wharf - Customer Price List - 27.06.2026</t>
+          <t>Wimbledon Bridge House - Price List - 29.06.26</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:18</t>
+          <t>2026-07-08T17:02:25</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>SE18 - Woolwich (London Square)</t>
+          <t>SW11 - Ransomes Wharf (London Square)</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Woolwich Price List 15.06.2026.pdf</t>
+          <t>Ransomes Wharf - Customer Price List - 15.06.2026.pdf</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Woolwich Price List 15.06.2026</t>
+          <t>Ransomes Wharf - Customer Price List - 15.06.2026</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:10</t>
+          <t>2026-07-08T17:02:18</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>SE18 - Woolwich (London Square)</t>
+          <t>SW11 - Ransomes Wharf (London Square)</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Woolwich Price List 29.06.2026.pdf</t>
+          <t>Ransomes Wharf - Customer Price List - 27.06.2026.pdf</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Woolwich Price List 29.06.2026</t>
+          <t>Ransomes Wharf - Customer Price List - 27.06.2026</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:10</t>
+          <t>2026-07-08T17:02:18</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>SE1 - Bermondsey (London Square)</t>
+          <t>SE18 - Woolwich (London Square)</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Bermondsey Price List 16.06.26.pdf</t>
+          <t>Woolwich Price List 15.06.2026.pdf</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Bermondsey Price List 16.06.26</t>
+          <t>Woolwich Price List 15.06.2026</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:05</t>
+          <t>2026-07-08T17:02:10</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>SE1 - Bermondsey (London Square)</t>
+          <t>SE18 - Woolwich (London Square)</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Bermondsey Price List 29.06.26.pdf</t>
+          <t>Woolwich Price List 29.06.2026.pdf</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Bermondsey Price List 29.06.26</t>
+          <t>Woolwich Price List 29.06.2026</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:05</t>
+          <t>2026-07-08T17:02:10</t>
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>SE17 - The Wilderly</t>
+          <t>SE1 - Bermondsey (London Square)</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>The Wilderly Tower Availability List July 2026.pdf</t>
+          <t>Bermondsey Price List 16.06.26.pdf</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>The Wilderly Tower Availability List July 2026</t>
+          <t>Bermondsey Price List 16.06.26</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:00</t>
+          <t>2026-07-08T17:02:05</t>
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>SE17 - The Wilderly</t>
+          <t>SE1 - Bermondsey (London Square)</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>The Wilderly Tower Availability List May 2026.pdf</t>
+          <t>Bermondsey Price List 29.06.26.pdf</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>The Wilderly Tower Availability List May 2026</t>
+          <t>Bermondsey Price List 29.06.26</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:00</t>
+          <t>2026-07-08T17:02:05</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>E14 - Goodluck Hope</t>
+          <t>SE17 - The Wilderly</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Goodluck Hope Price List 12th June 2026.pdf</t>
+          <t>The Wilderly Tower Availability List July 2026.pdf</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Goodluck Hope Price List 12th June 2026</t>
+          <t>The Wilderly Tower Availability List July 2026</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:52</t>
+          <t>2026-07-08T17:02:00</t>
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>E14 - Goodluck Hope</t>
+          <t>SE17 - The Wilderly</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Goodluck Hope Price List 30th June 2026.pdf</t>
+          <t>The Wilderly Tower Availability List May 2026.pdf</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Goodluck Hope Price List 30th June 2026</t>
+          <t>The Wilderly Tower Availability List May 2026</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:52</t>
+          <t>2026-07-08T17:02:00</t>
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>WC1X - Postmark, Farringdon</t>
+          <t>E14 - Goodluck Hope</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
+          <t>Goodluck Hope Price List 12th June 2026.pdf</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>04.07.26 - Monograph Square - Price List Block H</t>
+          <t>Goodluck Hope Price List 12th June 2026</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:41</t>
+          <t>2026-07-08T17:01:52</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>WC1X - Postmark, Farringdon</t>
+          <t>E14 - Goodluck Hope</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>20.06.26 - Monograph Square - Price List Block H.pdf</t>
+          <t>Goodluck Hope Price List 30th June 2026.pdf</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>20.06.26 - Monograph Square - Price List Block H</t>
+          <t>Goodluck Hope Price List 30th June 2026</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:41</t>
+          <t>2026-07-08T17:01:52</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>SE1 - Westminster Tower (London Square)</t>
+          <t>WC1X - Postmark, Farringdon</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Westminster Tower Price List - 05.07.2026.pdf</t>
+          <t>04.07.26 - Monograph Square - Price List Block H.pdf</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Westminster Tower Price List - 05.07.2026</t>
+          <t>04.07.26 - Monograph Square - Price List Block H</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:36</t>
+          <t>2026-07-08T17:01:41</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>SE1 - Westminster Tower (London Square)</t>
+          <t>WC1X - Postmark, Farringdon</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Westminster Tower Price List - 15.06.2026.pdf</t>
+          <t>20.06.26 - Monograph Square - Price List Block H.pdf</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Westminster Tower Price List - 15.06.2026</t>
+          <t>20.06.26 - Monograph Square - Price List Block H</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:36</t>
+          <t>2026-07-08T17:01:41</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>No recognizable unit table found</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>CR0 - Croydon (London Square)</t>
+          <t>SE1 - Westminster Tower (London Square)</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Croydon Price List - 15 June 26.pdf</t>
+          <t>Westminster Tower Price List - 05.07.2026.pdf</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Croydon Price List - 15 June 26</t>
+          <t>Westminster Tower Price List - 05.07.2026</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:30</t>
+          <t>2026-07-08T17:01:36</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="F46" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>CR0 - Croydon (London Square)</t>
+          <t>SE1 - Westminster Tower (London Square)</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Croydon Price List - 29 June 26.pdf</t>
+          <t>Westminster Tower Price List - 15.06.2026.pdf</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Croydon Price List - 29 June 26</t>
+          <t>Westminster Tower Price List - 15.06.2026</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:30</t>
+          <t>2026-07-08T17:01:36</t>
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="F47" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>No recognizable unit table found</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>W12 - White City Living</t>
+          <t>CR0 - Croydon (London Square)</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>WCL - Solaris Two 02.07.26.pdf</t>
+          <t>Croydon Price List - 15 June 26.pdf</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>WCL - Solaris Two 02.07.26</t>
+          <t>Croydon Price List - 15 June 26</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-08T17:01:30</t>
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>W12 - White City Living</t>
+          <t>CR0 - Croydon (London Square)</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>WCL - Solaris Two 27.06.26.pdf</t>
+          <t>Croydon Price List - 29 June 26.pdf</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>WCL - Solaris Two 27.06.26</t>
+          <t>Croydon Price List - 29 June 26</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-08T17:01:30</t>
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
     </row>
@@ -47824,21 +48464,21 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>WCL - Cascades Three price list - 02.07.26.pdf</t>
+          <t>WCL - Solaris Two 02.07.26.pdf</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>WCL - Cascades Three price list - 02.07.26</t>
+          <t>WCL - Solaris Two 02.07.26</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:16</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
     </row>
@@ -47850,125 +48490,125 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>WCL - Cascades Three price list - 27.06.26.pdf</t>
+          <t>WCL - Solaris Two 27.06.26.pdf</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>WCL - Cascades Three price list - 27.06.26</t>
+          <t>WCL - Solaris Two 27.06.26</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:16</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>SW18 - Wandsworth Mills</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>CN - WM_ The Artisan Price list - 05.07.26.pdf</t>
+          <t>WCL - Cascades Three price list - 02.07.26.pdf</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>CN - WM_ The Artisan Price list - 05.07.26</t>
+          <t>WCL - Cascades Three price list - 02.07.26</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:05</t>
+          <t>2026-07-08T17:01:16</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>SW18 - Wandsworth Mills</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>CN - WM_ The Artisan Price list 27.06.26.pdf</t>
+          <t>WCL - Cascades Three price list - 27.06.26.pdf</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>CN - WM_ The Artisan Price list 27.06.26</t>
+          <t>WCL - Cascades Three price list - 27.06.26</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:05</t>
+          <t>2026-07-08T17:01:16</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>UB1 - The Green Quarter</t>
+          <t>SW18 - Wandsworth Mills</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>CN-The Green Quarter - Brickfields Customer Pricelist -05.07.26.pdf</t>
+          <t>CN - WM_ The Artisan Price list - 05.07.26.pdf</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>CN-The Green Quarter - Brickfields Customer Pricelist -05.07.26</t>
+          <t>CN - WM_ The Artisan Price list - 05.07.26</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:58</t>
+          <t>2026-07-08T17:01:05</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>UB1 - The Green Quarter</t>
+          <t>SW18 - Wandsworth Mills</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>The Green Quarter - Brickfields Customer Pricelist -28.06.26.pdf</t>
+          <t>CN - WM_ The Artisan Price list 27.06.26.pdf</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>The Green Quarter - Brickfields Customer Pricelist -28.06.26</t>
+          <t>CN - WM_ The Artisan Price list 27.06.26</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:00:58</t>
+          <t>2026-07-08T17:01:05</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
     </row>

--- a/outputs/weekly_unit_change_database.xlsx
+++ b/outputs/weekly_unit_change_database.xlsx
@@ -17,9 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'房源变化'!$A$1:$N$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'房源变化'!$A$1:$N$114</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'降价房源'!$A$1:$N$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'新增房源'!$A$1:$N$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'新增房源'!$A$1:$N$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'售出房源'!$A$1:$N$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'其他变化'!$A$1:$N$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'当前房源数据库'!$A$1:$J$716</definedName>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N115"/>
+  <dimension ref="A1:N114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -462,7 +462,7 @@
     <col width="42" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
   </cols>
@@ -3938,35 +3938,39 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>SE3 - Kidbrooke Village</t>
+          <t>SW19 - Wimbledon Bridge House (London Square)</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>2-3-4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr"/>
+          <t>1 Bed</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
       <c r="F65" s="2" t="n"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>29.06.26</t>
+          <t>15.06.26</t>
         </is>
       </c>
       <c r="H65" s="2" t="n"/>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>06.07.26</t>
+          <t>29.06.26</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -3975,15 +3979,11 @@
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr"/>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>Show Apartment</t>
-        </is>
-      </c>
+      <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="2" t="n"/>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:53:11</t>
+          <t>2026-07-08T17:02:25</t>
         </is>
       </c>
     </row>
@@ -3995,22 +3995,22 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>102</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>1 Bed</t>
+          <t>2 Bed</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>North</t>
         </is>
       </c>
       <c r="F66" s="2" t="n"/>
@@ -4019,7 +4019,9 @@
           <t>15.06.26</t>
         </is>
       </c>
-      <c r="H66" s="2" t="n"/>
+      <c r="H66" s="3" t="n">
+        <v>1185000</v>
+      </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
           <t>29.06.26</t>
@@ -4047,7 +4049,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>104</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -4057,12 +4059,12 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>2 Bed</t>
+          <t>1 Bed</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="F67" s="2" t="n"/>
@@ -4072,7 +4074,7 @@
         </is>
       </c>
       <c r="H67" s="3" t="n">
-        <v>1185000</v>
+        <v>710000</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
@@ -4101,22 +4103,22 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>1 Bed</t>
+          <t>Suite</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="F68" s="2" t="n"/>
@@ -4126,7 +4128,7 @@
         </is>
       </c>
       <c r="H68" s="3" t="n">
-        <v>710000</v>
+        <v>512500</v>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
@@ -4155,12 +4157,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>56</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4180,7 +4182,7 @@
         </is>
       </c>
       <c r="H69" s="3" t="n">
-        <v>512500</v>
+        <v>507500</v>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
@@ -4209,12 +4211,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>71</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4234,7 +4236,7 @@
         </is>
       </c>
       <c r="H70" s="3" t="n">
-        <v>507500</v>
+        <v>517500</v>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
@@ -4263,22 +4265,22 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>93</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Suite</t>
+          <t>1 Bed</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>North</t>
         </is>
       </c>
       <c r="F71" s="2" t="n"/>
@@ -4288,7 +4290,7 @@
         </is>
       </c>
       <c r="H71" s="3" t="n">
-        <v>517500</v>
+        <v>720000</v>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
@@ -4317,17 +4319,17 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1 Bed</t>
+          <t>2 Bed</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -4335,15 +4337,15 @@
           <t>North</t>
         </is>
       </c>
-      <c r="F72" s="2" t="n"/>
+      <c r="F72" s="3" t="n">
+        <v>1225000</v>
+      </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
           <t>15.06.26</t>
         </is>
       </c>
-      <c r="H72" s="3" t="n">
-        <v>720000</v>
-      </c>
+      <c r="H72" s="2" t="n"/>
       <c r="I72" s="2" t="inlineStr">
         <is>
           <t>29.06.26</t>
@@ -4351,11 +4353,15 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>NEW_RELEASE</t>
+          <t>SOLD</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
-      <c r="L72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
       <c r="M72" s="2" t="n"/>
       <c r="N72" s="2" t="inlineStr">
         <is>
@@ -4371,26 +4377,26 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>2 Bed</t>
+          <t>Suite</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>East</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>1225000</v>
+        <v>502500</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
@@ -4429,12 +4435,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4444,11 +4450,11 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>North</t>
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>502500</v>
+        <v>512500</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
@@ -4487,7 +4493,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4497,17 +4503,15 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Suite</t>
+          <t>1 Bed</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="F75" s="3" t="n">
-        <v>512500</v>
-      </c>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="n"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
           <t>15.06.26</t>
@@ -4545,12 +4549,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -4560,10 +4564,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="n"/>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>597500</v>
+      </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
           <t>15.06.26</t>
@@ -4601,26 +4607,26 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>1 Bed</t>
+          <t>Suite</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>South</t>
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>597500</v>
+        <v>517500</v>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
@@ -4659,26 +4665,26 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Suite</t>
+          <t>1 Bed</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>South East</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>517500</v>
+        <v>740000</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
@@ -4712,58 +4718,50 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>SW19 - Wimbledon Bridge House (London Square)</t>
+          <t>SW6 - Chelsea Waterfront Tower East</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>1 Bed</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>South East</t>
-        </is>
-      </c>
-      <c r="F79" s="3" t="n">
-        <v>740000</v>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="n"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>15.06.26</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="n"/>
+          <t>8th June 2026</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>5842000</v>
+      </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>29.06.26</t>
+          <t>29th June 2026</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>SOLD</t>
+          <t>NEW_RELEASE</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>缺失</t>
-        </is>
-      </c>
+      <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="n"/>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:25</t>
+          <t>2026-07-08T17:02:57</t>
         </is>
       </c>
     </row>
@@ -4775,12 +4773,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -4795,9 +4793,7 @@
           <t>8th June 2026</t>
         </is>
       </c>
-      <c r="H80" s="3" t="n">
-        <v>5842000</v>
-      </c>
+      <c r="H80" s="2" t="n"/>
       <c r="I80" s="2" t="inlineStr">
         <is>
           <t>29th June 2026</t>
@@ -4805,11 +4801,15 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>NEW_RELEASE</t>
+          <t>SOLD</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
       <c r="M80" s="2" t="n"/>
       <c r="N80" s="2" t="inlineStr">
         <is>
@@ -4820,52 +4820,54 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>SW6 - Chelsea Waterfront Tower East</t>
+          <t>SW6 - King's Road Park</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>G1.3-01-04</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr"/>
+          <t>2 Bedroom</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>S/W - Park Views</t>
+        </is>
+      </c>
       <c r="F81" s="2" t="n"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>8th June 2026</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="n"/>
+          <t>28.06.2026</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>1370000</v>
+      </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>29th June 2026</t>
+          <t>05.07.2026</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>SOLD</t>
+          <t>NEW_RELEASE</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>缺失</t>
-        </is>
-      </c>
+      <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="n"/>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:57</t>
+          <t>2026-07-08T16:53:34</t>
         </is>
       </c>
     </row>
@@ -4877,12 +4879,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>G1.3-01-04</t>
+          <t>G1.4-00-06</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -4892,7 +4894,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>S/W - Park Views</t>
+          <t>S – Park Views</t>
         </is>
       </c>
       <c r="F82" s="2" t="n"/>
@@ -4901,9 +4903,7 @@
           <t>28.06.2026</t>
         </is>
       </c>
-      <c r="H82" s="3" t="n">
-        <v>1370000</v>
-      </c>
+      <c r="H82" s="2" t="n"/>
       <c r="I82" s="2" t="inlineStr">
         <is>
           <t>05.07.2026</t>
@@ -4931,31 +4931,35 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>G1.4-00-06</t>
+          <t>H1-19-06</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>2 Bedroom</t>
+          <t>3 Bedroom</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>S – Park Views</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="n"/>
+          <t>South / West</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>2975500</v>
+      </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
           <t>28.06.2026</t>
         </is>
       </c>
-      <c r="H83" s="2" t="n"/>
+      <c r="H83" s="3" t="n">
+        <v>2975000</v>
+      </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
           <t>05.07.2026</t>
@@ -4963,73 +4967,71 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>NEW_RELEASE</t>
+          <t>PRICE_DROP</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr"/>
-      <c r="M83" s="2" t="n"/>
+      <c r="M83" s="2" t="n">
+        <v>-500</v>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:53:34</t>
+          <t>2026-07-08T16:53:41</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>SW6 - King's Road Park</t>
+          <t>UB1 - The Green Quarter</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>H1-19-06</t>
+          <t>257</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>3 Bedroom</t>
+          <t>2 Bed 2 Bath</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>South / West</t>
-        </is>
-      </c>
-      <c r="F84" s="3" t="n">
-        <v>2975500</v>
-      </c>
+          <t>S &amp; E</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="n"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>28.06.2026</t>
+          <t>28.06.26</t>
         </is>
       </c>
       <c r="H84" s="3" t="n">
-        <v>2975000</v>
+        <v>545000</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>05.07.2026</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>PRICE_DROP</t>
+          <t>NEW_RELEASE</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr"/>
-      <c r="M84" s="2" t="n">
-        <v>-500</v>
-      </c>
+      <c r="M84" s="2" t="n"/>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:53:41</t>
+          <t>2026-07-09T11:09:36</t>
         </is>
       </c>
     </row>
@@ -5041,22 +5043,22 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>261</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>2 Bed 2 Bath</t>
+          <t>2 Bed 2.5 Bath</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>S &amp; E</t>
+          <t>N &amp; W</t>
         </is>
       </c>
       <c r="F85" s="2" t="n"/>
@@ -5066,7 +5068,7 @@
         </is>
       </c>
       <c r="H85" s="3" t="n">
-        <v>545000</v>
+        <v>555000</v>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
@@ -5095,12 +5097,12 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>269</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -5120,7 +5122,7 @@
         </is>
       </c>
       <c r="H86" s="3" t="n">
-        <v>555000</v>
+        <v>565000</v>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
@@ -5149,12 +5151,12 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>285</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -5174,7 +5176,7 @@
         </is>
       </c>
       <c r="H87" s="3" t="n">
-        <v>565000</v>
+        <v>575000</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
@@ -5203,33 +5205,33 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>2 Bed 2.5 Bath</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>N &amp; W</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="n"/>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>400000</v>
+      </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
           <t>28.06.26</t>
         </is>
       </c>
-      <c r="H88" s="3" t="n">
-        <v>575000</v>
-      </c>
+      <c r="H88" s="2" t="n"/>
       <c r="I88" s="2" t="inlineStr">
         <is>
           <t>05.07.26</t>
@@ -5237,11 +5239,15 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>NEW_RELEASE</t>
+          <t>RESERVED</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>ON HOLD</t>
+        </is>
+      </c>
       <c r="M88" s="2" t="n"/>
       <c r="N88" s="2" t="inlineStr">
         <is>
@@ -5257,17 +5263,17 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>291</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>1 Bed</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -5275,9 +5281,7 @@
           <t>W</t>
         </is>
       </c>
-      <c r="F89" s="3" t="n">
-        <v>400000</v>
-      </c>
+      <c r="F89" s="2" t="n"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
           <t>28.06.26</t>
@@ -5291,13 +5295,17 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
+          <t>SOLD</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
           <t>RESERVED</t>
         </is>
       </c>
-      <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>ON HOLD</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="M89" s="2" t="n"/>
@@ -5315,17 +5323,17 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>308</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>1 Bed</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -5370,60 +5378,58 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>UB1 - The Green Quarter</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>V18.02</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>3+Study</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="n"/>
+          <t>South/West/North</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>2850000</v>
+      </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>28.06.26</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="n"/>
+          <t>27.06.26</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>2815000</v>
+      </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>05.07.26</t>
+          <t>02.07.26</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>SOLD</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>RESERVED</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>缺失</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="n"/>
+          <t>PRICE_DROP</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="n">
+        <v>-35000</v>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T11:09:36</t>
+          <t>2026-07-09T09:53:11</t>
         </is>
       </c>
     </row>
@@ -5435,34 +5441,32 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>V18.02</t>
+          <t>W.14.03</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>3+Study</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>South/West/North</t>
-        </is>
-      </c>
-      <c r="F92" s="3" t="n">
-        <v>2850000</v>
-      </c>
+          <t>North/East</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="n"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
           <t>27.06.26</t>
         </is>
       </c>
       <c r="H92" s="3" t="n">
-        <v>2815000</v>
+        <v>775000</v>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
@@ -5471,17 +5475,15 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>PRICE_DROP</t>
+          <t>NEW_RELEASE</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
-      <c r="M92" s="2" t="n">
-        <v>-35000</v>
-      </c>
+      <c r="M92" s="2" t="n"/>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:53:11</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
     </row>
@@ -5493,32 +5495,34 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>W.14.03</t>
+          <t>W.30.01</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>30/31</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Penthouse</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>North/East</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="n"/>
+          <t>South/West/North</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>4000000</v>
+      </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
           <t>27.06.26</t>
         </is>
       </c>
       <c r="H93" s="3" t="n">
-        <v>775000</v>
+        <v>3990000</v>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
@@ -5527,12 +5531,14 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>NEW_RELEASE</t>
+          <t>PRICE_DROP</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
-      <c r="M93" s="2" t="n"/>
+      <c r="M93" s="2" t="n">
+        <v>-10000</v>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>2026-07-08T17:01:26</t>
@@ -5547,7 +5553,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>W.30.01</t>
+          <t>W.30.02</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5562,7 +5568,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>South/West/North</t>
+          <t>South/East/North</t>
         </is>
       </c>
       <c r="F94" s="3" t="n">
@@ -5605,35 +5611,33 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>W.30.02</t>
+          <t>W.08.01</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>30/31</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Penthouse</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>South/East/North</t>
+          <t>North/West</t>
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>4000000</v>
+        <v>775000</v>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
           <t>27.06.26</t>
         </is>
       </c>
-      <c r="H95" s="3" t="n">
-        <v>3990000</v>
-      </c>
+      <c r="H95" s="2" t="n"/>
       <c r="I95" s="2" t="inlineStr">
         <is>
           <t>02.07.26</t>
@@ -5641,14 +5645,16 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>PRICE_DROP</t>
+          <t>SOLD</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
-      <c r="L95" s="2" t="inlineStr"/>
-      <c r="M95" s="2" t="n">
-        <v>-10000</v>
-      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n"/>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>2026-07-08T17:01:26</t>
@@ -5663,12 +5669,12 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>W.08.01</t>
+          <t>W.14.01</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -5681,9 +5687,7 @@
           <t>North/West</t>
         </is>
       </c>
-      <c r="F96" s="3" t="n">
-        <v>775000</v>
-      </c>
+      <c r="F96" s="2" t="n"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
           <t>27.06.26</t>
@@ -5716,22 +5720,22 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>W12 - White City Living</t>
+          <t>W2 - Trillium</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>W.14.01</t>
+          <t>I.01.07</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -5742,30 +5746,26 @@
       <c r="F97" s="2" t="n"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>27.06.26</t>
+          <t>28.06.26</t>
         </is>
       </c>
       <c r="H97" s="2" t="n"/>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>02.07.26</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>SOLD</t>
+          <t>NEW_RELEASE</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>缺失</t>
-        </is>
-      </c>
+      <c r="L97" s="2" t="inlineStr"/>
       <c r="M97" s="2" t="n"/>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-08T16:56:04</t>
         </is>
       </c>
     </row>
@@ -5777,22 +5777,22 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>I.01.07</t>
+          <t>I.08.05</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
+          <t>South/West</t>
         </is>
       </c>
       <c r="F98" s="2" t="n"/>
@@ -5829,22 +5829,22 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>I.08.05</t>
+          <t>I.10.07</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>South/West</t>
+          <t>North/West</t>
         </is>
       </c>
       <c r="F99" s="2" t="n"/>
@@ -5881,22 +5881,22 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>I.10.07</t>
+          <t>I.14.01</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
+          <t>North/East</t>
         </is>
       </c>
       <c r="F100" s="2" t="n"/>
@@ -5905,7 +5905,9 @@
           <t>28.06.26</t>
         </is>
       </c>
-      <c r="H100" s="2" t="n"/>
+      <c r="H100" s="3" t="n">
+        <v>1598500</v>
+      </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
           <t>05.07.26</t>
@@ -5933,7 +5935,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>I.14.01</t>
+          <t>I.14.06</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -5943,12 +5945,12 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>North/East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="F101" s="2" t="n"/>
@@ -5957,9 +5959,7 @@
           <t>28.06.26</t>
         </is>
       </c>
-      <c r="H101" s="3" t="n">
-        <v>1598500</v>
-      </c>
+      <c r="H101" s="2" t="n"/>
       <c r="I101" s="2" t="inlineStr">
         <is>
           <t>05.07.26</t>
@@ -5987,22 +5987,22 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>I.14.06</t>
+          <t>I.17.03</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>South</t>
         </is>
       </c>
       <c r="F102" s="2" t="n"/>
@@ -6039,22 +6039,22 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>I.17.03</t>
+          <t>I.20.06</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North/West</t>
         </is>
       </c>
       <c r="F103" s="2" t="n"/>
@@ -6063,7 +6063,9 @@
           <t>28.06.26</t>
         </is>
       </c>
-      <c r="H103" s="2" t="n"/>
+      <c r="H103" s="3" t="n">
+        <v>2505000</v>
+      </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
           <t>05.07.26</t>
@@ -6091,33 +6093,33 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>I.20.06</t>
+          <t>I.02.05</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="n"/>
+          <t>South/ West</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>1350000</v>
+      </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
           <t>28.06.26</t>
         </is>
       </c>
-      <c r="H104" s="3" t="n">
-        <v>2505000</v>
-      </c>
+      <c r="H104" s="2" t="n"/>
       <c r="I104" s="2" t="inlineStr">
         <is>
           <t>05.07.26</t>
@@ -6125,11 +6127,15 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>NEW_RELEASE</t>
+          <t>SOLD</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr"/>
-      <c r="L104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
       <c r="M104" s="2" t="n"/>
       <c r="N104" s="2" t="inlineStr">
         <is>
@@ -6145,7 +6151,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>I.02.05</t>
+          <t>I.02.07</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -6155,17 +6161,15 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>South/ West</t>
-        </is>
-      </c>
-      <c r="F105" s="3" t="n">
-        <v>1350000</v>
-      </c>
+          <t>North/West</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="n"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
           <t>28.06.26</t>
@@ -6203,12 +6207,12 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>I.02.07</t>
+          <t>I.07.07</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -6221,7 +6225,9 @@
           <t>North/West</t>
         </is>
       </c>
-      <c r="F106" s="2" t="n"/>
+      <c r="F106" s="3" t="n">
+        <v>2005000</v>
+      </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
           <t>28.06.26</t>
@@ -6259,27 +6265,25 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>I.07.07</t>
+          <t>I.13.01</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
-        </is>
-      </c>
-      <c r="F107" s="3" t="n">
-        <v>2005000</v>
-      </c>
+          <t>North/East</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="n"/>
       <c r="G107" s="2" t="inlineStr">
         <is>
           <t>28.06.26</t>
@@ -6317,7 +6321,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>I.13.01</t>
+          <t>I.13.07</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -6327,15 +6331,17 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>North/East</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="n"/>
+          <t>North/West</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>2181500</v>
+      </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
           <t>28.06.26</t>
@@ -6373,26 +6379,26 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>I.13.07</t>
+          <t>I.15.03</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
+          <t>South</t>
         </is>
       </c>
       <c r="F109" s="3" t="n">
-        <v>2181500</v>
+        <v>1199000</v>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
@@ -6431,7 +6437,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>I.15.03</t>
+          <t>I.15.05</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -6441,17 +6447,15 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>K</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="F110" s="3" t="n">
-        <v>1199000</v>
-      </c>
+          <t>South/West</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="n"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
           <t>28.06.26</t>
@@ -6489,25 +6493,27 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>I.15.05</t>
+          <t>I.17.04</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>J</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>South/West</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="n"/>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>1115000</v>
+      </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
           <t>28.06.26</t>
@@ -6545,26 +6551,26 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>I.17.04</t>
+          <t>I.20.01</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North/East</t>
         </is>
       </c>
       <c r="F112" s="3" t="n">
-        <v>1115000</v>
+        <v>1845000</v>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
@@ -6603,12 +6609,12 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>I.20.01</t>
+          <t>I.22.01</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -6622,7 +6628,7 @@
         </is>
       </c>
       <c r="F113" s="3" t="n">
-        <v>1845000</v>
+        <v>1897000</v>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
@@ -6661,7 +6667,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>I.22.01</t>
+          <t>I.22.04*</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -6671,16 +6677,16 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>J</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>North/East</t>
+          <t>South</t>
         </is>
       </c>
       <c r="F114" s="3" t="n">
-        <v>1897000</v>
+        <v>1205000</v>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
@@ -6711,66 +6717,8 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>W2 - Trillium</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>I.22.04*</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="F115" s="3" t="n">
-        <v>1205000</v>
-      </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>28.06.26</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="n"/>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t>05.07.26</t>
-        </is>
-      </c>
-      <c r="J115" s="2" t="inlineStr">
-        <is>
-          <t>SOLD</t>
-        </is>
-      </c>
-      <c r="K115" s="2" t="inlineStr"/>
-      <c r="L115" s="2" t="inlineStr">
-        <is>
-          <t>缺失</t>
-        </is>
-      </c>
-      <c r="M115" s="2" t="n"/>
-      <c r="N115" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-08T16:56:04</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N115"/>
+  <autoFilter ref="A1:N114"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7848,7 +7796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N56"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -7862,7 +7810,7 @@
     <col width="42" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
   </cols>
@@ -9636,35 +9584,39 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>SE3 - Kidbrooke Village</t>
+          <t>SW19 - Wimbledon Bridge House (London Square)</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2-3-4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr"/>
+          <t>1 Bed</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
       <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>29.06.26</t>
+          <t>15.06.26</t>
         </is>
       </c>
       <c r="H34" s="2" t="n"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>06.07.26</t>
+          <t>29.06.26</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9673,15 +9625,11 @@
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>Show Apartment</t>
-        </is>
-      </c>
+      <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="n"/>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:53:11</t>
+          <t>2026-07-08T17:02:25</t>
         </is>
       </c>
     </row>
@@ -9693,22 +9641,22 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>102</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1 Bed</t>
+          <t>2 Bed</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>North</t>
         </is>
       </c>
       <c r="F35" s="2" t="n"/>
@@ -9717,7 +9665,9 @@
           <t>15.06.26</t>
         </is>
       </c>
-      <c r="H35" s="2" t="n"/>
+      <c r="H35" s="3" t="n">
+        <v>1185000</v>
+      </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
           <t>29.06.26</t>
@@ -9745,7 +9695,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>104</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -9755,12 +9705,12 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2 Bed</t>
+          <t>1 Bed</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="F36" s="2" t="n"/>
@@ -9770,7 +9720,7 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>1185000</v>
+        <v>710000</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
@@ -9799,22 +9749,22 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1 Bed</t>
+          <t>Suite</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="F37" s="2" t="n"/>
@@ -9824,7 +9774,7 @@
         </is>
       </c>
       <c r="H37" s="3" t="n">
-        <v>710000</v>
+        <v>512500</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
@@ -9853,12 +9803,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>56</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -9878,7 +9828,7 @@
         </is>
       </c>
       <c r="H38" s="3" t="n">
-        <v>512500</v>
+        <v>507500</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
@@ -9907,12 +9857,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>71</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -9932,7 +9882,7 @@
         </is>
       </c>
       <c r="H39" s="3" t="n">
-        <v>507500</v>
+        <v>517500</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
@@ -9961,22 +9911,22 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>93</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Suite</t>
+          <t>1 Bed</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>North</t>
         </is>
       </c>
       <c r="F40" s="2" t="n"/>
@@ -9986,7 +9936,7 @@
         </is>
       </c>
       <c r="H40" s="3" t="n">
-        <v>517500</v>
+        <v>720000</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
@@ -10010,41 +9960,37 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>SW19 - Wimbledon Bridge House (London Square)</t>
+          <t>SW6 - Chelsea Waterfront Tower East</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>1 Bed</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="n"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>15.06.26</t>
+          <t>8th June 2026</t>
         </is>
       </c>
       <c r="H41" s="3" t="n">
-        <v>720000</v>
+        <v>5842000</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>29.06.26</t>
+          <t>29th June 2026</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10057,44 +10003,48 @@
       <c r="M41" s="2" t="n"/>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:25</t>
+          <t>2026-07-08T17:02:57</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>SW6 - Chelsea Waterfront Tower East</t>
+          <t>SW6 - King's Road Park</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>G1.3-01-04</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr"/>
+          <t>2 Bedroom</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>S/W - Park Views</t>
+        </is>
+      </c>
       <c r="F42" s="2" t="n"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>8th June 2026</t>
+          <t>28.06.2026</t>
         </is>
       </c>
       <c r="H42" s="3" t="n">
-        <v>5842000</v>
+        <v>1370000</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>29th June 2026</t>
+          <t>05.07.2026</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10107,7 +10057,7 @@
       <c r="M42" s="2" t="n"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:02:57</t>
+          <t>2026-07-08T16:53:34</t>
         </is>
       </c>
     </row>
@@ -10119,12 +10069,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>G1.3-01-04</t>
+          <t>G1.4-00-06</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -10134,7 +10084,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>S/W - Park Views</t>
+          <t>S – Park Views</t>
         </is>
       </c>
       <c r="F43" s="2" t="n"/>
@@ -10143,9 +10093,7 @@
           <t>28.06.2026</t>
         </is>
       </c>
-      <c r="H43" s="3" t="n">
-        <v>1370000</v>
-      </c>
+      <c r="H43" s="2" t="n"/>
       <c r="I43" s="2" t="inlineStr">
         <is>
           <t>05.07.2026</t>
@@ -10168,39 +10116,41 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>SW6 - King's Road Park</t>
+          <t>UB1 - The Green Quarter</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>G1.4-00-06</t>
+          <t>257</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>2 Bedroom</t>
+          <t>2 Bed 2 Bath</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>S – Park Views</t>
+          <t>S &amp; E</t>
         </is>
       </c>
       <c r="F44" s="2" t="n"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>28.06.2026</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="n"/>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>545000</v>
+      </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>05.07.2026</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10213,7 +10163,7 @@
       <c r="M44" s="2" t="n"/>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T16:53:34</t>
+          <t>2026-07-09T11:09:36</t>
         </is>
       </c>
     </row>
@@ -10225,22 +10175,22 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>261</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>2 Bed 2 Bath</t>
+          <t>2 Bed 2.5 Bath</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>S &amp; E</t>
+          <t>N &amp; W</t>
         </is>
       </c>
       <c r="F45" s="2" t="n"/>
@@ -10250,7 +10200,7 @@
         </is>
       </c>
       <c r="H45" s="3" t="n">
-        <v>545000</v>
+        <v>555000</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
@@ -10279,12 +10229,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>269</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -10304,7 +10254,7 @@
         </is>
       </c>
       <c r="H46" s="3" t="n">
-        <v>555000</v>
+        <v>565000</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
@@ -10333,12 +10283,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>285</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -10358,7 +10308,7 @@
         </is>
       </c>
       <c r="H47" s="3" t="n">
-        <v>565000</v>
+        <v>575000</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
@@ -10382,41 +10332,41 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>UB1 - The Green Quarter</t>
+          <t>W12 - White City Living</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>W.14.03</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>2 Bed 2.5 Bath</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>N &amp; W</t>
+          <t>North/East</t>
         </is>
       </c>
       <c r="F48" s="2" t="n"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>28.06.26</t>
+          <t>27.06.26</t>
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>575000</v>
+        <v>775000</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>05.07.26</t>
+          <t>02.07.26</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -10429,48 +10379,46 @@
       <c r="M48" s="2" t="n"/>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T11:09:36</t>
+          <t>2026-07-08T17:01:26</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>W12 - White City Living</t>
+          <t>W2 - Trillium</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>W.14.03</t>
+          <t>I.01.07</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>North/East</t>
+          <t>North/West</t>
         </is>
       </c>
       <c r="F49" s="2" t="n"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>27.06.26</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="n">
-        <v>775000</v>
-      </c>
+          <t>28.06.26</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="n"/>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>02.07.26</t>
+          <t>05.07.26</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -10483,7 +10431,7 @@
       <c r="M49" s="2" t="n"/>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T17:01:26</t>
+          <t>2026-07-08T16:56:04</t>
         </is>
       </c>
     </row>
@@ -10495,22 +10443,22 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>I.01.07</t>
+          <t>I.08.05</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
+          <t>South/West</t>
         </is>
       </c>
       <c r="F50" s="2" t="n"/>
@@ -10547,22 +10495,22 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>I.08.05</t>
+          <t>I.10.07</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>South/West</t>
+          <t>North/West</t>
         </is>
       </c>
       <c r="F51" s="2" t="n"/>
@@ -10599,22 +10547,22 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>I.10.07</t>
+          <t>I.14.01</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>North/West</t>
+          <t>North/East</t>
         </is>
       </c>
       <c r="F52" s="2" t="n"/>
@@ -10623,7 +10571,9 @@
           <t>28.06.26</t>
         </is>
       </c>
-      <c r="H52" s="2" t="n"/>
+      <c r="H52" s="3" t="n">
+        <v>1598500</v>
+      </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
           <t>05.07.26</t>
@@ -10651,7 +10601,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>I.14.01</t>
+          <t>I.14.06</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -10661,12 +10611,12 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>North/East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="F53" s="2" t="n"/>
@@ -10675,9 +10625,7 @@
           <t>28.06.26</t>
         </is>
       </c>
-      <c r="H53" s="3" t="n">
-        <v>1598500</v>
-      </c>
+      <c r="H53" s="2" t="n"/>
       <c r="I53" s="2" t="inlineStr">
         <is>
           <t>05.07.26</t>
@@ -10705,22 +10653,22 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>I.14.06</t>
+          <t>I.17.03</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>South</t>
         </is>
       </c>
       <c r="F54" s="2" t="n"/>
@@ -10757,22 +10705,22 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>I.17.03</t>
+          <t>I.20.06</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North/West</t>
         </is>
       </c>
       <c r="F55" s="2" t="n"/>
@@ -10781,7 +10729,9 @@
           <t>28.06.26</t>
         </is>
       </c>
-      <c r="H55" s="2" t="n"/>
+      <c r="H55" s="3" t="n">
+        <v>2505000</v>
+      </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
           <t>05.07.26</t>
@@ -10801,62 +10751,8 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>W2 - Trillium</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>I.20.06</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>North/West</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="n"/>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>28.06.26</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="n">
-        <v>2505000</v>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>05.07.26</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>NEW_RELEASE</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="2" t="inlineStr"/>
-      <c r="M56" s="2" t="n"/>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-08T16:56:04</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N56"/>
+  <autoFilter ref="A1:N55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/outputs/weekly_unit_change_database.xlsx
+++ b/outputs/weekly_unit_change_database.xlsx
@@ -58854,7 +58854,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -58917,11 +58917,7 @@
           <t>E14 - South Quay Plaza</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>E14 - South Quay Plaza · sqp</t>
-        </is>
-      </c>
+      <c r="B2" s="2" t="inlineStr"/>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>SQP Daily Price List 25.06.2026.pdf</t>
@@ -58932,17 +58928,11 @@
           <t>SQP Daily Price List 04.07.2026.pdf</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
